--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -415,6 +415,70 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2A78D6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="EB6834"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1BAF7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="EDA100"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="&quot;$&quot;#,##0&quot;B&quot;"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'Summary'!$A$16:$A$19</f>
@@ -426,15 +490,16 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="60"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -446,6 +511,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -466,6 +532,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -494,7 +561,7 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
+        <barDir val="bar"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
@@ -509,6 +576,84 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A29C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="A3A29C"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2A78D6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="EB6834"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1BAF7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="EDA100"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="&quot;$&quot;#,##0&quot;B&quot;"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'Value Bridge'!$A$49:$A$53</f>
@@ -520,15 +665,16 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="60"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -540,6 +686,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -560,6 +707,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -2122,16 +2122,16 @@
         </is>
       </c>
       <c r="E14" s="48" t="n">
-        <v>-965.5958029079999</v>
+        <v>-960.45442678288</v>
       </c>
       <c r="F14" s="48" t="n">
-        <v>571.8114816440648</v>
+        <v>569.1669985864507</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>-393.7843212639353</v>
+        <v>-391.2874281964292</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>0.4891057518312402</v>
+        <v>0.4889942299198121</v>
       </c>
     </row>
     <row r="16">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="E81" s="78" t="n">
-        <v>154.8429860104542</v>
+        <v>149.7773849697697</v>
       </c>
       <c r="F81" s="79" t="n">
-        <v>-11.13717395678219</v>
+        <v>-10.77282758605313</v>
       </c>
       <c r="G81" s="80" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="E82" s="78" t="n">
-        <v>158.8547874640003</v>
+        <v>153.657942599222</v>
       </c>
       <c r="F82" s="79" t="n">
-        <v>-7.125372503236122</v>
+        <v>-6.892269956600785</v>
       </c>
       <c r="G82" s="81" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="E83" s="78" t="n">
-        <v>159.8723512892945</v>
+        <v>154.6422173973205</v>
       </c>
       <c r="F83" s="79" t="n">
-        <v>-6.107808677941904</v>
+        <v>-5.907995158502331</v>
       </c>
       <c r="G83" s="81" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="E84" s="78" t="n">
-        <v>160.0192444322226</v>
+        <v>154.784305013845</v>
       </c>
       <c r="F84" s="79" t="n">
-        <v>-5.960915535013811</v>
+        <v>-5.765907541977811</v>
       </c>
       <c r="G84" s="81" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  infra share strips non-AI (Amazon AWS 68%); server share CFO-disclosed (MSFT ~50%, Google 60%); accel-within-server ~67-80% from BOM.</t>
+          <t xml:space="preserve">  infra (data-center) share from 10-K/10-Q P&amp;E and segment notes (MSFT 97%, Alphabet 93-95%, Meta 95-98%, Amazon AWS 68-76%); server share CFO-disclosed (MSFT ~50%, Google 60%); accel-within-server ~67-80% from BOM.</t>
         </is>
       </c>
     </row>
@@ -5997,28 +5997,28 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>- Net AI FY25: 6 named firms spend ~$375B (capex+opex) vs ~$79B AI revenue = ~ -$295B/yr cash burn.</t>
+          <t>- Net AI FY25: 6 named firms spend ~$362B (capex+opex) vs ~$79B AI revenue = ~ -$283B/yr cash burn.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>- With our architecture: spend cut ~$166B -&gt; burn shrinks to ~ -$129B/yr (~44% of AI spend cut).</t>
+          <t>- With our architecture: spend cut ~$161B -&gt; burn shrinks to ~ -$122B/yr (~44% of AI spend cut).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>- Spend-cut value (named floor, 6% discount rate): FY25 ~$166B/yr (~$2.8T capitalized); FY26 r/r ~$382B/yr (~$6.4T). Ceiling: within rounding of Today (the cut saturates).</t>
+          <t>- Spend-cut value (named floor, 6% discount rate): FY25 ~$161B/yr (~$2.7T capitalized); FY26 r/r ~$380B/yr (~$6.3T). Ceiling: within rounding of Today (the cut saturates).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>- GLOBAL estimate (named ~80% of world AI capex): FY25 ~$3.5T, FY26 ~$8.0T capitalized. Clearly an estimate.</t>
+          <t>- GLOBAL estimate (named ~80% of world AI capex): FY25 ~$3.3T, FY26 ~$7.9T capitalized. Clearly an estimate.</t>
         </is>
       </c>
     </row>
@@ -8953,14 +8953,14 @@
         </is>
       </c>
       <c r="B4" s="33" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>strips non-AI (Amazon = AWS only)</t>
+          <t>FILING: P&amp;E note (FY25/FY26 10-K). Leasehold improvements, the only non-datacenter class, are $2.5B of $86.6B (FY25) and $4.2B of $133.1B (FY26) of gross additions -&gt; 97%.</t>
         </is>
       </c>
     </row>
@@ -9641,14 +9641,14 @@
         </is>
       </c>
       <c r="B4" s="33" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>strips non-AI (Amazon = AWS only)</t>
+          <t>FILING: P&amp;E note. Technical infrastructure +$61.8B vs office space +$2.9B and corporate +$1.9B in 2025 (10-K) -&gt; 93%; +$43.5B vs +$2.3B office in H1 2026 (10-Q) -&gt; 95%.</t>
         </is>
       </c>
     </row>
@@ -10318,11 +10318,11 @@
         <v>0.68</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>strips non-AI (Amazon = AWS only)</t>
+          <t>FILING: segment note, AWS share of net P&amp;E additions. $96.5B of $142.4B in 2025 (10-K) -&gt; 68%; $90.1B of $118.6B in H1 2026 (10-Q) -&gt; 76%. Strips fulfillment/logistics.</t>
         </is>
       </c>
     </row>
@@ -10989,14 +10989,14 @@
         </is>
       </c>
       <c r="B4" s="33" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>strips non-AI (Amazon = AWS only)</t>
+          <t>FILING: Note 6 P&amp;E. Leasehold improvements + equipment and other are $3.3B of $69.1B gross additions in 2025 (10-K) -&gt; 95%; $0.95B of $59.1B in H1 2026 (10-Q) -&gt; 98%.</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>strips non-AI (Amazon = AWS only)</t>
+          <t>ESTIMATE: the P&amp;E note has no office line (buildings mix datacenters with the Nashville HQ build); capex growth is 'primarily due to the expansion of our data centers' (FY26 10-K).</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>strips non-AI (Amazon = AWS only)</t>
+          <t>FILING: capex is the AI segment's own figure (S-1; Q2 2026 10-Q segment note, $23.6B in H1 2026).</t>
         </is>
       </c>
     </row>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -33,7 +33,7 @@
     <definedName name="ServeThroughput">Levers!$C$11</definedName>
     <definedName name="TrainLever">Levers!$C$14</definedName>
     <definedName name="ServeComputeLever">Levers!$C$16</definedName>
-    <definedName name="MemShare">Levers!$C$17</definedName>
+    <definedName name="ServeGPULever">Levers!$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,20 +447,6 @@
             <idx val="2"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="1BAF7A"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill>
                 <a:srgbClr val="EDA100"/>
               </a:solidFill>
               <a:ln>
@@ -481,12 +467,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Summary'!$A$16:$A$19</f>
+              <f>'Summary'!$A$16:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$B$16:$B$19</f>
+              <f>'Summary'!$B$16:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -1272,7 +1258,7 @@
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>B16/$B$20</f>
+        <f>B16/$B$19</f>
         <v/>
       </c>
       <c r="D16" s="3">
@@ -1283,7 +1269,7 @@
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Serving: memory</t>
+          <t>Serving GPUs</t>
         </is>
       </c>
       <c r="B17" s="6">
@@ -1291,70 +1277,51 @@
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>B17/$B$20</f>
+        <f>B17/$B$19</f>
         <v/>
       </c>
       <c r="D17" s="3">
-        <f>"A transformer's memory grows with every token of every live conversation; Helarctos keeps a fixed-size state → ÷"&amp;TEXT(MemoryLever,"0")&amp;" memory per conversation (memory is ~60% of a GPU's cost)."</f>
+        <f>"A transformer's memory grows with every token of every live conversation; Helarctos keeps a fixed-size state (÷"&amp;TEXT(MemoryLever,"0")&amp;" memory) and does "&amp;TEXT(ServeComputeLever,"0")&amp;"× less compute per token. A GPU is bought whole, so the fleet shrinks by whichever limit binds: "&amp;TEXT(ServeGPULever,"0")&amp;"× fewer serving GPUs."</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Serving: compute</t>
+          <t>Power &amp; operations</t>
         </is>
       </c>
       <c r="B18" s="6">
-        <f>'Value Bridge'!H70</f>
+        <f>'Value Bridge'!K70</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>B18/$B$20</f>
-        <v/>
-      </c>
-      <c r="D18" s="3">
-        <f>"Smaller model ("&amp;TEXT(SmallerModel,"0.0")&amp;"×) × far more conversations per GPU ("&amp;TEXT(ServeThroughput,"0")&amp;"× at a 128k-token average) → "&amp;TEXT(ServeComputeLever,"0")&amp;"× less compute per token served."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1">
+        <f>B18/$B$19</f>
+        <v/>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Fewer chips draw less power and need less cooling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Power &amp; operations</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>'Value Bridge'!K70</f>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B19" s="15">
+        <f>SUM(B16:B18)</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f>B19/$B$20</f>
-        <v/>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Fewer chips draw less power and need less cooling.</t>
-        </is>
+        <f>SUM(C16:C18)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <f>SUM(B16:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="14">
-        <f>SUM(C16:C19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Step-by-step build and the one-lever-at-a-time view: Value Bridge tab.</t>
         </is>
@@ -1643,7 +1610,7 @@
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Costs add; they don't multiply. A GPU's cost is ~60% memory and ~40% compute. Once Helarctos cuts the memory needed 100× and the compute needed hundreds of times, ~99% of the chip bill for the same AI output is gone — bigger multiples can only move the last 1%. So the dollars are set by how much these firms spend on chips, not by how large the multiple is. We report dollars.</t>
+          <t>Multiples don't multiply. A GPU is bought whole — memory and compute together — so a serving fleet shrinks by whichever need falls LEAST (here the conservative 100× memory cap), not by 100 × 793. Cutting a fleet 100× already removes 99% of it; bigger multiples can only move the last 1%. So the dollars are set by how much these firms spend on chips, not by how large the multiple is. We report dollars.</t>
         </is>
       </c>
     </row>
@@ -1728,19 +1695,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B38:G38"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D19:G19"/>
     <mergeCell ref="B40:G40"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="B39:G39"/>
@@ -6516,29 +6482,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>STEP 4 — SERVING: less memory and more conversations per GPU → smaller serving fleet</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>$ today</t>
-        </is>
-      </c>
+          <t>STEP 4 — SERVING: less memory and more conversations per GPU → fewer serving GPUs</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>falls by</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>$ needed</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>$ avoided</t>
-        </is>
-      </c>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
@@ -6558,64 +6512,75 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Memory part of those chips (≈60% of cost)</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
-        <f>B27*MemShare</f>
-        <v/>
+          <t>Memory needed per conversation falls by</t>
+        </is>
       </c>
       <c r="C28" s="23">
         <f>MemoryLever</f>
         <v/>
       </c>
-      <c r="D28" s="6">
-        <f>B28/C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="6">
-        <f>B28-D28</f>
-        <v/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>fixed-size state (lever 4)</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Compute part of those chips (≈40% of cost)</t>
-        </is>
-      </c>
-      <c r="B29" s="6">
-        <f>B27*(1-MemShare)</f>
-        <v/>
+          <t>Compute needed per token falls by</t>
+        </is>
       </c>
       <c r="C29" s="21">
         <f>ServeComputeLever</f>
         <v/>
       </c>
-      <c r="D29" s="6">
-        <f>B29/C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="6">
-        <f>B29-D29</f>
-        <v/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>smaller model × more conversations per GPU (levers 1 × 5)</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
+          <t>GPUs needed fall by — whichever limit binds</t>
+        </is>
+      </c>
+      <c r="C30" s="22">
+        <f>ServeGPULever</f>
+        <v/>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>the smaller of the two: a GPU is bought whole</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Serving fleet needed with Helarctos</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <f>B27/C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
           <t>SERVING CAPEX AVOIDED</t>
         </is>
       </c>
-      <c r="B30" s="15">
-        <f>E28+E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Memory: a transformer's memory grows with every token of every live conversation, so long conversations fill a GPU after one or two users; Helarctos keeps a fixed-size state (lever 4). Compute: the smaller model does less work per token and each GPU serves many more conversations at once (levers 1 × 5).</t>
+      <c r="B32" s="15">
+        <f>B27-B31</f>
+        <v/>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>A GPU brings memory and compute together; the fleet must cover whichever runs out first. Transformers at long context run out of MEMORY (the growing KV cache), so memory is the limit we relieve first; compute then binds only if it falls less than memory.</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6659,7 @@
         </is>
       </c>
       <c r="B39" s="6">
-        <f>B30</f>
+        <f>B32</f>
         <v/>
       </c>
     </row>
@@ -6743,7 +6708,7 @@
         </is>
       </c>
       <c r="B43" s="14">
-        <f>(B23+B30)/B7</f>
+        <f>(B23+B32)/B7</f>
         <v/>
       </c>
     </row>
@@ -6812,7 +6777,7 @@
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>Chip fleet cut</t>
+          <t>Chip fleet cut (serving GPUs fall by the smaller)</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -6842,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="25">
-        <f>(D70*(1-1/B49)+E70*(MemShare*(1-1/C49)+(1-MemShare)*(1-1/D49)))/B70</f>
+        <f>(D70*(1-1/B49)+E70*(1-1/MIN(C49,D49)))/B70</f>
         <v/>
       </c>
       <c r="F49" s="18">
@@ -6872,7 +6837,7 @@
         <v/>
       </c>
       <c r="E50" s="25">
-        <f>(D70*(1-1/B50)+E70*(MemShare*(1-1/C50)+(1-MemShare)*(1-1/D50)))/B70</f>
+        <f>(D70*(1-1/B50)+E70*(1-1/MIN(C50,D50)))/B70</f>
         <v/>
       </c>
       <c r="F50" s="18">
@@ -6903,7 +6868,7 @@
         <v/>
       </c>
       <c r="E51" s="25">
-        <f>(D70*(1-1/B51)+E70*(MemShare*(1-1/C51)+(1-MemShare)*(1-1/D51)))/B70</f>
+        <f>(D70*(1-1/B51)+E70*(1-1/MIN(C51,D51)))/B70</f>
         <v/>
       </c>
       <c r="F51" s="18">
@@ -6934,7 +6899,7 @@
         <v/>
       </c>
       <c r="E52" s="25">
-        <f>(D70*(1-1/B52)+E70*(MemShare*(1-1/C52)+(1-MemShare)*(1-1/D52)))/B70</f>
+        <f>(D70*(1-1/B52)+E70*(1-1/MIN(C52,D52)))/B70</f>
         <v/>
       </c>
       <c r="F52" s="18">
@@ -6965,7 +6930,7 @@
         <v/>
       </c>
       <c r="E53" s="25">
-        <f>(D70*(1-1/B53)+E70*(MemShare*(1-1/C53)+(1-MemShare)*(1-1/D53)))/B70</f>
+        <f>(D70*(1-1/B53)+E70*(1-1/MIN(C53,D53)))/B70</f>
         <v/>
       </c>
       <c r="F53" s="18">
@@ -6980,7 +6945,7 @@
     <row r="55" ht="62" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Read this as: the smaller model alone removes about half the chip bill (and nearly all of the training bill, since fewer parameters AND fewer tokens compound). Fixed-size memory is the biggest single serving lever because memory is ~60% of what a GPU costs. The later levers have large multiples but add little, because by then over 90% of the cost is already gone: a cost can only fall to zero once. That is why this workbook reports dollars, not multiples. The order is the storyline; the end point does not depend on it.</t>
+          <t>Read this as: the smaller model alone removes nearly all of the TRAINING bill (fewer parameters AND fewer tokens compound) but no serving GPUs — at long context a transformer's serving GPUs are full of memory (the growing KV cache), not busy computing, and a smaller model doesn't change that. Fixed-size memory unlocks serving, until compute becomes the limit; many more conversations per GPU lifts that limit. The last levers have big multiples but add little, because by then over 95% of the cost is already gone: a cost can only fall to zero once. That is why this workbook reports dollars, not multiples. The order is the storyline; the end point does not depend on it.</t>
         </is>
       </c>
     </row>
@@ -7002,7 +6967,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Totals tab, FY2026 spend cut (whole fleet priced on serving levers)</t>
+          <t>Totals tab, FY2026 spend cut (memory and compute priced separately, ~154×)</t>
         </is>
       </c>
       <c r="B58" s="6">
@@ -7013,7 +6978,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>This bridge (training priced on its own lever)</t>
+          <t>This bridge (training on GPU-hours, serving on whole GPUs)</t>
         </is>
       </c>
       <c r="B59" s="6">
@@ -7093,12 +7058,12 @@
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>Serving memory avoided</t>
+          <t>Serving capex avoided</t>
         </is>
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>Serving compute avoided</t>
+          <t>Serving fleet needed</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -7174,15 +7139,15 @@
         <v/>
       </c>
       <c r="G64" s="6">
-        <f>E64*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H64" s="6">
-        <f>E64*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E64*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H64" s="28">
+        <f>E64/ServeGPULever</f>
         <v/>
       </c>
       <c r="I64" s="6">
-        <f>F64+G64+H64</f>
+        <f>F64+G64</f>
         <v/>
       </c>
       <c r="J64" s="28">
@@ -7245,15 +7210,15 @@
         <v/>
       </c>
       <c r="G65" s="6">
-        <f>E65*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H65" s="6">
-        <f>E65*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E65*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H65" s="28">
+        <f>E65/ServeGPULever</f>
         <v/>
       </c>
       <c r="I65" s="6">
-        <f>F65+G65+H65</f>
+        <f>F65+G65</f>
         <v/>
       </c>
       <c r="J65" s="28">
@@ -7316,15 +7281,15 @@
         <v/>
       </c>
       <c r="G66" s="6">
-        <f>E66*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H66" s="6">
-        <f>E66*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E66*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H66" s="28">
+        <f>E66/ServeGPULever</f>
         <v/>
       </c>
       <c r="I66" s="6">
-        <f>F66+G66+H66</f>
+        <f>F66+G66</f>
         <v/>
       </c>
       <c r="J66" s="28">
@@ -7387,15 +7352,15 @@
         <v/>
       </c>
       <c r="G67" s="6">
-        <f>E67*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H67" s="6">
-        <f>E67*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E67*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H67" s="28">
+        <f>E67/ServeGPULever</f>
         <v/>
       </c>
       <c r="I67" s="6">
-        <f>F67+G67+H67</f>
+        <f>F67+G67</f>
         <v/>
       </c>
       <c r="J67" s="28">
@@ -7458,15 +7423,15 @@
         <v/>
       </c>
       <c r="G68" s="6">
-        <f>E68*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H68" s="6">
-        <f>E68*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E68*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H68" s="28">
+        <f>E68/ServeGPULever</f>
         <v/>
       </c>
       <c r="I68" s="6">
-        <f>F68+G68+H68</f>
+        <f>F68+G68</f>
         <v/>
       </c>
       <c r="J68" s="28">
@@ -7529,15 +7494,15 @@
         <v/>
       </c>
       <c r="G69" s="6">
-        <f>E69*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H69" s="6">
-        <f>E69*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E69*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H69" s="28">
+        <f>E69/ServeGPULever</f>
         <v/>
       </c>
       <c r="I69" s="6">
-        <f>F69+G69+H69</f>
+        <f>F69+G69</f>
         <v/>
       </c>
       <c r="J69" s="28">
@@ -7603,7 +7568,7 @@
         <f>SUM(G64:G69)</f>
         <v/>
       </c>
-      <c r="H70" s="18">
+      <c r="H70" s="29">
         <f>SUM(H64:H69)</f>
         <v/>
       </c>
@@ -7700,12 +7665,12 @@
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>Serving memory avoided</t>
+          <t>Serving capex avoided</t>
         </is>
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>Serving compute avoided</t>
+          <t>Serving fleet needed</t>
         </is>
       </c>
       <c r="I74" s="16" t="inlineStr">
@@ -7781,15 +7746,15 @@
         <v/>
       </c>
       <c r="G75" s="6">
-        <f>E75*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H75" s="6">
-        <f>E75*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E75*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H75" s="28">
+        <f>E75/ServeGPULever</f>
         <v/>
       </c>
       <c r="I75" s="6">
-        <f>F75+G75+H75</f>
+        <f>F75+G75</f>
         <v/>
       </c>
       <c r="J75" s="28">
@@ -7852,15 +7817,15 @@
         <v/>
       </c>
       <c r="G76" s="6">
-        <f>E76*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H76" s="6">
-        <f>E76*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E76*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H76" s="28">
+        <f>E76/ServeGPULever</f>
         <v/>
       </c>
       <c r="I76" s="6">
-        <f>F76+G76+H76</f>
+        <f>F76+G76</f>
         <v/>
       </c>
       <c r="J76" s="28">
@@ -7923,15 +7888,15 @@
         <v/>
       </c>
       <c r="G77" s="6">
-        <f>E77*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H77" s="6">
-        <f>E77*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E77*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H77" s="28">
+        <f>E77/ServeGPULever</f>
         <v/>
       </c>
       <c r="I77" s="6">
-        <f>F77+G77+H77</f>
+        <f>F77+G77</f>
         <v/>
       </c>
       <c r="J77" s="28">
@@ -7994,15 +7959,15 @@
         <v/>
       </c>
       <c r="G78" s="6">
-        <f>E78*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H78" s="6">
-        <f>E78*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E78*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H78" s="28">
+        <f>E78/ServeGPULever</f>
         <v/>
       </c>
       <c r="I78" s="6">
-        <f>F78+G78+H78</f>
+        <f>F78+G78</f>
         <v/>
       </c>
       <c r="J78" s="28">
@@ -8065,15 +8030,15 @@
         <v/>
       </c>
       <c r="G79" s="6">
-        <f>E79*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H79" s="6">
-        <f>E79*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E79*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H79" s="28">
+        <f>E79/ServeGPULever</f>
         <v/>
       </c>
       <c r="I79" s="6">
-        <f>F79+G79+H79</f>
+        <f>F79+G79</f>
         <v/>
       </c>
       <c r="J79" s="28">
@@ -8136,15 +8101,15 @@
         <v/>
       </c>
       <c r="G80" s="6">
-        <f>E80*MemShare*(1-1/MemoryLever)</f>
-        <v/>
-      </c>
-      <c r="H80" s="6">
-        <f>E80*(1-MemShare)*(1-1/ServeComputeLever)</f>
+        <f>E80*(1-1/ServeGPULever)</f>
+        <v/>
+      </c>
+      <c r="H80" s="28">
+        <f>E80/ServeGPULever</f>
         <v/>
       </c>
       <c r="I80" s="6">
-        <f>F80+G80+H80</f>
+        <f>F80+G80</f>
         <v/>
       </c>
       <c r="J80" s="28">
@@ -8210,7 +8175,7 @@
         <f>SUM(G75:G80)</f>
         <v/>
       </c>
-      <c r="H81" s="18">
+      <c r="H81" s="29">
         <f>SUM(H75:H80)</f>
         <v/>
       </c>
@@ -8252,25 +8217,28 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="21">
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="D10:I10"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D6:I6"/>
     <mergeCell ref="D21:I21"/>
-    <mergeCell ref="D45:I45"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8527,7 +8495,7 @@
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>Serving memory (≈60% of a GPU's cost)</t>
+          <t>Serving GPUs (the memory limit)</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8534,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>Serving compute (≈40% of a GPU's cost)</t>
+          <t>Serving GPUs (the compute limit)</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8571,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Serving: memory needed falls by</t>
+          <t>Serving: memory needed per conversation falls by</t>
         </is>
       </c>
       <c r="C15" s="32">
@@ -8619,7 +8587,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Serving: compute needed falls by</t>
+          <t>Serving: compute needed per token falls by</t>
         </is>
       </c>
       <c r="C16" s="22">
@@ -8635,32 +8603,32 @@
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Memory share of a GPU's cost</t>
-        </is>
-      </c>
-      <c r="C17" s="19">
-        <f>Inputs!$B$4</f>
+          <t>Serving: GPUs needed fall by</t>
+        </is>
+      </c>
+      <c r="C17" s="22">
+        <f>MIN(MemoryLever,ServeComputeLever)</f>
         <v/>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>HBM memory + its packaging ≈ 60%, the compute die ≈ 40% (chip teardowns; see Evidence).</t>
+          <t>A GPU is bought whole — memory and compute come together. The serving fleet has to cover whichever runs out first, so it shrinks by the SMALLER of the two levers (here the conservative ÷100 memory cap). Multiplying them (100 × 793 = 79,000×) would be wrong.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Serving: fleet cost falls by (blended)</t>
+          <t>For reference: technical tabs' blended serving cut</t>
         </is>
       </c>
       <c r="C18" s="22">
-        <f>1/(MemShare/MemoryLever+(1-MemShare)/ServeComputeLever)</f>
+        <f>Inputs!$B$20</f>
         <v/>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Costs add, they don't multiply: the less-improved part (here memory) sets the floor. This is why 100× and 793× combine to ~154×, not 79,000×.</t>
+          <t>The technical appendix (Totals, company tabs) prices memory (~60% of a GPU's cost) and compute (~40%) separately and blends them (~154×). Same chip bill, under $1B apart on FY2026.</t>
         </is>
       </c>
     </row>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -443,20 +443,6 @@
               </a:ln>
             </spPr>
           </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="EDA100"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="EDA100"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <numFmt formatCode="&quot;$&quot;#,##0&quot;B&quot;"/>
             <showLegendKey val="0"/>
@@ -467,12 +453,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Summary'!$A$16:$A$18</f>
+              <f>'Summary'!$A$16:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$B$16:$B$18</f>
+              <f>'Summary'!$B$16:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -618,20 +604,6 @@
               </a:ln>
             </spPr>
           </dPt>
-          <dPt>
-            <idx val="4"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="EDA100"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="EDA100"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <numFmt formatCode="&quot;$&quot;#,##0&quot;B&quot;"/>
             <showLegendKey val="0"/>
@@ -642,12 +614,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Value Bridge'!$A$49:$A$53</f>
+              <f>'Value Bridge'!$A$49:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Value Bridge'!$F$49:$F$53</f>
+              <f>'Value Bridge'!$F$49:$F$52</f>
             </numRef>
           </val>
         </ser>
@@ -706,7 +678,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -1046,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1055,7 +1027,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1073,7 +1046,7 @@
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3">
-        <f>"In FY2026 the six largest AI spenders (Microsoft, Alphabet, Amazon, Meta, Oracle, SpaceX) will spend ~$"&amp;TEXT('Value Bridge'!M70,"#,##0")&amp;"B on AI and earn ~$"&amp;TEXT('Value Bridge'!O70,"#,##0")&amp;"B from it. Helarctos models do the same AI work — training and serving at the same quality — on a fraction of the hardware. This page shows how much of that spend becomes unnecessary, and where the savings come from."</f>
+        <f>"In FY2026 the six largest AI spenders (Microsoft, Alphabet, Amazon, Meta, Oracle, SpaceX) will spend ~$"&amp;TEXT('Value Bridge'!M70,"#,##0")&amp;"B on AI and earn ~$"&amp;TEXT('Value Bridge'!O70,"#,##0")&amp;"B from it. Helarctos models do the same AI work — training and inference at the same quality — on a fraction of the hardware. This page shows how much of that spend becomes unnecessary, and where the savings come from."</f>
         <v/>
       </c>
     </row>
@@ -1225,12 +1198,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>$B / yr</t>
+          <t>$B / yr (capex + power)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1247,81 +1220,61 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
-    <row r="16" ht="46" customHeight="1">
+    <row r="16" ht="62" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Training clusters</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="B16" s="6">
-        <f>'Value Bridge'!F70</f>
+        <f>'Value Bridge'!F70+'Value Bridge'!J70</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>B16/$B$19</f>
+        <f>B16/$B$18</f>
         <v/>
       </c>
       <c r="D16" s="3">
-        <f>"Same-quality model is "&amp;TEXT(SmallerModel,"0.0")&amp;"× smaller and needs "&amp;TEXT(FewerTokens,"0.0")&amp;"× fewer training tokens; each token trains "&amp;TEXT(TrainSpeed,"0.0")&amp;"× faster on long documents → "&amp;TEXT(TrainLever,"0")&amp;"× fewer GPU-hours → training clusters (and their capex) shrink."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1">
+        <f>"Same-quality model is "&amp;TEXT(SmallerModel,"0.0")&amp;"× smaller and needs "&amp;TEXT(FewerTokens,"0.0")&amp;"× fewer training tokens (training speed per token is about the same) → "&amp;TEXT(TrainLever,"0")&amp;"× fewer GPU-hours → smaller training clusters, and the power they would draw."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Serving GPUs</t>
+          <t>Inference</t>
         </is>
       </c>
       <c r="B17" s="6">
-        <f>'Value Bridge'!G70</f>
+        <f>'Value Bridge'!G70+'Value Bridge'!K70</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>B17/$B$19</f>
+        <f>B17/$B$18</f>
         <v/>
       </c>
       <c r="D17" s="3">
-        <f>"A transformer's memory grows with every token of every live conversation; Helarctos keeps a fixed-size state (÷"&amp;TEXT(MemoryLever,"0")&amp;" memory) and does "&amp;TEXT(ServeComputeLever,"0")&amp;"× less compute per token. A GPU is bought whole, so the fleet shrinks by whichever limit binds: "&amp;TEXT(ServeGPULever,"0")&amp;"× fewer serving GPUs."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
+        <f>"A transformer's memory grows with every token of every live conversation; Helarctos keeps a fixed-size state (÷"&amp;TEXT(MemoryLever,"0")&amp;" memory) and does "&amp;TEXT(ServeComputeLever,"0")&amp;"× less compute per token. A GPU is bought whole, so the fleet shrinks by whichever limit binds: "&amp;TEXT(ServeGPULever,"0")&amp;"× fewer inference GPUs, and their power."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Power &amp; operations</t>
-        </is>
-      </c>
-      <c r="B18" s="6">
-        <f>'Value Bridge'!K70</f>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="15">
+        <f>SUM(B16:B17)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>B18/$B$19</f>
-        <v/>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Fewer chips draw less power and need less cooling.</t>
-        </is>
+        <f>SUM(C16:C17)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="15">
-        <f>SUM(B16:B18)</f>
-        <v/>
-      </c>
-      <c r="C19" s="14">
-        <f>SUM(C16:C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Step-by-step build and the one-lever-at-a-time view: Value Bridge tab.</t>
         </is>
@@ -1339,6 +1292,7 @@
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -1353,25 +1307,30 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
+          <t>Training saving</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Inference saving</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
           <t>Helarctos saving / yr</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>% of AI spend</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>…of which training</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>Net AI today</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>Net AI with Helarctos</t>
         </is>
@@ -1388,22 +1347,26 @@
         <v/>
       </c>
       <c r="C25" s="6">
+        <f>'Value Bridge'!F64+'Value Bridge'!J64</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f>'Value Bridge'!G64+'Value Bridge'!K64</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
         <f>'Value Bridge'!L64</f>
         <v/>
       </c>
-      <c r="D25" s="14">
+      <c r="F25" s="14">
         <f>'Value Bridge'!N64</f>
         <v/>
       </c>
-      <c r="E25" s="6">
-        <f>'Value Bridge'!F64</f>
-        <v/>
-      </c>
-      <c r="F25" s="6">
+      <c r="G25" s="6">
         <f>'Value Bridge'!P64</f>
         <v/>
       </c>
-      <c r="G25" s="6">
+      <c r="H25" s="6">
         <f>'Value Bridge'!Q64</f>
         <v/>
       </c>
@@ -1419,22 +1382,26 @@
         <v/>
       </c>
       <c r="C26" s="6">
+        <f>'Value Bridge'!F65+'Value Bridge'!J65</f>
+        <v/>
+      </c>
+      <c r="D26" s="6">
+        <f>'Value Bridge'!G65+'Value Bridge'!K65</f>
+        <v/>
+      </c>
+      <c r="E26" s="6">
         <f>'Value Bridge'!L65</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="F26" s="14">
         <f>'Value Bridge'!N65</f>
         <v/>
       </c>
-      <c r="E26" s="6">
-        <f>'Value Bridge'!F65</f>
-        <v/>
-      </c>
-      <c r="F26" s="6">
+      <c r="G26" s="6">
         <f>'Value Bridge'!P65</f>
         <v/>
       </c>
-      <c r="G26" s="6">
+      <c r="H26" s="6">
         <f>'Value Bridge'!Q65</f>
         <v/>
       </c>
@@ -1450,22 +1417,26 @@
         <v/>
       </c>
       <c r="C27" s="6">
+        <f>'Value Bridge'!F66+'Value Bridge'!J66</f>
+        <v/>
+      </c>
+      <c r="D27" s="6">
+        <f>'Value Bridge'!G66+'Value Bridge'!K66</f>
+        <v/>
+      </c>
+      <c r="E27" s="6">
         <f>'Value Bridge'!L66</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="F27" s="14">
         <f>'Value Bridge'!N66</f>
         <v/>
       </c>
-      <c r="E27" s="6">
-        <f>'Value Bridge'!F66</f>
-        <v/>
-      </c>
-      <c r="F27" s="6">
+      <c r="G27" s="6">
         <f>'Value Bridge'!P66</f>
         <v/>
       </c>
-      <c r="G27" s="6">
+      <c r="H27" s="6">
         <f>'Value Bridge'!Q66</f>
         <v/>
       </c>
@@ -1481,22 +1452,26 @@
         <v/>
       </c>
       <c r="C28" s="6">
+        <f>'Value Bridge'!F67+'Value Bridge'!J67</f>
+        <v/>
+      </c>
+      <c r="D28" s="6">
+        <f>'Value Bridge'!G67+'Value Bridge'!K67</f>
+        <v/>
+      </c>
+      <c r="E28" s="6">
         <f>'Value Bridge'!L67</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="F28" s="14">
         <f>'Value Bridge'!N67</f>
         <v/>
       </c>
-      <c r="E28" s="6">
-        <f>'Value Bridge'!F67</f>
-        <v/>
-      </c>
-      <c r="F28" s="6">
+      <c r="G28" s="6">
         <f>'Value Bridge'!P67</f>
         <v/>
       </c>
-      <c r="G28" s="6">
+      <c r="H28" s="6">
         <f>'Value Bridge'!Q67</f>
         <v/>
       </c>
@@ -1512,22 +1487,26 @@
         <v/>
       </c>
       <c r="C29" s="6">
+        <f>'Value Bridge'!F68+'Value Bridge'!J68</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f>'Value Bridge'!G68+'Value Bridge'!K68</f>
+        <v/>
+      </c>
+      <c r="E29" s="6">
         <f>'Value Bridge'!L68</f>
         <v/>
       </c>
-      <c r="D29" s="14">
+      <c r="F29" s="14">
         <f>'Value Bridge'!N68</f>
         <v/>
       </c>
-      <c r="E29" s="6">
-        <f>'Value Bridge'!F68</f>
-        <v/>
-      </c>
-      <c r="F29" s="6">
+      <c r="G29" s="6">
         <f>'Value Bridge'!P68</f>
         <v/>
       </c>
-      <c r="G29" s="6">
+      <c r="H29" s="6">
         <f>'Value Bridge'!Q68</f>
         <v/>
       </c>
@@ -1543,22 +1522,26 @@
         <v/>
       </c>
       <c r="C30" s="6">
+        <f>'Value Bridge'!F69+'Value Bridge'!J69</f>
+        <v/>
+      </c>
+      <c r="D30" s="6">
+        <f>'Value Bridge'!G69+'Value Bridge'!K69</f>
+        <v/>
+      </c>
+      <c r="E30" s="6">
         <f>'Value Bridge'!L69</f>
         <v/>
       </c>
-      <c r="D30" s="14">
+      <c r="F30" s="14">
         <f>'Value Bridge'!N69</f>
         <v/>
       </c>
-      <c r="E30" s="6">
-        <f>'Value Bridge'!F69</f>
-        <v/>
-      </c>
-      <c r="F30" s="6">
+      <c r="G30" s="6">
         <f>'Value Bridge'!P69</f>
         <v/>
       </c>
-      <c r="G30" s="6">
+      <c r="H30" s="6">
         <f>'Value Bridge'!Q69</f>
         <v/>
       </c>
@@ -1574,22 +1557,26 @@
         <v/>
       </c>
       <c r="C31" s="18">
+        <f>'Value Bridge'!F70+'Value Bridge'!J70</f>
+        <v/>
+      </c>
+      <c r="D31" s="18">
+        <f>'Value Bridge'!G70+'Value Bridge'!K70</f>
+        <v/>
+      </c>
+      <c r="E31" s="18">
         <f>'Value Bridge'!L70</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="F31" s="19">
         <f>'Value Bridge'!N70</f>
         <v/>
       </c>
-      <c r="E31" s="18">
-        <f>'Value Bridge'!F70</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
+      <c r="G31" s="18">
         <f>'Value Bridge'!P70</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="H31" s="18">
         <f>'Value Bridge'!Q70</f>
         <v/>
       </c>
@@ -1610,7 +1597,7 @@
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Multiples don't multiply. A GPU is bought whole — memory and compute together — so a serving fleet shrinks by whichever need falls LEAST (here the conservative 100× memory cap), not by 100 × 793. Cutting a fleet 100× already removes 99% of it; bigger multiples can only move the last 1%. So the dollars are set by how much these firms spend on chips, not by how large the multiple is. We report dollars.</t>
+          <t>Multiples don't multiply. A GPU is bought whole — memory and compute together — so an inference fleet shrinks by whichever need falls LEAST (here the conservative 100× memory cap), not by 100 × 793. Cutting a fleet 100× already removes 99% of it; bigger multiples can only move the last 1%. So the dollars are set by how much these firms spend on chips, not by how large the multiple is. We report dollars.</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1634,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>step by step from disclosed capex to the saving; training vs serving; where each lever moves the needle</t>
+          <t>step by step from disclosed capex to the saving; training vs inference; where each lever moves the needle</t>
         </is>
       </c>
     </row>
@@ -1695,20 +1682,19 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="B38:G38"/>
-    <mergeCell ref="D18:G18"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="B41:G41"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="B40:G40"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="B39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6193,7 +6179,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Read top to bottom: what the six largest AI spenders spend, how their chip fleet splits between TRAINING models and SERVING users, what Helarctos changes in each, and the dollars that follow. Every cell is a live formula; the levers live on the Levers tab.</t>
+          <t>Read top to bottom: what the six largest AI spenders spend, how their chip fleet splits between TRAINING models and INFERENCE (serving users), what Helarctos changes in each, and the dollars that follow. Every cell is a live formula; the levers live on the Levers tab.</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6253,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>J70</f>
+        <f>I70</f>
         <v/>
       </c>
     </row>
@@ -6345,7 +6331,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Serving fleet — answers users</t>
+          <t>Inference fleet — answers users</t>
         </is>
       </c>
       <c r="B14" s="6">
@@ -6360,7 +6346,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>STEP 3 — TRAINING: fewer GPU-hours per model → smaller training clusters → capex avoided</t>
+          <t>STEP 3 — TRAINING: fewer GPU-hours per model → smaller training clusters</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
@@ -6422,7 +6408,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>…and each token trains faster on long documents</t>
+          <t>…at about the same speed per token</t>
         </is>
       </c>
       <c r="C20" s="21">
@@ -6431,7 +6417,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>flat cost per token vs. rising (lever 3)</t>
+          <t>comparable at the same size — no speed credit taken (lever 3)</t>
         </is>
       </c>
     </row>
@@ -6463,157 +6449,153 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>TRAINING CAPEX AVOIDED</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Training capex avoided</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
         <f>B17-B22</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="3">
-        <f>"How training savings become capex savings: labs size their training clusters to the GPU-hours their training runs need. If every model of a given quality needs ~"&amp;TEXT(TrainLever,"0")&amp;"× fewer GPU-hours, the same training programme runs on a cluster ~"&amp;TEXT(TrainLever,"0")&amp;"× smaller — the GPUs that never have to be bought are capex avoided (and the power they would have drawn is opex avoided, Step 5)."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>STEP 4 — SERVING: less memory and more conversations per GPU → fewer serving GPUs</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Power &amp; operations those GPUs would have drawn</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>J70</f>
+        <v/>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>power scales with the fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>TRAINING SAVING (capex + power)</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>B23+B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="3">
+        <f>"How training savings become capex savings: labs size their training clusters to the GPU-hours their training runs need. If every model of a given quality needs ~"&amp;TEXT(TrainLever,"0")&amp;"× fewer GPU-hours, the same training programme runs on a cluster ~"&amp;TEXT(TrainLever,"0")&amp;"× smaller — the GPUs that never have to be bought are capex avoided, and the power they would have drawn is saved every year."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>STEP 4 — INFERENCE: less memory and more conversations per GPU → fewer inference GPUs</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Serving fleet capex today</t>
-        </is>
-      </c>
-      <c r="B27" s="6">
-        <f>B14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Memory needed per conversation falls by</t>
-        </is>
-      </c>
-      <c r="C28" s="23">
-        <f>MemoryLever</f>
-        <v/>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>fixed-size state (lever 4)</t>
-        </is>
-      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>Inference fleet capex today</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Memory needed per conversation falls by</t>
+        </is>
+      </c>
+      <c r="C30" s="23">
+        <f>MemoryLever</f>
+        <v/>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>fixed-size state (lever 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>Compute needed per token falls by</t>
         </is>
       </c>
-      <c r="C29" s="21">
+      <c r="C31" s="21">
         <f>ServeComputeLever</f>
         <v/>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>smaller model × more conversations per GPU (levers 1 × 5)</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>GPUs needed fall by — whichever limit binds</t>
-        </is>
-      </c>
-      <c r="C30" s="22">
-        <f>ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>the smaller of the two: a GPU is bought whole</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Serving fleet needed with Helarctos</t>
-        </is>
-      </c>
-      <c r="B31" s="6">
-        <f>B27/C30</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SERVING CAPEX AVOIDED</t>
-        </is>
-      </c>
-      <c r="B32" s="15">
-        <f>B27-B31</f>
+          <t>GPUs needed fall by — whichever limit binds</t>
+        </is>
+      </c>
+      <c r="C32" s="22">
+        <f>ServeGPULever</f>
         <v/>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>A GPU brings memory and compute together; the fleet must cover whichever runs out first. Transformers at long context run out of MEMORY (the growing KV cache), so memory is the limit we relieve first; compute then binds only if it falls less than memory.</t>
+          <t>the smaller of the two: a GPU is bought whole</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>STEP 5 — Power &amp; operations shrink with the fleet</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Inference fleet needed with Helarctos</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>B29/C32</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Power &amp; operations for the chip fleet today</t>
+          <t>Inference capex avoided</t>
         </is>
       </c>
       <c r="B34" s="6">
-        <f>B8</f>
+        <f>B29-B33</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Power &amp; operations saved per year</t>
+          <t>Power &amp; operations those GPUs would have drawn</t>
         </is>
       </c>
       <c r="B35" s="6">
@@ -6622,55 +6604,60 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Same share as the chip fleet cut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+          <t>power scales with the fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>INFERENCE SAVING (capex + power)</t>
+        </is>
+      </c>
+      <c r="B36" s="15">
+        <f>B34+B35</f>
+        <v/>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>A GPU brings memory and compute together; the fleet must cover whichever runs out first. Transformers at long context run out of MEMORY (the growing KV cache) first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>RESULT — FY2026</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Training capex avoided</t>
-        </is>
-      </c>
-      <c r="B38" s="6">
-        <f>B23</f>
-        <v/>
-      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Serving capex avoided</t>
+          <t>Training (capex + power)</t>
         </is>
       </c>
       <c r="B39" s="6">
-        <f>B32</f>
+        <f>B25</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Power &amp; operations saved</t>
+          <t>Inference (capex + power)</t>
         </is>
       </c>
       <c r="B40" s="6">
-        <f>B35</f>
+        <f>B36</f>
         <v/>
       </c>
     </row>
@@ -6681,7 +6668,7 @@
         </is>
       </c>
       <c r="B41" s="15">
-        <f>B38+B39+B40</f>
+        <f>B39+B40</f>
         <v/>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -6708,7 +6695,7 @@
         </is>
       </c>
       <c r="B43" s="14">
-        <f>(B23+B32)/B7</f>
+        <f>(B23+B34)/B7</f>
         <v/>
       </c>
     </row>
@@ -6767,17 +6754,17 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>Serving memory falls by</t>
+          <t>Inference memory falls by</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Serving compute falls by</t>
+          <t>Inference compute falls by</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>Chip fleet cut (serving GPUs fall by the smaller)</t>
+          <t>Chip fleet cut (inference GPUs fall by the smaller)</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -6811,7 +6798,7 @@
         <v/>
       </c>
       <c r="F49" s="18">
-        <f>E49*(B70+J70)</f>
+        <f>E49*(B70+I70)</f>
         <v/>
       </c>
       <c r="G49" s="26">
@@ -6841,7 +6828,7 @@
         <v/>
       </c>
       <c r="F50" s="18">
-        <f>E50*(B70+J70)</f>
+        <f>E50*(B70+I70)</f>
         <v/>
       </c>
       <c r="G50" s="26">
@@ -6872,7 +6859,7 @@
         <v/>
       </c>
       <c r="F51" s="18">
-        <f>E51*(B70+J70)</f>
+        <f>E51*(B70+I70)</f>
         <v/>
       </c>
       <c r="G51" s="26">
@@ -6881,13 +6868,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>+ Many more conversations per GPU (lever 5)</t>
         </is>
       </c>
       <c r="B52" s="21">
-        <f>SmallerModel^2</f>
+        <f>TrainLever</f>
         <v/>
       </c>
       <c r="C52" s="23">
@@ -6903,7 +6890,7 @@
         <v/>
       </c>
       <c r="F52" s="18">
-        <f>E52*(B70+J70)</f>
+        <f>E52*(B70+I70)</f>
         <v/>
       </c>
       <c r="G52" s="26">
@@ -6911,41 +6898,10 @@
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>+ Faster training on long documents (lever 3)</t>
-        </is>
-      </c>
-      <c r="B53" s="21">
-        <f>TrainLever</f>
-        <v/>
-      </c>
-      <c r="C53" s="23">
-        <f>MemoryLever</f>
-        <v/>
-      </c>
-      <c r="D53" s="21">
-        <f>ServeComputeLever</f>
-        <v/>
-      </c>
-      <c r="E53" s="25">
-        <f>(D70*(1-1/B53)+E70*(1-1/MIN(C53,D53)))/B70</f>
-        <v/>
-      </c>
-      <c r="F53" s="18">
-        <f>E53*(B70+J70)</f>
-        <v/>
-      </c>
-      <c r="G53" s="26">
-        <f>F53-F52</f>
-        <v/>
-      </c>
-    </row>
     <row r="55" ht="62" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Read this as: the smaller model alone removes nearly all of the TRAINING bill (fewer parameters AND fewer tokens compound) but no serving GPUs — at long context a transformer's serving GPUs are full of memory (the growing KV cache), not busy computing, and a smaller model doesn't change that. Fixed-size memory unlocks serving, until compute becomes the limit; many more conversations per GPU lifts that limit. The last levers have big multiples but add little, because by then over 95% of the cost is already gone: a cost can only fall to zero once. That is why this workbook reports dollars, not multiples. The order is the storyline; the end point does not depend on it.</t>
+          <t>Read this as: the smaller model alone removes nearly all of the TRAINING bill (fewer parameters AND fewer tokens compound) but no inference GPUs — at long context a transformer's inference GPUs are full of memory (the growing KV cache), not busy computing, and a smaller model doesn't change that. Fixed-size memory unlocks inference, until compute becomes the limit; many more conversations per GPU lifts that limit. By then ~99% of the chip bill is gone: bigger multiples can't add much, because a cost can only fall to zero once. That is why this workbook reports dollars, not multiples. The order is the storyline; the end point does not depend on it.</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6934,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>This bridge (training on GPU-hours, serving on whole GPUs)</t>
+          <t>This bridge (training on GPU-hours, inference on whole GPUs)</t>
         </is>
       </c>
       <c r="B59" s="6">
@@ -7048,7 +7004,7 @@
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>Serving fleet</t>
+          <t>Inference fleet</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
@@ -7058,27 +7014,27 @@
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>Serving capex avoided</t>
+          <t>Inference capex avoided</t>
         </is>
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>Serving fleet needed</t>
+          <t>Chip capex avoided</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
-          <t>Chip capex avoided</t>
+          <t>Power &amp; ops today</t>
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>Power &amp; ops today</t>
+          <t>Training power saved</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t>Power &amp; ops saved</t>
+          <t>Inference power saved</t>
         </is>
       </c>
       <c r="L63" s="16" t="inlineStr">
@@ -7142,28 +7098,28 @@
         <f>E64*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H64" s="28">
-        <f>E64/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I64" s="6">
+      <c r="H64" s="6">
         <f>F64+G64</f>
         <v/>
       </c>
+      <c r="I64" s="28">
+        <f>'Microsoft'!$C$34</f>
+        <v/>
+      </c>
       <c r="J64" s="28">
-        <f>'Microsoft'!$C$34</f>
+        <f>IF(B64&gt;0,I64*F64/B64,0)</f>
         <v/>
       </c>
       <c r="K64" s="28">
-        <f>IF(B64&gt;0,J64*I64/B64,0)</f>
+        <f>IF(B64&gt;0,I64*G64/B64,0)</f>
         <v/>
       </c>
       <c r="L64" s="18">
-        <f>I64+K64</f>
+        <f>H64+J64+K64</f>
         <v/>
       </c>
       <c r="M64" s="6">
-        <f>'Microsoft'!$C$10+J64</f>
+        <f>'Microsoft'!$C$10+I64</f>
         <v/>
       </c>
       <c r="N64" s="14">
@@ -7213,28 +7169,28 @@
         <f>E65*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H65" s="28">
-        <f>E65/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I65" s="6">
+      <c r="H65" s="6">
         <f>F65+G65</f>
         <v/>
       </c>
+      <c r="I65" s="28">
+        <f>'Alphabet'!$C$34</f>
+        <v/>
+      </c>
       <c r="J65" s="28">
-        <f>'Alphabet'!$C$34</f>
+        <f>IF(B65&gt;0,I65*F65/B65,0)</f>
         <v/>
       </c>
       <c r="K65" s="28">
-        <f>IF(B65&gt;0,J65*I65/B65,0)</f>
+        <f>IF(B65&gt;0,I65*G65/B65,0)</f>
         <v/>
       </c>
       <c r="L65" s="18">
-        <f>I65+K65</f>
+        <f>H65+J65+K65</f>
         <v/>
       </c>
       <c r="M65" s="6">
-        <f>'Alphabet'!$C$10+J65</f>
+        <f>'Alphabet'!$C$10+I65</f>
         <v/>
       </c>
       <c r="N65" s="14">
@@ -7284,28 +7240,28 @@
         <f>E66*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H66" s="28">
-        <f>E66/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I66" s="6">
+      <c r="H66" s="6">
         <f>F66+G66</f>
         <v/>
       </c>
+      <c r="I66" s="28">
+        <f>'Amazon'!$C$34</f>
+        <v/>
+      </c>
       <c r="J66" s="28">
-        <f>'Amazon'!$C$34</f>
+        <f>IF(B66&gt;0,I66*F66/B66,0)</f>
         <v/>
       </c>
       <c r="K66" s="28">
-        <f>IF(B66&gt;0,J66*I66/B66,0)</f>
+        <f>IF(B66&gt;0,I66*G66/B66,0)</f>
         <v/>
       </c>
       <c r="L66" s="18">
-        <f>I66+K66</f>
+        <f>H66+J66+K66</f>
         <v/>
       </c>
       <c r="M66" s="6">
-        <f>'Amazon'!$C$10+J66</f>
+        <f>'Amazon'!$C$10+I66</f>
         <v/>
       </c>
       <c r="N66" s="14">
@@ -7355,28 +7311,28 @@
         <f>E67*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H67" s="28">
-        <f>E67/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I67" s="6">
+      <c r="H67" s="6">
         <f>F67+G67</f>
         <v/>
       </c>
+      <c r="I67" s="28">
+        <f>'Meta'!$C$34</f>
+        <v/>
+      </c>
       <c r="J67" s="28">
-        <f>'Meta'!$C$34</f>
+        <f>IF(B67&gt;0,I67*F67/B67,0)</f>
         <v/>
       </c>
       <c r="K67" s="28">
-        <f>IF(B67&gt;0,J67*I67/B67,0)</f>
+        <f>IF(B67&gt;0,I67*G67/B67,0)</f>
         <v/>
       </c>
       <c r="L67" s="18">
-        <f>I67+K67</f>
+        <f>H67+J67+K67</f>
         <v/>
       </c>
       <c r="M67" s="6">
-        <f>'Meta'!$C$10+J67</f>
+        <f>'Meta'!$C$10+I67</f>
         <v/>
       </c>
       <c r="N67" s="14">
@@ -7426,28 +7382,28 @@
         <f>E68*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H68" s="28">
-        <f>E68/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I68" s="6">
+      <c r="H68" s="6">
         <f>F68+G68</f>
         <v/>
       </c>
+      <c r="I68" s="28">
+        <f>'Oracle'!$C$34</f>
+        <v/>
+      </c>
       <c r="J68" s="28">
-        <f>'Oracle'!$C$34</f>
+        <f>IF(B68&gt;0,I68*F68/B68,0)</f>
         <v/>
       </c>
       <c r="K68" s="28">
-        <f>IF(B68&gt;0,J68*I68/B68,0)</f>
+        <f>IF(B68&gt;0,I68*G68/B68,0)</f>
         <v/>
       </c>
       <c r="L68" s="18">
-        <f>I68+K68</f>
+        <f>H68+J68+K68</f>
         <v/>
       </c>
       <c r="M68" s="6">
-        <f>'Oracle'!$C$10+J68</f>
+        <f>'Oracle'!$C$10+I68</f>
         <v/>
       </c>
       <c r="N68" s="14">
@@ -7497,28 +7453,28 @@
         <f>E69*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H69" s="28">
-        <f>E69/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I69" s="6">
+      <c r="H69" s="6">
         <f>F69+G69</f>
         <v/>
       </c>
+      <c r="I69" s="28">
+        <f>'SpaceX'!$C$34</f>
+        <v/>
+      </c>
       <c r="J69" s="28">
-        <f>'SpaceX'!$C$34</f>
+        <f>IF(B69&gt;0,I69*F69/B69,0)</f>
         <v/>
       </c>
       <c r="K69" s="28">
-        <f>IF(B69&gt;0,J69*I69/B69,0)</f>
+        <f>IF(B69&gt;0,I69*G69/B69,0)</f>
         <v/>
       </c>
       <c r="L69" s="18">
-        <f>I69+K69</f>
+        <f>H69+J69+K69</f>
         <v/>
       </c>
       <c r="M69" s="6">
-        <f>'SpaceX'!$C$10+J69</f>
+        <f>'SpaceX'!$C$10+I69</f>
         <v/>
       </c>
       <c r="N69" s="14">
@@ -7568,11 +7524,11 @@
         <f>SUM(G64:G69)</f>
         <v/>
       </c>
-      <c r="H70" s="29">
+      <c r="H70" s="18">
         <f>SUM(H64:H69)</f>
         <v/>
       </c>
-      <c r="I70" s="18">
+      <c r="I70" s="29">
         <f>SUM(I64:I69)</f>
         <v/>
       </c>
@@ -7655,7 +7611,7 @@
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>Serving fleet</t>
+          <t>Inference fleet</t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
@@ -7665,27 +7621,27 @@
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>Serving capex avoided</t>
+          <t>Inference capex avoided</t>
         </is>
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>Serving fleet needed</t>
+          <t>Chip capex avoided</t>
         </is>
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
-          <t>Chip capex avoided</t>
+          <t>Power &amp; ops today</t>
         </is>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>Power &amp; ops today</t>
+          <t>Training power saved</t>
         </is>
       </c>
       <c r="K74" s="16" t="inlineStr">
         <is>
-          <t>Power &amp; ops saved</t>
+          <t>Inference power saved</t>
         </is>
       </c>
       <c r="L74" s="16" t="inlineStr">
@@ -7749,28 +7705,28 @@
         <f>E75*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H75" s="28">
-        <f>E75/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I75" s="6">
+      <c r="H75" s="6">
         <f>F75+G75</f>
         <v/>
       </c>
+      <c r="I75" s="28">
+        <f>'Microsoft'!$B$34</f>
+        <v/>
+      </c>
       <c r="J75" s="28">
-        <f>'Microsoft'!$B$34</f>
+        <f>IF(B75&gt;0,I75*F75/B75,0)</f>
         <v/>
       </c>
       <c r="K75" s="28">
-        <f>IF(B75&gt;0,J75*I75/B75,0)</f>
+        <f>IF(B75&gt;0,I75*G75/B75,0)</f>
         <v/>
       </c>
       <c r="L75" s="18">
-        <f>I75+K75</f>
+        <f>H75+J75+K75</f>
         <v/>
       </c>
       <c r="M75" s="6">
-        <f>'Microsoft'!$B$10+J75</f>
+        <f>'Microsoft'!$B$10+I75</f>
         <v/>
       </c>
       <c r="N75" s="14">
@@ -7820,28 +7776,28 @@
         <f>E76*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H76" s="28">
-        <f>E76/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I76" s="6">
+      <c r="H76" s="6">
         <f>F76+G76</f>
         <v/>
       </c>
+      <c r="I76" s="28">
+        <f>'Alphabet'!$B$34</f>
+        <v/>
+      </c>
       <c r="J76" s="28">
-        <f>'Alphabet'!$B$34</f>
+        <f>IF(B76&gt;0,I76*F76/B76,0)</f>
         <v/>
       </c>
       <c r="K76" s="28">
-        <f>IF(B76&gt;0,J76*I76/B76,0)</f>
+        <f>IF(B76&gt;0,I76*G76/B76,0)</f>
         <v/>
       </c>
       <c r="L76" s="18">
-        <f>I76+K76</f>
+        <f>H76+J76+K76</f>
         <v/>
       </c>
       <c r="M76" s="6">
-        <f>'Alphabet'!$B$10+J76</f>
+        <f>'Alphabet'!$B$10+I76</f>
         <v/>
       </c>
       <c r="N76" s="14">
@@ -7891,28 +7847,28 @@
         <f>E77*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H77" s="28">
-        <f>E77/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I77" s="6">
+      <c r="H77" s="6">
         <f>F77+G77</f>
         <v/>
       </c>
+      <c r="I77" s="28">
+        <f>'Amazon'!$B$34</f>
+        <v/>
+      </c>
       <c r="J77" s="28">
-        <f>'Amazon'!$B$34</f>
+        <f>IF(B77&gt;0,I77*F77/B77,0)</f>
         <v/>
       </c>
       <c r="K77" s="28">
-        <f>IF(B77&gt;0,J77*I77/B77,0)</f>
+        <f>IF(B77&gt;0,I77*G77/B77,0)</f>
         <v/>
       </c>
       <c r="L77" s="18">
-        <f>I77+K77</f>
+        <f>H77+J77+K77</f>
         <v/>
       </c>
       <c r="M77" s="6">
-        <f>'Amazon'!$B$10+J77</f>
+        <f>'Amazon'!$B$10+I77</f>
         <v/>
       </c>
       <c r="N77" s="14">
@@ -7962,28 +7918,28 @@
         <f>E78*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H78" s="28">
-        <f>E78/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I78" s="6">
+      <c r="H78" s="6">
         <f>F78+G78</f>
         <v/>
       </c>
+      <c r="I78" s="28">
+        <f>'Meta'!$B$34</f>
+        <v/>
+      </c>
       <c r="J78" s="28">
-        <f>'Meta'!$B$34</f>
+        <f>IF(B78&gt;0,I78*F78/B78,0)</f>
         <v/>
       </c>
       <c r="K78" s="28">
-        <f>IF(B78&gt;0,J78*I78/B78,0)</f>
+        <f>IF(B78&gt;0,I78*G78/B78,0)</f>
         <v/>
       </c>
       <c r="L78" s="18">
-        <f>I78+K78</f>
+        <f>H78+J78+K78</f>
         <v/>
       </c>
       <c r="M78" s="6">
-        <f>'Meta'!$B$10+J78</f>
+        <f>'Meta'!$B$10+I78</f>
         <v/>
       </c>
       <c r="N78" s="14">
@@ -8033,28 +7989,28 @@
         <f>E79*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H79" s="28">
-        <f>E79/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I79" s="6">
+      <c r="H79" s="6">
         <f>F79+G79</f>
         <v/>
       </c>
+      <c r="I79" s="28">
+        <f>'Oracle'!$B$34</f>
+        <v/>
+      </c>
       <c r="J79" s="28">
-        <f>'Oracle'!$B$34</f>
+        <f>IF(B79&gt;0,I79*F79/B79,0)</f>
         <v/>
       </c>
       <c r="K79" s="28">
-        <f>IF(B79&gt;0,J79*I79/B79,0)</f>
+        <f>IF(B79&gt;0,I79*G79/B79,0)</f>
         <v/>
       </c>
       <c r="L79" s="18">
-        <f>I79+K79</f>
+        <f>H79+J79+K79</f>
         <v/>
       </c>
       <c r="M79" s="6">
-        <f>'Oracle'!$B$10+J79</f>
+        <f>'Oracle'!$B$10+I79</f>
         <v/>
       </c>
       <c r="N79" s="14">
@@ -8104,28 +8060,28 @@
         <f>E80*(1-1/ServeGPULever)</f>
         <v/>
       </c>
-      <c r="H80" s="28">
-        <f>E80/ServeGPULever</f>
-        <v/>
-      </c>
-      <c r="I80" s="6">
+      <c r="H80" s="6">
         <f>F80+G80</f>
         <v/>
       </c>
+      <c r="I80" s="28">
+        <f>'SpaceX'!$B$34</f>
+        <v/>
+      </c>
       <c r="J80" s="28">
-        <f>'SpaceX'!$B$34</f>
+        <f>IF(B80&gt;0,I80*F80/B80,0)</f>
         <v/>
       </c>
       <c r="K80" s="28">
-        <f>IF(B80&gt;0,J80*I80/B80,0)</f>
+        <f>IF(B80&gt;0,I80*G80/B80,0)</f>
         <v/>
       </c>
       <c r="L80" s="18">
-        <f>I80+K80</f>
+        <f>H80+J80+K80</f>
         <v/>
       </c>
       <c r="M80" s="6">
-        <f>'SpaceX'!$B$10+J80</f>
+        <f>'SpaceX'!$B$10+I80</f>
         <v/>
       </c>
       <c r="N80" s="14">
@@ -8175,11 +8131,11 @@
         <f>SUM(G75:G80)</f>
         <v/>
       </c>
-      <c r="H81" s="29">
+      <c r="H81" s="18">
         <f>SUM(H75:H80)</f>
         <v/>
       </c>
-      <c r="I81" s="18">
+      <c r="I81" s="29">
         <f>SUM(I75:I80)</f>
         <v/>
       </c>
@@ -8217,26 +8173,27 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="D13:I13"/>
     <mergeCell ref="D32:I32"/>
     <mergeCell ref="D41:I41"/>
     <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="D28:I28"/>
     <mergeCell ref="D18:I18"/>
     <mergeCell ref="D9:I9"/>
     <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D24:I24"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="D35:I35"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="D60:I60"/>
-    <mergeCell ref="A24:I24"/>
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D31:I31"/>
     <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D36:I36"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="D21:I21"/>
   </mergeCells>
@@ -8380,7 +8337,7 @@
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>Training AND serving compute</t>
+          <t>Training and inference compute</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8388,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Faster training per token on long documents</t>
+          <t>Training speed per token (same model size)</t>
         </is>
       </c>
       <c r="C9" s="22">
@@ -8439,19 +8396,19 @@
         <v/>
       </c>
       <c r="D9" s="31" t="n">
-        <v>2.220667013967386</v>
+        <v>1</v>
       </c>
       <c r="E9" s="31" t="n">
-        <v>3.967000451897755</v>
+        <v>1</v>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Today: MEASURED cost per token at each document length; the training mix is illustrative. Optimized: TARGET</t>
+          <t>ASSUMPTION — roughly comparable to a transformer; no speed credit taken</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>A transformer's cost per token rises with document length (each token looks back over all the earlier ones); Helarctos' stays flat. Over a modern training mix (70% at 8k / 20% at 64k / 10% at 256k tokens) that is 2.2× cheaper per token. On short documents alone the transformer is still faster today (0.58× at 2k tokens).</t>
+          <t>At the same model size, Helarctos trains at roughly the same speed per token as a transformer, so we count no training speed-up. The training saving comes entirely from levers 1 and 2: a smaller model trained on fewer tokens. (Where Helarctos is much faster is inference — lever 5.)</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -8495,7 +8452,7 @@
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>Serving GPUs (the memory limit)</t>
+          <t>Inference GPUs (the memory limit)</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8491,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>Serving GPUs (the compute limit)</t>
+          <t>Inference GPUs (the compute limit)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8528,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Serving: memory needed per conversation falls by</t>
+          <t>Inference: memory needed per conversation falls by</t>
         </is>
       </c>
       <c r="C15" s="32">
@@ -8587,7 +8544,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Serving: compute needed per token falls by</t>
+          <t>Inference: compute needed per token falls by</t>
         </is>
       </c>
       <c r="C16" s="22">
@@ -8603,7 +8560,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Serving: GPUs needed fall by</t>
+          <t>Inference: GPUs needed fall by</t>
         </is>
       </c>
       <c r="C17" s="22">
@@ -8612,14 +8569,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>A GPU is bought whole — memory and compute come together. The serving fleet has to cover whichever runs out first, so it shrinks by the SMALLER of the two levers (here the conservative ÷100 memory cap). Multiplying them (100 × 793 = 79,000×) would be wrong.</t>
+          <t>A GPU is bought whole — memory and compute come together. The inference fleet has to cover whichever runs out first, so it shrinks by the SMALLER of the two levers (here the conservative ÷100 memory cap). Multiplying them (100 × 793 = 79,000×) would be wrong.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>For reference: technical tabs' blended serving cut</t>
+          <t>For reference: technical tabs' blended inference cut</t>
         </is>
       </c>
       <c r="C18" s="22">
@@ -8649,7 +8606,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Analysts put training at 30–45% of AI compute in 2026 (Gartner, Deloitte; the rest is serving users). Per-company estimates below follow what each firm is known to be building.</t>
+          <t>Analysts put training at 30–45% of AI compute in 2026 (Gartner, Deloitte; the rest is inference, i.e. serving users). Per-company estimates below follow what each firm is known to be building.</t>
         </is>
       </c>
     </row>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -10,19 +10,20 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Value Bridge" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Levers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Microsoft" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Alphabet" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Amazon" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Meta" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Oracle" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SpaceX" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Totals" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Inputs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="CostLadder" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ServingTraining" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Evidence" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Methodology" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="What Matters" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Microsoft" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Alphabet" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Amazon" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Meta" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Oracle" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SpaceX" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Totals" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Inputs" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Sensitivity" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="CostLadder" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ServingTraining" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Evidence" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Methodology" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="Scenario">Levers!$C$4</definedName>
@@ -41,7 +42,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
@@ -56,12 +57,13 @@
     <numFmt numFmtId="175" formatCode="+$#,##0.00;-$#,##0.00"/>
     <numFmt numFmtId="176" formatCode="0.0&quot;×&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;÷&quot;#,##0"/>
-    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0&quot;B&quot;;-&quot;$&quot;#,##0&quot;B&quot;"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.0&quot;B&quot;"/>
-    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.0&quot;T&quot;;-&quot;$&quot;#,##0.0&quot;T&quot;"/>
-    <numFmt numFmtId="181" formatCode="+&quot;$&quot;#,##0&quot;B&quot;;-&quot;$&quot;#,##0&quot;B&quot;;&quot;—&quot;"/>
+    <numFmt numFmtId="178" formatCode="+&quot;$&quot;#,##0.0&quot;B&quot;;-&quot;$&quot;#,##0.0&quot;B&quot;;&quot;$0&quot;"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0&quot;B&quot;;-&quot;$&quot;#,##0&quot;B&quot;"/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.0&quot;B&quot;"/>
+    <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0.0&quot;T&quot;;-&quot;$&quot;#,##0.0&quot;T&quot;"/>
+    <numFmt numFmtId="182" formatCode="+&quot;$&quot;#,##0&quot;B&quot;;-&quot;$&quot;#,##0&quot;B&quot;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,11 +88,15 @@
       <sz val="16"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -109,12 +115,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -153,6 +164,20 @@
       </top>
       <bottom style="thin">
         <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00C55A11"/>
+      </left>
+      <right style="medium">
+        <color rgb="00C55A11"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C55A11"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C55A11"/>
       </bottom>
     </border>
     <border>
@@ -203,106 +228,121 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="178" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="180" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="6" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="178" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="181" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="182" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="179" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="180" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1018,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1052,7 +1092,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>"Scenario: "&amp;Scenario&amp;"   (change it on the Levers tab)"</f>
+        <f>"Scenario: "&amp;Scenario&amp;" (◆ change it on the Levers tab) · 262k-token average conversation · ★ orange border = high-impact input (What Matters tab)"</f>
         <v/>
       </c>
     </row>
@@ -1646,45 +1686,59 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>the five Helarctos levers in plain English, how sure we are of each, the scenario switch, training shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>the five Helarctos levers in plain English, how sure we are of each, the scenario picker (◆ purple cells differ by scenario), training shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
+          <t>What Matters</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>which inputs move the answer and by how much; ★ marks the high-impact cells everywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
           <t>Microsoft / Alphabet / Amazon / Meta / Oracle / SpaceX</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>each company's capex build from its filings (green = disclosed)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Technical appendix</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Totals, Inputs, Sensitivity, CostLadder, ServingTraining, Evidence, Methodology — the full engineering ledger behind the levers</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Colours: yellow = assumption you can edit · green = disclosed filing / market data · blue = formula. Cash basis; FY2026 is company guidance; not investment advice.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A34:G34"/>
@@ -1693,7 +1747,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="B40:G40"/>
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="B39:G39"/>
   </mergeCells>
@@ -1703,6 +1756,694 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>SpaceX — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
+        </is>
+      </c>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>basis / source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total capex ($B)</t>
+        </is>
+      </c>
+      <c r="B3" s="44" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C3" s="45" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FY25 S-1 AI capex $12.7B [DISCLOSED]; FY26 ~$55B EST from H1'26 DISCLOSED $23.5B (Q1 $7.7B, Q2 $15.8B; 82.7% of total capex) + company guiding capex roughly flat Q3/Q4. ~all accelerator (greenfield COLOSSUS I/II). AI rev ~0 today; Anthropic (up to $1.25B/mo) and Google (up to $920M/mo) compute deals ramp from 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>★ Infra / data-center share</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>FILING: capex is the AI segment's own figure (S-1; Q2 2026 10-Q segment note, $23.6B in H1 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>★ Server / short-lived share</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>CFO-disclosed (MSFT rose 50%-&gt;67%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>★ Accelerator share within servers</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>from BOM teardowns (~67-80%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Market cap ($B, approx)</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>approximate June 2026 market data -- edit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>DERIVATION</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI-infra capex ($B)</t>
+        </is>
+      </c>
+      <c r="B10" s="48">
+        <f>B3*B4</f>
+        <v/>
+      </c>
+      <c r="C10" s="48">
+        <f>C3*C4</f>
+        <v/>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>total x infra share</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Server bucket ($B)</t>
+        </is>
+      </c>
+      <c r="B11" s="48">
+        <f>B10*B5</f>
+        <v/>
+      </c>
+      <c r="C11" s="48">
+        <f>C10*C5</f>
+        <v/>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>infra x server share</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ACCELERATOR capex ($B)</t>
+        </is>
+      </c>
+      <c r="B12" s="49">
+        <f>B11*B6</f>
+        <v/>
+      </c>
+      <c r="C12" s="49">
+        <f>C11*C6</f>
+        <v/>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>server x accel share</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Accel % of total capex</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>B12/B3</f>
+        <v/>
+      </c>
+      <c r="C13" s="14">
+        <f>C12/C3</f>
+        <v/>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>varies across companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet size (GPU-equiv)</t>
+        </is>
+      </c>
+      <c r="B16" s="50">
+        <f>B12*1000000000/Inputs!$B$7</f>
+        <v/>
+      </c>
+      <c r="C16" s="50">
+        <f>C12*1000000000/Inputs!$B$7</f>
+        <v/>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>accel capex / $ per GPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total wall power (MW)</t>
+        </is>
+      </c>
+      <c r="B17" s="50">
+        <f>B16*Inputs!$B$8/1000</f>
+        <v/>
+      </c>
+      <c r="C17" s="50">
+        <f>C16*Inputs!$B$8/1000</f>
+        <v/>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>GPUs x kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Daily energy (MWh)</t>
+        </is>
+      </c>
+      <c r="B18" s="50">
+        <f>B17*24</f>
+        <v/>
+      </c>
+      <c r="C18" s="50">
+        <f>C17*24</f>
+        <v/>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Daily all-in opex ($/day)</t>
+        </is>
+      </c>
+      <c r="B19" s="50">
+        <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
+        <v/>
+      </c>
+      <c r="C19" s="50">
+        <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>MWh x rate x (1+overhead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Annual opex ($M)</t>
+        </is>
+      </c>
+      <c r="B20" s="48">
+        <f>B19*365/1000000</f>
+        <v/>
+      </c>
+      <c r="C20" s="48">
+        <f>C19*365/1000000</f>
+        <v/>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lifetime opex ($B)</t>
+        </is>
+      </c>
+      <c r="B21" s="51">
+        <f>B20*Inputs!$B$11/1000</f>
+        <v/>
+      </c>
+      <c r="C21" s="51">
+        <f>C20*Inputs!$B$11/1000</f>
+        <v/>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>EFFICIENT VERSION &amp; VALUE</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Efficient AI capex ($B)</t>
+        </is>
+      </c>
+      <c r="B24" s="48">
+        <f>B10-B25</f>
+        <v/>
+      </c>
+      <c r="C24" s="48">
+        <f>C10-C25</f>
+        <v/>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>AI capex - avoided</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Capex avoided/yr ($B)</t>
+        </is>
+      </c>
+      <c r="B25" s="48">
+        <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
+        <v/>
+      </c>
+      <c r="C25" s="48">
+        <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
+        <v/>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>accel + (datacenter x dc-scale), all x (1-1/reduction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Annual opex savings ($M)</t>
+        </is>
+      </c>
+      <c r="B26" s="48">
+        <f>B20*(1-1/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="C26" s="48">
+        <f>C20*(1-1/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sustained annual benefit ($B/yr)</t>
+        </is>
+      </c>
+      <c r="B27" s="52">
+        <f>B25+B26/1000</f>
+        <v/>
+      </c>
+      <c r="C27" s="52">
+        <f>C25+C26/1000</f>
+        <v/>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>avoided + opex savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Capitalized value ($B)</t>
+        </is>
+      </c>
+      <c r="B28" s="53">
+        <f>B27/Inputs!$B$6</f>
+        <v/>
+      </c>
+      <c r="C28" s="53">
+        <f>C27/Inputs!$B$6</f>
+        <v/>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>benefit / discount rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>% of market cap</t>
+        </is>
+      </c>
+      <c r="B29" s="25">
+        <f>B28/$B$7</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>C28/$B$7</f>
+        <v/>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI revenue ($B)</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C32" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATE (see Methodology). MSFT $37B &amp; Amazon $15B run-rates disclosed; Google/Meta/SpaceX estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI capex ($B)</t>
+        </is>
+      </c>
+      <c r="B33" s="48">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="C33" s="48">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>AI-infra capex (full: accel + buildings + power + net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI opex ($B)</t>
+        </is>
+      </c>
+      <c r="B34" s="48">
+        <f>B20/1000</f>
+        <v/>
+      </c>
+      <c r="C34" s="48">
+        <f>C20/1000</f>
+        <v/>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>annual power/operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Net AI NOW ($B)</t>
+        </is>
+      </c>
+      <c r="B35" s="49">
+        <f>B32-B33-B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="49">
+        <f>C32-C33-C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>revenue - capex - opex (cash burn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Spend cut, our arch ($B)</t>
+        </is>
+      </c>
+      <c r="B36" s="48">
+        <f>B27</f>
+        <v/>
+      </c>
+      <c r="C36" s="48">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>accel capex avoided + opex saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Net AI WITH our arch ($B)</t>
+        </is>
+      </c>
+      <c r="B37" s="49">
+        <f>B35+B36</f>
+        <v/>
+      </c>
+      <c r="C37" s="49">
+        <f>C35+C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Net AI now + spend cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>% AI spend reduction</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>B36/(B33+B34)</f>
+        <v/>
+      </c>
+      <c r="C38" s="14">
+        <f>C36/(C33+C34)</f>
+        <v/>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>spend cut / total AI spend (accel-only; upside if DC scales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; REFERENCES</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>S-1 registration statement (SEC EDGAR)</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1181412/000162828026036936/spaceexplorationtechnologi.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>S-1 financials &amp; AI breakdown (Hargreaves Lansdown)</t>
+        </is>
+      </c>
+      <c r="B42" s="54" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/news/inside-spacexs-ipo-filing-revenue-starlink-ai-and-key-financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>$12.7B AI capex = ~60% of capex; COLOSSUS buildout (Investing.com)</t>
+        </is>
+      </c>
+      <c r="B43" s="54" t="inlineStr">
+        <is>
+          <t>https://www.investing.com/analysis/spacex-is-quietly-becoming-an-ai-compute-and-orbital-infrastructure-company-200681776</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>AI1 orbital data centers; Anthropic as compute customer (DCD)</t>
+        </is>
+      </c>
+      <c r="B44" s="54" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/spacex-ipo-musks-firm-set-to-launch-first-orbital-data-center-ai1-satellites-in-2027-will-put-compute-on-starlink-craft/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B43:D43"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -1723,18 +2464,18 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>6-COMPANY AI ECONOMICS — current AI cash burn &amp; the effect of our architecture</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-      <c r="E1" s="35" t="n"/>
-      <c r="F1" s="35" t="n"/>
-      <c r="G1" s="35" t="n"/>
-      <c r="H1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+      <c r="E1" s="43" t="n"/>
+      <c r="F1" s="43" t="n"/>
+      <c r="G1" s="43" t="n"/>
+      <c r="H1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1744,18 +2485,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>NET AI ECONOMICS — FY2025 (cash basis: AI revenue - AI capex - AI opex)</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n"/>
-      <c r="C4" s="35" t="n"/>
-      <c r="D4" s="35" t="n"/>
-      <c r="E4" s="35" t="n"/>
-      <c r="F4" s="35" t="n"/>
-      <c r="G4" s="35" t="n"/>
-      <c r="H4" s="35" t="n"/>
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="43" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -1805,27 +2546,27 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="48">
         <f>Microsoft!$B$32</f>
         <v/>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="48">
         <f>Microsoft!$B$33</f>
         <v/>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="48">
         <f>Microsoft!$B$34</f>
         <v/>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="49">
         <f>Microsoft!$B$35</f>
         <v/>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="48">
         <f>Microsoft!$B$36</f>
         <v/>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="49">
         <f>Microsoft!$B$37</f>
         <v/>
       </c>
@@ -1840,27 +2581,27 @@
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="48">
         <f>Alphabet!$B$32</f>
         <v/>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="48">
         <f>Alphabet!$B$33</f>
         <v/>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="48">
         <f>Alphabet!$B$34</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="49">
         <f>Alphabet!$B$35</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="48">
         <f>Alphabet!$B$36</f>
         <v/>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="49">
         <f>Alphabet!$B$37</f>
         <v/>
       </c>
@@ -1875,27 +2616,27 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="48">
         <f>Amazon!$B$32</f>
         <v/>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="48">
         <f>Amazon!$B$33</f>
         <v/>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="48">
         <f>Amazon!$B$34</f>
         <v/>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="49">
         <f>Amazon!$B$35</f>
         <v/>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="48">
         <f>Amazon!$B$36</f>
         <v/>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="49">
         <f>Amazon!$B$37</f>
         <v/>
       </c>
@@ -1910,27 +2651,27 @@
           <t>Meta</t>
         </is>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="48">
         <f>Meta!$B$32</f>
         <v/>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="48">
         <f>Meta!$B$33</f>
         <v/>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="48">
         <f>Meta!$B$34</f>
         <v/>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="49">
         <f>Meta!$B$35</f>
         <v/>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="48">
         <f>Meta!$B$36</f>
         <v/>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="49">
         <f>Meta!$B$37</f>
         <v/>
       </c>
@@ -1945,27 +2686,27 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="48">
         <f>Oracle!$B$32</f>
         <v/>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="48">
         <f>Oracle!$B$33</f>
         <v/>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="48">
         <f>Oracle!$B$34</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="49">
         <f>Oracle!$B$35</f>
         <v/>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="48">
         <f>Oracle!$B$36</f>
         <v/>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="49">
         <f>Oracle!$B$37</f>
         <v/>
       </c>
@@ -1980,27 +2721,27 @@
           <t>SpaceX</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="48">
         <f>SpaceX!$B$32</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="48">
         <f>SpaceX!$B$33</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="48">
         <f>SpaceX!$B$34</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="49">
         <f>SpaceX!$B$35</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="48">
         <f>SpaceX!$B$36</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="49">
         <f>SpaceX!$B$37</f>
         <v/>
       </c>
@@ -2015,31 +2756,31 @@
           <t>TOTAL (6)</t>
         </is>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="55">
         <f>SUM(B6:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="55">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="55">
         <f>SUM(D6:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="55">
         <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="55">
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="55">
         <f>SUM(G6:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="47">
+      <c r="H12" s="56">
         <f>F12/(C12+D12)</f>
         <v/>
       </c>
@@ -2050,19 +2791,19 @@
           <t>FY2026 (estimate)</t>
         </is>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="57">
         <f>SUM(Microsoft!$C$35,Alphabet!$C$35,Amazon!$C$35,Meta!$C$35,Oracle!$C$35,SpaceX!$C$35)</f>
         <v/>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="57">
         <f>SUM(Microsoft!$C$36,Alphabet!$C$36,Amazon!$C$36,Meta!$C$36,Oracle!$C$36,SpaceX!$C$36)</f>
         <v/>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="57">
         <f>SUM(Microsoft!$C$37,Alphabet!$C$37,Amazon!$C$37,Meta!$C$37,Oracle!$C$37,SpaceX!$C$37)</f>
         <v/>
       </c>
-      <c r="H13" s="49">
+      <c r="H13" s="58">
         <f>SUM(Microsoft!$C$36,Alphabet!$C$36,Amazon!$C$36,Meta!$C$36,Oracle!$C$36,SpaceX!$C$36)/(SUM(Microsoft!$C$33,Alphabet!$C$33,Amazon!$C$33,Meta!$C$33,Oracle!$C$33,SpaceX!$C$33)+SUM(Microsoft!$C$34,Alphabet!$C$34,Amazon!$C$34,Meta!$C$34,Oracle!$C$34,SpaceX!$C$34))</f>
         <v/>
       </c>
@@ -2073,32 +2814,32 @@
           <t>FY2027 (STREET-EST prediction, static)</t>
         </is>
       </c>
-      <c r="E14" s="48" t="n">
-        <v>-960.45442678288</v>
-      </c>
-      <c r="F14" s="48" t="n">
-        <v>569.1669985864507</v>
-      </c>
-      <c r="G14" s="48" t="n">
-        <v>-391.2874281964292</v>
-      </c>
-      <c r="H14" s="49" t="n">
-        <v>0.4889942299198121</v>
+      <c r="E14" s="57" t="n">
+        <v>-965.3195453336799</v>
+      </c>
+      <c r="F14" s="57" t="n">
+        <v>574.1429873323519</v>
+      </c>
+      <c r="G14" s="57" t="n">
+        <v>-391.1765580013281</v>
+      </c>
+      <c r="H14" s="58" t="n">
+        <v>0.4912161074175423</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>SAVINGS BREAKDOWN — the spend cut, split</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
+      <c r="B16" s="43" t="n"/>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="43" t="n"/>
+      <c r="E16" s="43" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="43" t="n"/>
+      <c r="H16" s="43" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2106,7 +2847,7 @@
           <t>Cost-weighted reduction (Amdahl)</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="59">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
@@ -2139,15 +2880,15 @@
           <t>FY2025 annual ($B/yr)</t>
         </is>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="48">
         <f>SUM(Microsoft!B26,Alphabet!B26,Amazon!B26,Meta!B26,Oracle!B26,SpaceX!B26)/1000</f>
         <v/>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="48">
         <f>SUM(Microsoft!B25,Alphabet!B25,Amazon!B25,Meta!B25,Oracle!B25,SpaceX!B25)</f>
         <v/>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="48">
         <f>B20+C20</f>
         <v/>
       </c>
@@ -2158,15 +2899,15 @@
           <t>FY2025 capitalized ($B)</t>
         </is>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="53">
         <f>B20/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="53">
         <f>C20/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="53">
         <f>B21+C21</f>
         <v/>
       </c>
@@ -2177,15 +2918,15 @@
           <t>FY2026 annual ($B/yr)</t>
         </is>
       </c>
-      <c r="B22" s="39">
+      <c r="B22" s="48">
         <f>SUM(Microsoft!C26,Alphabet!C26,Amazon!C26,Meta!C26,Oracle!C26,SpaceX!C26)/1000</f>
         <v/>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="48">
         <f>SUM(Microsoft!C25,Alphabet!C25,Amazon!C25,Meta!C25,Oracle!C25,SpaceX!C25)</f>
         <v/>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="48">
         <f>B22+C22</f>
         <v/>
       </c>
@@ -2196,15 +2937,15 @@
           <t>FY2026 capitalized ($B)</t>
         </is>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="53">
         <f>B22/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="53">
         <f>C22/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="53">
         <f>B23+C23</f>
         <v/>
       </c>
@@ -2215,11 +2956,11 @@
           <t>GLOBAL capitalized -- est. ($B)</t>
         </is>
       </c>
-      <c r="B24" s="44">
+      <c r="B24" s="53">
         <f>D21/Inputs!$B$14</f>
         <v/>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="53">
         <f>D23/Inputs!$B$14</f>
         <v/>
       </c>
@@ -2252,18 +2993,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>TABS</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n"/>
-      <c r="C28" s="35" t="n"/>
-      <c r="D28" s="35" t="n"/>
-      <c r="E28" s="35" t="n"/>
-      <c r="F28" s="35" t="n"/>
-      <c r="G28" s="35" t="n"/>
-      <c r="H28" s="35" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+      <c r="H28" s="43" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2309,7 +3050,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>SpaceX value across the Today / Ceiling / live cost-weighted tiers + context sensitivity</t>
+          <t>SpaceX value under both pricing methods + how the compute lever varies with context</t>
         </is>
       </c>
     </row>
@@ -2386,14 +3127,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2403,22 +3144,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>GLOBAL INPUTS  —  edit yellow (assumption) cells; green = disclosed/market data</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Memory reduction factor</t>
-        </is>
-      </c>
-      <c r="B2" s="51" t="n">
+          <t>★ Memory reduction factor</t>
+        </is>
+      </c>
+      <c r="B2" s="60" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -2438,8 +3179,8 @@
           <t>FLOPs reduction factor</t>
         </is>
       </c>
-      <c r="B3" s="51">
-        <f>$B$24</f>
+      <c r="B3" s="61">
+        <f>$B$27</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -2449,7 +3190,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>TODAY scenario (default, RE-BASED 2026-09-01) = x793: the full-workload serving lever (decode 2.5 ms/token x 64 resident streams — an ESTIMATE, aggregate-decode receipt PENDING — prefill at the BANKED x3.936 campaign speedup) x the fit-derived equal-quality parameter ratio x4.22 at 1T (rows 23-25 below). Overtype with =B25 for the CEILING scenario (x816 = same lever, prefill at the full x7.03 maturity factor), or any number. The pre-campaign x9.24 lever is RETIRED 2026-09-01 (measured on kernels that no longer exist). See ServingTraining for the measured background blend.</t>
+          <t>B27 = inference throughput per GPU at a 262k-token average context for the active scenario (B26, picked on the Levers tab) x the equal-quality parameter ratio (B23). Edit B23-B25, or overtype this cell to pin the lever. See ServingTraining for the measured background.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +3200,7 @@
           <t>Memory share of GPU cost (BOM)</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n">
+      <c r="B4" s="62" t="n">
         <v>0.6</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -2479,7 +3220,7 @@
           <t>Opex / energy reduction factor</t>
         </is>
       </c>
-      <c r="B5" s="51">
+      <c r="B5" s="63">
         <f>B20</f>
         <v/>
       </c>
@@ -2497,10 +3238,10 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Discount rate</t>
-        </is>
-      </c>
-      <c r="B6" s="52" t="n">
+          <t>★ Discount rate</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="n">
         <v>0.06</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -2520,7 +3261,7 @@
           <t>Fully-loaded cost per GPU</t>
         </is>
       </c>
-      <c r="B7" s="53" t="n">
+      <c r="B7" s="65" t="n">
         <v>50000</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -2540,8 +3281,8 @@
           <t>Wall power per GPU</t>
         </is>
       </c>
-      <c r="B8" s="51" t="n">
-        <v>1.8</v>
+      <c r="B8" s="63" t="n">
+        <v>2.3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2550,7 +3291,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>~1 kW TDP + node overhead x PUE 1.3.</t>
+          <t>GB200 NVL72: 120-132 kW per rack / 72 GPUs = ~1.7-1.8 kW IT per GPU (incl. CPUs, switches) x PUE ~1.3 = ~2.3 kW. Was 1.8 until 2026-09-29.</t>
         </is>
       </c>
     </row>
@@ -2560,7 +3301,7 @@
           <t>Electricity rate</t>
         </is>
       </c>
-      <c r="B9" s="51" t="n">
+      <c r="B9" s="63" t="n">
         <v>0.08</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -2580,7 +3321,7 @@
           <t>Cooling/ops overhead on energy</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n">
+      <c r="B10" s="62" t="n">
         <v>0.25</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -2600,7 +3341,7 @@
           <t>Fleet useful life</t>
         </is>
       </c>
-      <c r="B11" s="51" t="n">
+      <c r="B11" s="63" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -2620,7 +3361,7 @@
           <t>SpaceX market cap</t>
         </is>
       </c>
-      <c r="B12" s="54" t="n">
+      <c r="B12" s="66" t="n">
         <v>1950</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -2640,7 +3381,7 @@
           <t>Datacenter scaling factor</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="62" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -2660,7 +3401,7 @@
           <t>Named share of global AI capex</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n">
+      <c r="B14" s="62" t="n">
         <v>0.8</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -2675,14 +3416,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>REDUCTION ENGINE (Amdahl cost-weighting) — derived</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2706,7 +3447,7 @@
           <t>Memory cost fraction after reduction</t>
         </is>
       </c>
-      <c r="B17" s="55">
+      <c r="B17" s="67">
         <f>B4/B2</f>
         <v/>
       </c>
@@ -2722,7 +3463,7 @@
           <t>Compute cost fraction after reduction</t>
         </is>
       </c>
-      <c r="B18" s="55">
+      <c r="B18" s="67">
         <f>B16/B3</f>
         <v/>
       </c>
@@ -2754,7 +3495,7 @@
           <t>COST-WEIGHTED reduction factor</t>
         </is>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="59">
         <f>1/B19</f>
         <v/>
       </c>
@@ -2770,22 +3511,22 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>SCENARIOS (2026-09-01 ruling) — TODAY (default) vs CEILING (campaign landed)</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>HELARCTOS COMPUTE LEVER — 262k-token average context. ◆ purple = differs by scenario</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="43" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equal-quality parameter ratio at 1T</t>
-        </is>
-      </c>
-      <c r="B23" s="56" t="n">
+          <t>★ Equal-quality parameter ratio at 1T (lever 1)</t>
+        </is>
+      </c>
+      <c r="B23" s="68" t="n">
         <v>4.2185</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -2795,19 +3536,18 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>FIT-DERIVED (sealed 2026-08-14 refit): bAttention matches the transformer fit's quality on 23.7% of the params at 1T -&gt; x4.22 compute per token at equal quality. 84.2% at 1B, 55.2% at 10B, 36.2% at 100B, 15.5% at 10T (x6.44). A projection of the two fits, not a measurement.</t>
+          <t>FIT-DERIVED (sealed 2026-08-14 refit): bAttention matches the transformer fit's quality on 23.7% of the params at 1T -&gt; x4.22 compute per token at equal quality. 84.2% at 1B, 55.2% at 10B, 36.2% at 100B, 15.5% at 10T (x6.44). A projection of the two fits, not a measurement. Same in both scenarios.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>TODAY compute lever = serving lever x ratio</t>
-        </is>
-      </c>
-      <c r="B24" s="57">
-        <f>188.0305*$B$23</f>
-        <v/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>◆★ Inference throughput per GPU — Current kernels (lever 5)</t>
+        </is>
+      </c>
+      <c r="B24" s="69" t="n">
+        <v>368.07</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2816,19 +3556,18 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>B3 (the FLOPs lever) points here by default. The x188.0 serving half is model-computed (campaign_landed_flop_lever): decode 2.5 ms/token x 64 resident streams — an ESTIMATE, the aggregate-decode receipt is PENDING — with prefill at the BANKED x3.936 (our own step went 400.4 -&gt; 101.7 ms at B16/T2048; 2026-08-29 clean-wall position of record); transformer side stays the measured 1/context law at its KV ceiling, 128k E[context].</t>
+          <t>Tokens served per GPU vs the transformer at the same model size, 262,144-token average context: decode 2.5 ms/token x 64 resident streams (ESTIMATE, aggregate-decode receipt PENDING), prefill at the banked x3.936; transformer at its measured KV ceiling (1 stream per GPU at 262k). Context matters: ~x12 at 8k, ~x48 at 32k, ~x188 at 128k.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CEILING compute lever (campaign landed)</t>
-        </is>
-      </c>
-      <c r="B25" s="42">
-        <f>193.3376*$B$23</f>
-        <v/>
+          <t>◆★ Inference throughput per GPU — Optimized kernels (lever 5)</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="n">
+        <v>381.9</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2837,7 +3576,49 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Same full-workload lever with prefill at the full x7.03 maturity factor = x3.936 MEASURED (already banked) x x1.786 TARGET (the funded 8k-win gate, no receipt yet). Decode-dominated, so it sits only ~3% above TODAY. Overtype B3 with =B25 to run the workbook at the ceiling (~x154 cost-weighted — memory-floored; dollars move within rounding).</t>
+          <t>Same, with prefill at the full x7.03 = x3.936 MEASURED x x1.786 TARGET (the funded kernel programme). Decode dominates at long context, so it sits only ~4% above Current kernels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>◆ Inference throughput per GPU — ACTIVE scenario</t>
+        </is>
+      </c>
+      <c r="B26" s="70">
+        <f>IF(Scenario="Optimized kernels",$B$25,$B$24)</f>
+        <v/>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Follows the scenario picked on the Levers tab (cell C4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Compute (FLOPs) lever = B23 x B26</t>
+        </is>
+      </c>
+      <c r="B27" s="71">
+        <f>$B$23*$B$26</f>
+        <v/>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>B3 points here.</t>
         </is>
       </c>
     </row>
@@ -2846,7 +3627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -2865,15 +3646,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>SENSITIVITY (SpaceX) — TODAY vs CEILING vs live cost-weighted</t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-      <c r="E1" s="35" t="n"/>
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>SENSITIVITY (SpaceX) — memory/compute cost split vs whole-GPU pricing</t>
+        </is>
+      </c>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+      <c r="E1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -2883,17 +3664,12 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>TODAY (~154x)</t>
+          <t>Memory/compute cost split (Totals engine)</t>
         </is>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>CEILING (~154x)</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>Cost-weighted (live)</t>
+          <t>Whole GPUs (Value Bridge logic)</t>
         </is>
       </c>
     </row>
@@ -2903,16 +3679,12 @@
           <t>Efficient acquisition ($B)</t>
         </is>
       </c>
-      <c r="B3" s="42">
-        <f>SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$24))</f>
-        <v/>
-      </c>
-      <c r="C3" s="42">
-        <f>SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$25))</f>
-        <v/>
-      </c>
-      <c r="D3" s="42">
+      <c r="B3" s="51">
         <f>SpaceX!$B$12/(Inputs!$B$20)</f>
+        <v/>
+      </c>
+      <c r="C3" s="51">
+        <f>SpaceX!$B$12/(MIN(Inputs!$B$2,Inputs!$B$3))</f>
         <v/>
       </c>
     </row>
@@ -2922,16 +3694,12 @@
           <t>Capex avoided/yr ($B)</t>
         </is>
       </c>
-      <c r="B4" s="42">
-        <f>SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$24))</f>
-        <v/>
-      </c>
-      <c r="C4" s="42">
-        <f>SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$25))</f>
-        <v/>
-      </c>
-      <c r="D4" s="42">
+      <c r="B4" s="51">
         <f>SpaceX!$B$12-SpaceX!$B$12/(Inputs!$B$20)</f>
+        <v/>
+      </c>
+      <c r="C4" s="51">
+        <f>SpaceX!$B$12-SpaceX!$B$12/(MIN(Inputs!$B$2,Inputs!$B$3))</f>
         <v/>
       </c>
     </row>
@@ -2941,15 +3709,11 @@
           <t>Annual opex savings ($M)</t>
         </is>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="48">
         <f>SpaceX!$B$26</f>
         <v/>
       </c>
-      <c r="C5" s="39">
-        <f>SpaceX!$B$26</f>
-        <v/>
-      </c>
-      <c r="D5" s="39">
+      <c r="C5" s="48">
         <f>SpaceX!$B$26</f>
         <v/>
       </c>
@@ -2960,16 +3724,12 @@
           <t>Sustained annual benefit ($B)</t>
         </is>
       </c>
-      <c r="B6" s="42">
-        <f>(SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$24)))+SpaceX!$B$26/1000</f>
-        <v/>
-      </c>
-      <c r="C6" s="42">
-        <f>(SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$25)))+SpaceX!$B$26/1000</f>
-        <v/>
-      </c>
-      <c r="D6" s="42">
+      <c r="B6" s="51">
         <f>(SpaceX!$B$12-SpaceX!$B$12/(Inputs!$B$20))+SpaceX!$B$26/1000</f>
+        <v/>
+      </c>
+      <c r="C6" s="51">
+        <f>(SpaceX!$B$12-SpaceX!$B$12/(MIN(Inputs!$B$2,Inputs!$B$3)))+SpaceX!$B$26/1000</f>
         <v/>
       </c>
     </row>
@@ -2979,16 +3739,12 @@
           <t>Capitalized value ($B)</t>
         </is>
       </c>
-      <c r="B7" s="41">
-        <f>((SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$24)))+SpaceX!$B$26/1000)/Inputs!$B$6</f>
-        <v/>
-      </c>
-      <c r="C7" s="41">
-        <f>((SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$25)))+SpaceX!$B$26/1000)/Inputs!$B$6</f>
-        <v/>
-      </c>
-      <c r="D7" s="41">
+      <c r="B7" s="50">
         <f>((SpaceX!$B$12-SpaceX!$B$12/(Inputs!$B$20))+SpaceX!$B$26/1000)/Inputs!$B$6</f>
+        <v/>
+      </c>
+      <c r="C7" s="50">
+        <f>((SpaceX!$B$12-SpaceX!$B$12/(MIN(Inputs!$B$2,Inputs!$B$3)))+SpaceX!$B$26/1000)/Inputs!$B$6</f>
         <v/>
       </c>
     </row>
@@ -2999,36 +3755,32 @@
         </is>
       </c>
       <c r="B8" s="25">
-        <f>(((SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$24)))+SpaceX!$B$26/1000)/Inputs!$B$6)/Inputs!$B$12</f>
+        <f>(((SpaceX!$B$12-SpaceX!$B$12/(Inputs!$B$20))+SpaceX!$B$26/1000)/Inputs!$B$6)/Inputs!$B$12</f>
         <v/>
       </c>
       <c r="C8" s="25">
-        <f>(((SpaceX!$B$12-SpaceX!$B$12/(1/(Inputs!$B$4/Inputs!$B$2+(1-Inputs!$B$4)/Inputs!$B$25)))+SpaceX!$B$26/1000)/Inputs!$B$6)/Inputs!$B$12</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>(((SpaceX!$B$12-SpaceX!$B$12/(Inputs!$B$20))+SpaceX!$B$26/1000)/Inputs!$B$6)/Inputs!$B$12</f>
+        <f>(((SpaceX!$B$12-SpaceX!$B$12/(MIN(Inputs!$B$2,Inputs!$B$3)))+SpaceX!$B$26/1000)/Inputs!$B$6)/Inputs!$B$12</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Base = SpaceX accelerator capex (SpaceX!B12), not total capex. The 'Cost-weighted' column ties to the SpaceX tab (B25/B27) at the conservative dc_scale=0.</t>
+          <t>Base = SpaceX accelerator capex (SpaceX!B12), not total capex. The first column ties to the SpaceX tab (B25/B27) at the conservative dc_scale=0; the second prices the fleet on whole GPUs (shrinks by the smaller of the memory and compute levers).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>CONTEXT SENSITIVITY — prefill share of serving cost vs fleet E[context]</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="43" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="E12" s="43" t="n"/>
+      <c r="F12" s="43" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -3043,24 +3795,20 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Our prefill share (Today)</t>
+          <t>Our prefill share</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Today lever (x)</t>
+          <t>Compute lever (x)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Ceiling lever (x)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Today-&gt;Ceiling gap</t>
-        </is>
-      </c>
+          <t>Throughput per GPU, same size (x)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3068,20 +3816,17 @@
           <t>8k</t>
         </is>
       </c>
-      <c r="B14" s="55" t="n">
+      <c r="B14" s="67" t="n">
         <v>0.005899250258734248</v>
       </c>
       <c r="C14" s="25" t="n">
         <v>0.05208995366081766</v>
       </c>
-      <c r="D14" s="41" t="n">
+      <c r="D14" s="50" t="n">
         <v>50.29665229131971</v>
       </c>
-      <c r="E14" s="41" t="n">
-        <v>51.47706163855121</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>0.02346894462069837</v>
+      <c r="E14" s="48" t="n">
+        <v>11.92287815199857</v>
       </c>
     </row>
     <row r="15">
@@ -3090,70 +3835,61 @@
           <t>32k</t>
         </is>
       </c>
-      <c r="B15" s="55" t="n">
+      <c r="B15" s="67" t="n">
         <v>0.002981160980333002</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>0.05196631516233694</v>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D15" s="50" t="n">
         <v>200.6239377794075</v>
       </c>
-      <c r="E15" s="41" t="n">
-        <v>205.3209324850361</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>0.02341193557267873</v>
+      <c r="E15" s="48" t="n">
+        <v>47.55813072137281</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>128k (pinned)</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>128k</t>
+        </is>
+      </c>
+      <c r="B16" s="67" t="n">
         <v>0.002359266800993781</v>
       </c>
       <c r="C16" s="25" t="n">
         <v>0.06235575593664416</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D16" s="50" t="n">
         <v>793.2064858179596</v>
       </c>
-      <c r="E16" s="41" t="n">
-        <v>815.5945097216911</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>0.0282247110985796</v>
+      <c r="E16" s="48" t="n">
+        <v>188.0304920694428</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>256k</t>
-        </is>
-      </c>
-      <c r="B17" s="55" t="n">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>262k (used)</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="n">
         <v>0.00230050437708008</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>0.08221381175542121</v>
       </c>
-      <c r="D17" s="41" t="n">
+      <c r="D17" s="50" t="n">
         <v>1552.723400990788</v>
       </c>
-      <c r="E17" s="41" t="n">
-        <v>1611.029390134314</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>0.03755078921739785</v>
+      <c r="E17" s="48" t="n">
+        <v>368.0748334211694</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Cost = box wall-clock, not FLOPs. The transformer's decode leg is KV-bandwidth-bound (measured 1/context law) while its prefill runs near peak, so prefill is &lt;1% of its serving cost at every context — which is why the banked x3.936 prefill (TODAY) and the full x7.03 (CEILING) land within a few percent of each other. Inputs!B24/B25 quote the pinned 128k row (2026-08-31 fleet-context ruling). Static values from the the model — rebuild the workbook to refresh.</t>
+          <t>Cost = box wall-clock, not FLOPs. The transformer's decode leg is KV-bandwidth-bound (measured 1/context law) while its prefill runs near peak, so prefill is &lt;1% of its serving cost at every context, and the lever is set by decode. Inputs!B24 quotes the pinned 262k row (2026-09-29 ruling). Static values computed by the model — rebuild the workbook to refresh.</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -3183,14 +3919,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>COST LADDER — $/H100-equivalent GPU-hour (at scale). Green = market price; yellow = assumption.</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -3220,10 +3956,10 @@
           <t>Own custom silicon (TPU/Trainium)</t>
         </is>
       </c>
-      <c r="B3" s="58" t="n">
+      <c r="B3" s="72" t="n">
         <v>0.9</v>
       </c>
-      <c r="C3" s="58" t="n">
+      <c r="C3" s="72" t="n">
         <v>1.4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -3238,10 +3974,10 @@
           <t>Buy + operate NVIDIA (scale)</t>
         </is>
       </c>
-      <c r="B4" s="58" t="n">
+      <c r="B4" s="72" t="n">
         <v>1.5</v>
       </c>
-      <c r="C4" s="58" t="n">
+      <c r="C4" s="72" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3256,10 +3992,10 @@
           <t>Rent NVIDIA - neocloud / committed</t>
         </is>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="72" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="58" t="n">
+      <c r="C5" s="72" t="n">
         <v>3.5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3274,10 +4010,10 @@
           <t>Rent NVIDIA - hyperscaler on-demand</t>
         </is>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="58" t="n">
+      <c r="C6" s="72" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3287,14 +4023,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>OWNED-NVIDIA TCO CROSS-CHECK (from Inputs)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3302,7 +4038,7 @@
           <t>Utilization</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="39" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -3312,7 +4048,7 @@
           <t>Capex $/hr</t>
         </is>
       </c>
-      <c r="B10" s="42">
+      <c r="B10" s="51">
         <f>Inputs!$B$7/(Inputs!$B$11*8760*B9)</f>
         <v/>
       </c>
@@ -3328,7 +4064,7 @@
           <t>Power $/hr</t>
         </is>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="51">
         <f>Inputs!$B$8*Inputs!$B$9</f>
         <v/>
       </c>
@@ -3344,7 +4080,7 @@
           <t>DC/staff adder $/hr</t>
         </is>
       </c>
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="73" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -3354,7 +4090,7 @@
           <t>Owned TCO $/hr</t>
         </is>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" s="74">
         <f>B10+B11+B12</f>
         <v/>
       </c>
@@ -3411,7 +4147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -3430,28 +4166,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>SERVING &amp; TRAINING — measured 2026-08-07/08 (2/4/8 x H100), priced at the CostLadder rent mid ($2.50/GPU-hr). Source: internal measurement archive (keys in the model).</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-      <c r="E1" s="35" t="n"/>
-      <c r="F1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+      <c r="E1" s="43" t="n"/>
+      <c r="F1" s="43" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>WORKLOAD — measured pre-campaign blend (background; the workbook lever lives at Inputs B24/B25)</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n"/>
-      <c r="C4" s="35" t="n"/>
-      <c r="D4" s="35" t="n"/>
-      <c r="E4" s="35" t="n"/>
-      <c r="F4" s="35" t="n"/>
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3466,7 +4202,7 @@
           <t>Input : output token ratio</t>
         </is>
       </c>
-      <c r="B7" s="51" t="n">
+      <c r="B7" s="63" t="n">
         <v>10</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3481,7 +4217,7 @@
           <t>E[context] (tokens)</t>
         </is>
       </c>
-      <c r="B8" s="53" t="n">
+      <c r="B8" s="65" t="n">
         <v>65536</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3496,7 +4232,7 @@
           <t>Training share of accelerator cost</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="73" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3518,7 +4254,7 @@
           <t>Owned decode, tokens/s/box (context-flat)</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n">
+      <c r="B12" s="47" t="n">
         <v>4496.668604837461</v>
       </c>
     </row>
@@ -3528,7 +4264,7 @@
           <t>KV MB per token per stream</t>
         </is>
       </c>
-      <c r="B13" s="59" t="n">
+      <c r="B13" s="75" t="n">
         <v>0.15234375</v>
       </c>
     </row>
@@ -3538,7 +4274,7 @@
           <t>HBM TB/s per GPU</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="73" t="n">
         <v>3.35</v>
       </c>
     </row>
@@ -3548,7 +4284,7 @@
           <t>Transformer KV compression (mature stack)</t>
         </is>
       </c>
-      <c r="B15" s="51" t="n">
+      <c r="B15" s="63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3558,7 +4294,7 @@
           <t>GPUs per box</t>
         </is>
       </c>
-      <c r="B16" s="60" t="n">
+      <c r="B16" s="76" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3568,7 +4304,7 @@
           <t>Training advantage, short sequence (owned / transformer)</t>
         </is>
       </c>
-      <c r="B17" s="61" t="n">
+      <c r="B17" s="77" t="n">
         <v>0.5825609168739003</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3590,7 +4326,7 @@
           <t>KV GB per stream</t>
         </is>
       </c>
-      <c r="B20" s="42">
+      <c r="B20" s="51">
         <f>$B$8*$B$13/1024</f>
         <v/>
       </c>
@@ -3601,7 +4337,7 @@
           <t>KV GB per stream, compressed</t>
         </is>
       </c>
-      <c r="B21" s="62">
+      <c r="B21" s="78">
         <f>$B$20/$B$15</f>
         <v/>
       </c>
@@ -3612,7 +4348,7 @@
           <t>Transformer decode, tokens/s/box</t>
         </is>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="50">
         <f>511.8416*32768/$B$8*$B$15*$B$16</f>
         <v/>
       </c>
@@ -3628,7 +4364,7 @@
           <t>Prefill table row (lookup)</t>
         </is>
       </c>
-      <c r="B23" s="63">
+      <c r="B23" s="79">
         <f>MATCH($B$8,$A$33:$A$39,1)</f>
         <v/>
       </c>
@@ -3639,7 +4375,7 @@
           <t>Prefill tokens/s/box — transformer</t>
         </is>
       </c>
-      <c r="B24" s="41">
+      <c r="B24" s="50">
         <f>IF(INDEX($B$33:$B$39,MIN($B$23+1,7))=INDEX($B$33:$B$39,$B$23),INDEX($B$33:$B$39,$B$23),EXP(LN(INDEX($B$33:$B$39,$B$23))+(LN($B$8)-LN(INDEX($A$33:$A$39,$B$23)))/(LN(INDEX($A$33:$A$39,MIN($B$23+1,7)))-LN(INDEX($A$33:$A$39,$B$23)))*(LN(INDEX($B$33:$B$39,MIN($B$23+1,7)))-LN(INDEX($B$33:$B$39,$B$23)))))*$B$16</f>
         <v/>
       </c>
@@ -3650,7 +4386,7 @@
           <t>Prefill tokens/s/box — owned</t>
         </is>
       </c>
-      <c r="B25" s="41">
+      <c r="B25" s="50">
         <f>IF(INDEX($C$33:$C$39,MIN($B$23+1,7))=INDEX($C$33:$C$39,$B$23),INDEX($C$33:$C$39,$B$23),EXP(LN(INDEX($C$33:$C$39,$B$23))+(LN($B$8)-LN(INDEX($A$33:$A$39,$B$23)))/(LN(INDEX($A$33:$A$39,MIN($B$23+1,7)))-LN(INDEX($A$33:$A$39,$B$23)))*(LN(INDEX($C$33:$C$39,MIN($B$23+1,7)))-LN(INDEX($C$33:$C$39,$B$23)))))*$B$16</f>
         <v/>
       </c>
@@ -3661,7 +4397,7 @@
           <t>Transformer seconds per generated token</t>
         </is>
       </c>
-      <c r="B26" s="64">
+      <c r="B26" s="80">
         <f>$B$7/$B$24+1/$B$22</f>
         <v/>
       </c>
@@ -3672,7 +4408,7 @@
           <t>Owned seconds per generated token</t>
         </is>
       </c>
-      <c r="B27" s="64">
+      <c r="B27" s="80">
         <f>$B$7/$B$25+1/$B$12</f>
         <v/>
       </c>
@@ -3683,7 +4419,7 @@
           <t>BLENDED COMPUTE LEVER (flop_factor)</t>
         </is>
       </c>
-      <c r="B28" s="57">
+      <c r="B28" s="74">
         <f>IF($B$9&gt;0,1/($B$9/$B$17+(1-$B$9)/($B$26/$B$27)),$B$26/$B$27)</f>
         <v/>
       </c>
@@ -3699,7 +4435,7 @@
           <t xml:space="preserve">  of which: prefill advantage</t>
         </is>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="51">
         <f>($B$7/$B$24)/($B$7/$B$25)</f>
         <v/>
       </c>
@@ -3710,7 +4446,7 @@
           <t xml:space="preserve">  of which: decode advantage</t>
         </is>
       </c>
-      <c r="B30" s="65">
+      <c r="B30" s="61">
         <f>(1/$B$22)/(1/$B$12)</f>
         <v/>
       </c>
@@ -3721,96 +4457,96 @@
           <t>Measured prefill throughput, tokens/s/GPU (bf16 saturated lane, d2048)</t>
         </is>
       </c>
-      <c r="D32" s="66" t="inlineStr">
+      <c r="D32" s="81" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="E32" s="66" t="inlineStr">
+      <c r="E32" s="81" t="inlineStr">
         <is>
           <t>Transformer</t>
         </is>
       </c>
-      <c r="F32" s="66" t="inlineStr">
+      <c r="F32" s="81" t="inlineStr">
         <is>
           <t>Owned</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="67" t="n">
+      <c r="A33" s="82" t="n">
         <v>2048</v>
       </c>
-      <c r="B33" s="38" t="n">
+      <c r="B33" s="47" t="n">
         <v>4682606.88285999</v>
       </c>
-      <c r="C33" s="38" t="n">
+      <c r="C33" s="47" t="n">
         <v>1185825</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="67" t="n">
+      <c r="A34" s="82" t="n">
         <v>8192</v>
       </c>
-      <c r="B34" s="38" t="n">
+      <c r="B34" s="47" t="n">
         <v>3450080</v>
       </c>
-      <c r="C34" s="38" t="n">
+      <c r="C34" s="47" t="n">
         <v>1183690</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="67" t="n">
+      <c r="A35" s="82" t="n">
         <v>32768</v>
       </c>
-      <c r="B35" s="38" t="n">
+      <c r="B35" s="47" t="n">
         <v>1711802</v>
       </c>
-      <c r="C35" s="38" t="n">
+      <c r="C35" s="47" t="n">
         <v>1186661</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="67" t="n">
+      <c r="A36" s="82" t="n">
         <v>65536</v>
       </c>
-      <c r="B36" s="38" t="n">
+      <c r="B36" s="47" t="n">
         <v>1007187</v>
       </c>
-      <c r="C36" s="38" t="n">
+      <c r="C36" s="47" t="n">
         <v>1181622</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="n">
+      <c r="A37" s="82" t="n">
         <v>131072</v>
       </c>
-      <c r="B37" s="38" t="n">
+      <c r="B37" s="47" t="n">
         <v>541094</v>
       </c>
-      <c r="C37" s="38" t="n">
+      <c r="C37" s="47" t="n">
         <v>978107</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="67" t="n">
+      <c r="A38" s="82" t="n">
         <v>262144</v>
       </c>
-      <c r="B38" s="38" t="n">
+      <c r="B38" s="47" t="n">
         <v>277474</v>
       </c>
-      <c r="C38" s="38" t="n">
+      <c r="C38" s="47" t="n">
         <v>726142</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="67" t="n">
+      <c r="A39" s="82" t="n">
         <v>524288</v>
       </c>
-      <c r="B39" s="38" t="n">
+      <c r="B39" s="47" t="n">
         <v>140820</v>
       </c>
-      <c r="C39" s="38" t="n">
+      <c r="C39" s="47" t="n">
         <v>478522</v>
       </c>
     </row>
@@ -3822,153 +4558,153 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Serving at long context — $/1M generated tokens, one 8xH100 box</t>
         </is>
       </c>
-      <c r="B43" s="35" t="n"/>
-      <c r="C43" s="35" t="n"/>
-      <c r="D43" s="35" t="n"/>
-      <c r="E43" s="35" t="n"/>
-      <c r="F43" s="35" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="66" t="inlineStr">
+      <c r="A44" s="81" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="B44" s="66" t="inlineStr">
+      <c r="B44" s="81" t="inlineStr">
         <is>
           <t>bAttention $/1M tok</t>
         </is>
       </c>
-      <c r="C44" s="66" t="inlineStr">
+      <c r="C44" s="81" t="inlineStr">
         <is>
           <t>Transformer $/1M tok (mature stack)</t>
         </is>
       </c>
-      <c r="D44" s="66" t="inlineStr">
+      <c r="D44" s="81" t="inlineStr">
         <is>
           <t>TF streams/GPU</t>
         </is>
       </c>
-      <c r="E44" s="66" t="inlineStr">
+      <c r="E44" s="81" t="inlineStr">
         <is>
           <t>Cost ratio</t>
         </is>
       </c>
-      <c r="F44" s="66" t="inlineStr">
+      <c r="F44" s="81" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="67" t="n">
+      <c r="A45" s="82" t="n">
         <v>4096</v>
       </c>
-      <c r="B45" s="68" t="n">
+      <c r="B45" s="83" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C45" s="69" t="n">
+      <c r="C45" s="84" t="n">
         <v>0.1695945640120853</v>
       </c>
-      <c r="D45" s="63" t="n">
+      <c r="D45" s="79" t="n">
         <v>118</v>
       </c>
-      <c r="E45" s="70" t="n">
+      <c r="E45" s="85" t="n">
         <v>0.1372698992779634</v>
       </c>
       <c r="F45" s="24" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="67" t="n">
+      <c r="A46" s="82" t="n">
         <v>16384</v>
       </c>
-      <c r="B46" s="68" t="n">
+      <c r="B46" s="83" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C46" s="69" t="n">
+      <c r="C46" s="84" t="n">
         <v>0.678378256048341</v>
       </c>
-      <c r="D46" s="63" t="n">
+      <c r="D46" s="79" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="70" t="n">
+      <c r="E46" s="85" t="n">
         <v>0.5490795971118535</v>
       </c>
       <c r="F46" s="24" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="67" t="n">
+      <c r="A47" s="82" t="n">
         <v>32768</v>
       </c>
-      <c r="B47" s="68" t="n">
+      <c r="B47" s="83" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C47" s="69" t="n">
+      <c r="C47" s="84" t="n">
         <v>1.356756512096682</v>
       </c>
-      <c r="D47" s="63" t="n">
+      <c r="D47" s="79" t="n">
         <v>14</v>
       </c>
-      <c r="E47" s="70" t="n">
+      <c r="E47" s="85" t="n">
         <v>1.098159194223707</v>
       </c>
       <c r="F47" s="24" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="67" t="n">
+      <c r="A48" s="82" t="n">
         <v>65536</v>
       </c>
-      <c r="B48" s="68" t="n">
+      <c r="B48" s="83" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C48" s="69" t="n">
+      <c r="C48" s="84" t="n">
         <v>2.713513024193364</v>
       </c>
-      <c r="D48" s="63" t="n">
+      <c r="D48" s="79" t="n">
         <v>7</v>
       </c>
-      <c r="E48" s="70" t="n">
+      <c r="E48" s="85" t="n">
         <v>2.196318388447414</v>
       </c>
       <c r="F48" s="24" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="67" t="n">
+      <c r="A49" s="82" t="n">
         <v>131072</v>
       </c>
-      <c r="B49" s="68" t="n">
+      <c r="B49" s="83" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C49" s="69" t="n">
+      <c r="C49" s="84" t="n">
         <v>5.427026048386728</v>
       </c>
-      <c r="D49" s="63" t="n">
+      <c r="D49" s="79" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="70" t="n">
+      <c r="E49" s="85" t="n">
         <v>4.392636776894828</v>
       </c>
       <c r="F49" s="24" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="67" t="n">
+      <c r="A50" s="82" t="n">
         <v>262144</v>
       </c>
-      <c r="B50" s="68" t="n">
+      <c r="B50" s="83" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C50" s="69" t="n">
+      <c r="C50" s="84" t="n">
         <v>10.85405209677346</v>
       </c>
-      <c r="D50" s="63" t="n">
+      <c r="D50" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="70" t="n">
+      <c r="E50" s="85" t="n">
         <v>8.785273553789656</v>
       </c>
       <c r="F50" s="24" t="inlineStr">
@@ -3978,19 +4714,19 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="67" t="n">
+      <c r="A51" s="82" t="n">
         <v>1048576</v>
       </c>
-      <c r="B51" s="71" t="n">
+      <c r="B51" s="86" t="n">
         <v>1.235482541359387</v>
       </c>
-      <c r="C51" s="69" t="n">
-        <v/>
-      </c>
-      <c r="D51" s="63" t="n">
+      <c r="C51" s="84" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="79" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="70" t="n">
+      <c r="E51" s="85" t="n">
         <v/>
       </c>
       <c r="F51" s="24" t="inlineStr">
@@ -4007,36 +4743,36 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="A54" s="42" t="inlineStr">
         <is>
           <t>Training at scale — same cluster, more steps/s</t>
         </is>
       </c>
-      <c r="B54" s="35" t="n"/>
-      <c r="C54" s="35" t="n"/>
-      <c r="D54" s="35" t="n"/>
-      <c r="E54" s="35" t="n"/>
-      <c r="F54" s="35" t="n"/>
+      <c r="B54" s="43" t="n"/>
+      <c r="C54" s="43" t="n"/>
+      <c r="D54" s="43" t="n"/>
+      <c r="E54" s="43" t="n"/>
+      <c r="F54" s="43" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="66" t="inlineStr">
+      <c r="A55" s="81" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B55" s="66" t="inlineStr">
+      <c r="B55" s="81" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C55" s="66" t="inlineStr">
+      <c r="C55" s="81" t="inlineStr">
         <is>
           <t>Ratio / consequence</t>
         </is>
       </c>
-      <c r="D55" s="66" t="inlineStr"/>
-      <c r="E55" s="66" t="inlineStr"/>
-      <c r="F55" s="66" t="inlineStr">
+      <c r="D55" s="81" t="inlineStr"/>
+      <c r="E55" s="81" t="inlineStr"/>
+      <c r="F55" s="81" t="inlineStr">
         <is>
           <t>Status — internal measurement archive key</t>
         </is>
@@ -4048,12 +4784,12 @@
           <t>8-GPU speedup, matched load (16 in flight)</t>
         </is>
       </c>
-      <c r="B56" s="72" t="inlineStr">
+      <c r="B56" s="87" t="inlineStr">
         <is>
           <t>x5.15 fwd+bwd vs x3.70 fwd-only Ulysses best</t>
         </is>
       </c>
-      <c r="C56" s="73" t="inlineStr">
+      <c r="C56" s="88" t="inlineStr">
         <is>
           <t>x1.39 cluster throughput</t>
         </is>
@@ -4070,12 +4806,12 @@
           <t>8-GPU speedup, deep load (256 in flight)</t>
         </is>
       </c>
-      <c r="B57" s="72" t="inlineStr">
+      <c r="B57" s="87" t="inlineStr">
         <is>
           <t>x6.27 (pipeline keeps filling; TF saturated by 16)</t>
         </is>
       </c>
-      <c r="C57" s="73" t="inlineStr">
+      <c r="C57" s="88" t="inlineStr">
         <is>
           <t>x1.70</t>
         </is>
@@ -4092,7 +4828,7 @@
           <t>GPU-hours for the same training work</t>
         </is>
       </c>
-      <c r="B58" s="74" t="inlineStr">
+      <c r="B58" s="89" t="inlineStr">
         <is>
           <t>-28% (matched) … -41% (deep)</t>
         </is>
@@ -4110,7 +4846,7 @@
           <t>64k-token sequence on one 80 GB GPU</t>
         </is>
       </c>
-      <c r="B59" s="72" t="inlineStr">
+      <c r="B59" s="87" t="inlineStr">
         <is>
           <t>30.9 GB fits vs OOM (78.4 GB attempted)</t>
         </is>
@@ -4128,12 +4864,12 @@
           <t>Pipeline per-GPU peak (flat in load)</t>
         </is>
       </c>
-      <c r="B60" s="72" t="inlineStr">
+      <c r="B60" s="87" t="inlineStr">
         <is>
           <t>9.05 GB vs 43.3 GB GPipe stage</t>
         </is>
       </c>
-      <c r="C60" s="73" t="inlineStr">
+      <c r="C60" s="88" t="inlineStr">
         <is>
           <t>x4.8 (component-scope, width-unmatched)</t>
         </is>
@@ -4150,7 +4886,7 @@
           <t>Params for equal quality at 70B</t>
         </is>
       </c>
-      <c r="B61" s="75" t="inlineStr">
+      <c r="B61" s="90" t="inlineStr">
         <is>
           <t>x4.1 [2.2-7.7] transformer</t>
         </is>
@@ -4168,7 +4904,7 @@
           <t>Tokens for equal quality at 70B</t>
         </is>
       </c>
-      <c r="B62" s="75" t="inlineStr">
+      <c r="B62" s="90" t="inlineStr">
         <is>
           <t>x1.68 [1.33-2.10] (beta=0.28 assumption)</t>
         </is>
@@ -4186,7 +4922,7 @@
           <t>Token-by-token vs production training</t>
         </is>
       </c>
-      <c r="B63" s="72" t="inlineStr">
+      <c r="B63" s="87" t="inlineStr">
         <is>
           <t>x24 cost to run training token-by-token instead of the production path</t>
         </is>
@@ -4199,16 +4935,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="A65" s="42" t="inlineStr">
         <is>
           <t>The measured workload blend (pre-campaign background; the workbook lever lives at Inputs B24/B25)</t>
         </is>
       </c>
-      <c r="B65" s="35" t="n"/>
-      <c r="C65" s="35" t="n"/>
-      <c r="D65" s="35" t="n"/>
-      <c r="E65" s="35" t="n"/>
-      <c r="F65" s="35" t="n"/>
+      <c r="B65" s="43" t="n"/>
+      <c r="C65" s="43" t="n"/>
+      <c r="D65" s="43" t="n"/>
+      <c r="E65" s="43" t="n"/>
+      <c r="F65" s="43" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -4218,16 +4954,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="A68" s="42" t="inlineStr">
         <is>
           <t>Estimated TRAINING cost at equal quality (ESTIMATE: measured kernels x fitted quality)</t>
         </is>
       </c>
-      <c r="B68" s="35" t="n"/>
-      <c r="C68" s="35" t="n"/>
-      <c r="D68" s="35" t="n"/>
-      <c r="E68" s="35" t="n"/>
-      <c r="F68" s="35" t="n"/>
+      <c r="B68" s="43" t="n"/>
+      <c r="C68" s="43" t="n"/>
+      <c r="D68" s="43" t="n"/>
+      <c r="E68" s="43" t="n"/>
+      <c r="F68" s="43" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -4237,37 +4973,37 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="66" t="inlineStr">
+      <c r="A71" s="81" t="inlineStr">
         <is>
           <t>Transformer params</t>
         </is>
       </c>
-      <c r="B71" s="66" t="inlineStr">
+      <c r="B71" s="81" t="inlineStr">
         <is>
           <t>s(N) fit</t>
         </is>
       </c>
-      <c r="C71" s="66" t="inlineStr">
+      <c r="C71" s="81" t="inlineStr">
         <is>
           <t>Chinchilla 2k</t>
         </is>
       </c>
-      <c r="D71" s="66" t="inlineStr">
+      <c r="D71" s="81" t="inlineStr">
         <is>
           <t>Chinchilla 8k</t>
         </is>
       </c>
-      <c r="E71" s="66" t="inlineStr">
+      <c r="E71" s="81" t="inlineStr">
         <is>
           <t>Chinchilla 32k</t>
         </is>
       </c>
-      <c r="F71" s="66" t="inlineStr">
+      <c r="F71" s="81" t="inlineStr">
         <is>
           <t>Chinchilla 256k*</t>
         </is>
       </c>
-      <c r="G71" s="66" t="inlineStr">
+      <c r="G71" s="81" t="inlineStr">
         <is>
           <t>Fixed-D 2k / 8k / 32k / 256k*</t>
         </is>
@@ -4279,22 +5015,22 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="B72" s="56" t="n">
+      <c r="B72" s="73" t="n">
         <v>1.187536580013817</v>
       </c>
-      <c r="C72" s="42" t="n">
+      <c r="C72" s="51" t="n">
         <v>0.8215525301701575</v>
       </c>
-      <c r="D72" s="42" t="n">
+      <c r="D72" s="51" t="n">
         <v>1.151570796996963</v>
       </c>
-      <c r="E72" s="42" t="n">
+      <c r="E72" s="51" t="n">
         <v>2.471643864304184</v>
       </c>
-      <c r="F72" s="42" t="n">
+      <c r="F72" s="51" t="n">
         <v>14.79232582583825</v>
       </c>
-      <c r="G72" s="73" t="inlineStr">
+      <c r="G72" s="88" t="inlineStr">
         <is>
           <t>0.69 / 0.97 / 2.08 / 12.46</t>
         </is>
@@ -4306,22 +5042,22 @@
           <t>10B</t>
         </is>
       </c>
-      <c r="B73" s="56" t="n">
+      <c r="B73" s="73" t="n">
         <v>1.811968550196262</v>
       </c>
-      <c r="C73" s="42" t="n">
+      <c r="C73" s="51" t="n">
         <v>1.912681494778985</v>
       </c>
-      <c r="D73" s="42" t="n">
+      <c r="D73" s="51" t="n">
         <v>2.681007084096966</v>
       </c>
-      <c r="E73" s="42" t="n">
+      <c r="E73" s="51" t="n">
         <v>5.754309441368888</v>
       </c>
-      <c r="F73" s="42" t="n">
+      <c r="F73" s="51" t="n">
         <v>34.43846477590683</v>
       </c>
-      <c r="G73" s="73" t="inlineStr">
+      <c r="G73" s="88" t="inlineStr">
         <is>
           <t>1.06 / 1.48 / 3.18 / 19.01</t>
         </is>
@@ -4333,22 +5069,22 @@
           <t>100B</t>
         </is>
       </c>
-      <c r="B74" s="56" t="n">
+      <c r="B74" s="73" t="n">
         <v>2.764740120141925</v>
       </c>
-      <c r="C74" s="42" t="n">
+      <c r="C74" s="51" t="n">
         <v>4.452972106010361</v>
       </c>
-      <c r="D74" s="42" t="n">
+      <c r="D74" s="51" t="n">
         <v>6.241734336892029</v>
       </c>
-      <c r="E74" s="42" t="n">
+      <c r="E74" s="51" t="n">
         <v>13.3967832604187</v>
       </c>
-      <c r="F74" s="42" t="n">
+      <c r="F74" s="51" t="n">
         <v>80.17723988000094</v>
       </c>
-      <c r="G74" s="73" t="inlineStr">
+      <c r="G74" s="88" t="inlineStr">
         <is>
           <t>1.61 / 2.26 / 4.85 / 29.00</t>
         </is>
@@ -4360,22 +5096,22 @@
           <t>1T</t>
         </is>
       </c>
-      <c r="B75" s="56" t="n">
+      <c r="B75" s="73" t="n">
         <v>4.21849922897088</v>
       </c>
-      <c r="C75" s="42" t="n">
+      <c r="C75" s="51" t="n">
         <v>10.36710013195259</v>
       </c>
-      <c r="D75" s="42" t="n">
+      <c r="D75" s="51" t="n">
         <v>14.53157202136217</v>
       </c>
-      <c r="E75" s="42" t="n">
+      <c r="E75" s="51" t="n">
         <v>31.1894595790005</v>
       </c>
-      <c r="F75" s="42" t="n">
+      <c r="F75" s="51" t="n">
         <v>186.6630767836249</v>
       </c>
-      <c r="G75" s="73" t="inlineStr">
+      <c r="G75" s="88" t="inlineStr">
         <is>
           <t>2.46 / 3.44 / 7.39 / 44.25</t>
         </is>
@@ -4387,22 +5123,22 @@
           <t>10T</t>
         </is>
       </c>
-      <c r="B76" s="56" t="n">
+      <c r="B76" s="73" t="n">
         <v>6.436675771144228</v>
       </c>
-      <c r="C76" s="42" t="n">
+      <c r="C76" s="51" t="n">
         <v>24.13596191201503</v>
       </c>
-      <c r="D76" s="42" t="n">
+      <c r="D76" s="51" t="n">
         <v>33.83139589327395</v>
       </c>
-      <c r="E76" s="42" t="n">
+      <c r="E76" s="51" t="n">
         <v>72.61313181830963</v>
       </c>
-      <c r="F76" s="42" t="n">
+      <c r="F76" s="51" t="n">
         <v>434.576000451976</v>
       </c>
-      <c r="G76" s="73" t="inlineStr">
+      <c r="G76" s="88" t="inlineStr">
         <is>
           <t>3.75 / 5.26 / 11.28 / 67.52</t>
         </is>
@@ -4416,37 +5152,37 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="66" t="inlineStr">
+      <c r="A80" s="81" t="inlineStr">
         <is>
           <t>Training curriculum</t>
         </is>
       </c>
-      <c r="B80" s="66" t="inlineStr">
+      <c r="B80" s="81" t="inlineStr">
         <is>
           <t>Advantage (TF / ours)</t>
         </is>
       </c>
-      <c r="C80" s="66" t="inlineStr">
+      <c r="C80" s="81" t="inlineStr">
         <is>
           <t>Effective r</t>
         </is>
       </c>
-      <c r="D80" s="66" t="inlineStr">
+      <c r="D80" s="81" t="inlineStr">
         <is>
           <t>Mix: token share -&gt; transformer cost share</t>
         </is>
       </c>
-      <c r="E80" s="66" t="inlineStr">
+      <c r="E80" s="81" t="inlineStr">
         <is>
           <t>FY25 cut @ 20% training</t>
         </is>
       </c>
-      <c r="F80" s="66" t="inlineStr">
+      <c r="F80" s="81" t="inlineStr">
         <is>
           <t>vs serving-only</t>
         </is>
       </c>
-      <c r="G80" s="66" t="inlineStr">
+      <c r="G80" s="81" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -4458,10 +5194,10 @@
           <t>Legacy short (all training at 2k)</t>
         </is>
       </c>
-      <c r="B81" s="76" t="n">
+      <c r="B81" s="91" t="n">
         <v>0.5825609168739004</v>
       </c>
-      <c r="C81" s="77" t="n">
+      <c r="C81" s="92" t="n">
         <v>1.716558682594317</v>
       </c>
       <c r="D81" s="24" t="inlineStr">
@@ -4469,13 +5205,13 @@
           <t>2k: 100% tok -&gt; 100% cost</t>
         </is>
       </c>
-      <c r="E81" s="78" t="n">
-        <v>149.7773849697697</v>
-      </c>
-      <c r="F81" s="79" t="n">
-        <v>-10.77282758605313</v>
-      </c>
-      <c r="G81" s="80" t="inlineStr">
+      <c r="E81" s="93" t="n">
+        <v>151.049323023638</v>
+      </c>
+      <c r="F81" s="94" t="n">
+        <v>-10.90451281465531</v>
+      </c>
+      <c r="G81" s="95" t="inlineStr">
         <is>
           <t>MEASURED (degenerate one-context case)</t>
         </is>
@@ -4487,10 +5223,10 @@
           <t>Modern standard (8k bulk + 64k/256k extension)</t>
         </is>
       </c>
-      <c r="B82" s="76" t="n">
+      <c r="B82" s="91" t="n">
         <v>2.220667013967386</v>
       </c>
-      <c r="C82" s="77" t="n">
+      <c r="C82" s="92" t="n">
         <v>0.4503151502275102</v>
       </c>
       <c r="D82" s="24" t="inlineStr">
@@ -4498,13 +5234,13 @@
           <t>8k: 70% tok -&gt; 26% cost  64k: 20% tok -&gt; 27% cost  256k: 10% tok -&gt; 47% cost</t>
         </is>
       </c>
-      <c r="E82" s="78" t="n">
-        <v>153.657942599222</v>
-      </c>
-      <c r="F82" s="79" t="n">
-        <v>-6.892269956600785</v>
-      </c>
-      <c r="G82" s="81" t="inlineStr">
+      <c r="E82" s="93" t="n">
+        <v>154.9628350868998</v>
+      </c>
+      <c r="F82" s="94" t="n">
+        <v>-6.991000751393557</v>
+      </c>
+      <c r="G82" s="96" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE ASSUMPTION</t>
         </is>
@@ -4516,10 +5252,10 @@
           <t>Long-context heavy (frontier extension phases)</t>
         </is>
       </c>
-      <c r="B83" s="76" t="n">
+      <c r="B83" s="91" t="n">
         <v>7.743424712739709</v>
       </c>
-      <c r="C83" s="77" t="n">
+      <c r="C83" s="92" t="n">
         <v>0.1291418251093435</v>
       </c>
       <c r="D83" s="24" t="inlineStr">
@@ -4527,13 +5263,13 @@
           <t>8k: 40% tok -&gt; 4% cost  64k: 25% tok -&gt; 10% cost  256k: 25% tok -&gt; 34% cost  1024k: 10% tok -&gt; 52% cost</t>
         </is>
       </c>
-      <c r="E83" s="78" t="n">
-        <v>154.6422173973205</v>
-      </c>
-      <c r="F83" s="79" t="n">
-        <v>-5.907995158502331</v>
-      </c>
-      <c r="G83" s="81" t="inlineStr">
+      <c r="E83" s="93" t="n">
+        <v>155.9554685338785</v>
+      </c>
+      <c r="F83" s="94" t="n">
+        <v>-5.998367304414813</v>
+      </c>
+      <c r="G83" s="96" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE ASSUMPTION</t>
         </is>
@@ -4545,10 +5281,10 @@
           <t>Frontier + long-rollout RL</t>
         </is>
       </c>
-      <c r="B84" s="76" t="n">
+      <c r="B84" s="91" t="n">
         <v>12.08050561742532</v>
       </c>
-      <c r="C84" s="77" t="n">
+      <c r="C84" s="92" t="n">
         <v>0.08277799221893223</v>
       </c>
       <c r="D84" s="24" t="inlineStr">
@@ -4556,13 +5292,13 @@
           <t>8k: 30% tok -&gt; 2% cost  64k: 20% tok -&gt; 5% cost  256k: 30% tok -&gt; 26% cost  1024k: 20% tok -&gt; 67% cost</t>
         </is>
       </c>
-      <c r="E84" s="78" t="n">
-        <v>154.784305013845</v>
-      </c>
-      <c r="F84" s="79" t="n">
-        <v>-5.765907541977811</v>
-      </c>
-      <c r="G84" s="81" t="inlineStr">
+      <c r="E84" s="93" t="n">
+        <v>156.09876278548</v>
+      </c>
+      <c r="F84" s="94" t="n">
+        <v>-5.855073052813339</v>
+      </c>
+      <c r="G84" s="96" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE ASSUMPTION</t>
         </is>
@@ -4583,44 +5319,44 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="66" t="inlineStr">
+      <c r="A90" s="81" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="B90" s="66" t="inlineStr">
+      <c r="B90" s="81" t="inlineStr">
         <is>
           <t>Transformer ms</t>
         </is>
       </c>
-      <c r="C90" s="66" t="inlineStr">
+      <c r="C90" s="81" t="inlineStr">
         <is>
           <t>bAttention ms</t>
         </is>
       </c>
-      <c r="D90" s="66" t="inlineStr">
+      <c r="D90" s="81" t="inlineStr">
         <is>
           <t>TF / bAttention</t>
         </is>
       </c>
-      <c r="E90" s="66" t="inlineStr"/>
-      <c r="F90" s="66" t="inlineStr">
+      <c r="E90" s="81" t="inlineStr"/>
+      <c r="F90" s="81" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="67" t="n">
+      <c r="A91" s="82" t="n">
         <v>2048</v>
       </c>
-      <c r="B91" s="39" t="n">
+      <c r="B91" s="48" t="n">
         <v>111.229</v>
       </c>
-      <c r="C91" s="36" t="n">
+      <c r="C91" s="44" t="n">
         <v>663.1130000000001</v>
       </c>
-      <c r="D91" s="76" t="n">
+      <c r="D91" s="91" t="n">
         <v>0.16773762541226</v>
       </c>
       <c r="F91" s="24" t="inlineStr">
@@ -4630,16 +5366,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="67" t="n">
+      <c r="A92" s="82" t="n">
         <v>4096</v>
       </c>
-      <c r="B92" s="39" t="n">
+      <c r="B92" s="48" t="n">
         <v>125.091</v>
       </c>
-      <c r="C92" s="36" t="n">
+      <c r="C92" s="44" t="n">
         <v>662.751</v>
       </c>
-      <c r="D92" s="76" t="n">
+      <c r="D92" s="91" t="n">
         <v>0.1887450943114382</v>
       </c>
       <c r="F92" s="24" t="inlineStr">
@@ -4649,16 +5385,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="67" t="n">
+      <c r="A93" s="82" t="n">
         <v>8192</v>
       </c>
-      <c r="B93" s="39" t="n">
+      <c r="B93" s="48" t="n">
         <v>153.085</v>
       </c>
-      <c r="C93" s="36" t="n">
+      <c r="C93" s="44" t="n">
         <v>663.327</v>
       </c>
-      <c r="D93" s="76" t="n">
+      <c r="D93" s="91" t="n">
         <v>0.2307836104967836</v>
       </c>
       <c r="F93" s="24" t="inlineStr">
@@ -4668,16 +5404,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="67" t="n">
+      <c r="A94" s="82" t="n">
         <v>16384</v>
       </c>
-      <c r="B94" s="39" t="n">
+      <c r="B94" s="48" t="n">
         <v>204.919</v>
       </c>
-      <c r="C94" s="36" t="n">
+      <c r="C94" s="44" t="n">
         <v>663.202</v>
       </c>
-      <c r="D94" s="76" t="n">
+      <c r="D94" s="91" t="n">
         <v>0.3089842913622094</v>
       </c>
       <c r="F94" s="24" t="inlineStr">
@@ -4687,16 +5423,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="67" t="n">
+      <c r="A95" s="82" t="n">
         <v>32768</v>
       </c>
-      <c r="B95" s="39" t="n">
+      <c r="B95" s="48" t="n">
         <v>309.886</v>
       </c>
-      <c r="C95" s="36" t="n">
+      <c r="C95" s="44" t="n">
         <v>662.6180000000001</v>
       </c>
-      <c r="D95" s="76" t="n">
+      <c r="D95" s="91" t="n">
         <v>0.4676691547769605</v>
       </c>
       <c r="F95" s="24" t="inlineStr">
@@ -4706,16 +5442,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="67" t="n">
+      <c r="A96" s="82" t="n">
         <v>65536</v>
       </c>
-      <c r="B96" s="39" t="n">
+      <c r="B96" s="48" t="n">
         <v>520.986</v>
       </c>
-      <c r="C96" s="36" t="n">
+      <c r="C96" s="44" t="n">
         <v>663.199</v>
       </c>
-      <c r="D96" s="76" t="n">
+      <c r="D96" s="91" t="n">
         <v>0.7855651169558459</v>
       </c>
       <c r="F96" s="24" t="inlineStr">
@@ -4725,81 +5461,81 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="67" t="n">
+      <c r="A97" s="82" t="n">
         <v>131072</v>
       </c>
-      <c r="B97" s="39" t="n">
+      <c r="B97" s="48" t="n">
         <v>969.79</v>
       </c>
-      <c r="C97" s="36" t="n">
+      <c r="C97" s="44" t="n">
         <v>753.457</v>
       </c>
-      <c r="D97" s="76" t="n">
+      <c r="D97" s="91" t="n">
         <v>1.287120565606265</v>
       </c>
       <c r="F97" s="24" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="67" t="n">
+      <c r="A98" s="82" t="n">
         <v>262144</v>
       </c>
-      <c r="B98" s="39" t="n">
+      <c r="B98" s="48" t="n">
         <v>1889.616</v>
       </c>
-      <c r="C98" s="36" t="n">
+      <c r="C98" s="44" t="n">
         <v>938.175</v>
       </c>
-      <c r="D98" s="76" t="n">
+      <c r="D98" s="91" t="n">
         <v>2.014140219042289</v>
       </c>
       <c r="F98" s="24" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="67" t="n">
+      <c r="A99" s="82" t="n">
         <v>524288</v>
       </c>
-      <c r="B99" s="39" t="n">
+      <c r="B99" s="48" t="n">
         <v>3718.717</v>
       </c>
-      <c r="C99" s="36" t="n">
+      <c r="C99" s="44" t="n">
         <v>1308.837</v>
       </c>
-      <c r="D99" s="76" t="n">
+      <c r="D99" s="91" t="n">
         <v>2.841237678947035</v>
       </c>
       <c r="F99" s="24" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="34" t="inlineStr">
+      <c r="A101" s="42" t="inlineStr">
         <is>
           <t>Assumptions — one row each (MEASURED / PROJECTION / ASSUMPTION)</t>
         </is>
       </c>
-      <c r="B101" s="35" t="n"/>
-      <c r="C101" s="35" t="n"/>
-      <c r="D101" s="35" t="n"/>
-      <c r="E101" s="35" t="n"/>
-      <c r="F101" s="35" t="n"/>
+      <c r="B101" s="43" t="n"/>
+      <c r="C101" s="43" t="n"/>
+      <c r="D101" s="43" t="n"/>
+      <c r="E101" s="43" t="n"/>
+      <c r="F101" s="43" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="66" t="inlineStr">
+      <c r="A102" s="81" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B102" s="66" t="inlineStr">
+      <c r="B102" s="81" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C102" s="66" t="inlineStr"/>
-      <c r="D102" s="66" t="inlineStr"/>
-      <c r="E102" s="66" t="inlineStr">
+      <c r="C102" s="81" t="inlineStr"/>
+      <c r="D102" s="81" t="inlineStr"/>
+      <c r="E102" s="81" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F102" s="66" t="inlineStr">
+      <c r="F102" s="81" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4813,10 +5549,10 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>x793 = full-workload serving lever (decode 2.5 ms/token x 64 streams ESTIMATE, prefill at the BANKED x3.94) x the x4.22 FIT-DERIVED equal-quality ratio at trillion scale; Ceiling = same at the full x7.03 maturity factor (x816)</t>
-        </is>
-      </c>
-      <c r="E103" s="81" t="inlineStr">
+          <t>x1553 = full-workload serving lever (decode 2.5 ms/token x 64 streams ESTIMATE, prefill at the BANKED x3.94) x the x4.22 FIT-DERIVED equal-quality ratio at trillion scale; Ceiling = same at the full x7.03 maturity factor (x1611)</t>
+        </is>
+      </c>
+      <c r="E103" s="96" t="inlineStr">
         <is>
           <t>ESTIMATE x PROJECTION</t>
         </is>
@@ -4838,7 +5574,7 @@
           <t>sealed 2026-08-14 refit, 4 rungs per family (47M-663M params): the fits cross at 392M and bAttention then matches the transformer fit's quality on 84.2% of the params at 1B, 55.2% at 10B, 36.2% at 100B, 23.7% at 1T, 15.5% at 10T. The receipt's own words: 'a projection of the two fits, not a measurement'</t>
         </is>
       </c>
-      <c r="E104" s="81" t="inlineStr">
+      <c r="E104" s="96" t="inlineStr">
         <is>
           <t>PROJECTION</t>
         </is>
@@ -4860,7 +5596,7 @@
           <t>RE-BASED 2026-08-24: on one GH200, single layer, fwd+bwd, bf16, checkpointing off both arms, against a MODERN transformer block (24Q/4KV, head_dim 256, RoPE 64, gated attention), a bAttention step costs x1.72 MORE at T=2,048 (101.7 vs 59.3 ms/step) and x1.79 at T=8,192. It read x6.116 (400.4 ms) the same morning and x6.46 on the older d1536/27L fp16 601-step receipt. Fwd x1.82, bwd x2.35. Training is still excluded from the serving claim, but the gap is now a kernel-program line item with a funded gate, not a structural loss</t>
         </is>
       </c>
-      <c r="E105" s="80" t="inlineStr">
+      <c r="E105" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -4882,7 +5618,7 @@
           <t>x1.579 at T=2,048 (17,087.5 vs 10,823.6 MiB) and x1.567 at T=8,192, down from x2.829 the same morning. This is TRAINING peak memory and is NOT the mem_factor lever, which is SERVING state (O(1) internal state vs O(T) KV cache) and is unaffected. It is not an input to the cost model; it caps per-GPU batch density</t>
         </is>
       </c>
-      <c r="E106" s="80" t="inlineStr">
+      <c r="E106" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -4904,7 +5640,7 @@
           <t>the funded 8k-win gate is a T=8,192 step at or below 83.08 ms, i.e. x1.786 still to remove (44% of the step). Named levers: recompute removal ~-12.8 ms; backward-fold + occupancy redesign (~3x headroom in the dominant fused kernel); copies elimination (24.8% of the step). Memory target x0.88 (parity or below). the model = the MEASURED x3.936 already banked x this x1.786 target</t>
         </is>
       </c>
-      <c r="E107" s="81" t="inlineStr">
+      <c r="E107" s="96" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
@@ -4926,7 +5662,7 @@
           <t>at matched tokens/step, 2k -&gt; 8k (4x context): our step grows x1.000, the transformer's x1.319, so the ratio decays x0.758 per 4x. The equal-token B4/T32,768 ~parity cell is RETIRED 2026-08-25 as a B4 occupancy artifact (it shared the retired growth residual); the flat per-token model puts the crossover at a PROJECTED T~13,000 (the model, 2026-08-29 anchor). Holding the old x0.802 decay constant instead would say x1.43 at 32k and a crossover near T~310,000 - that is the CONSERVATIVE extrapolation, because the transformer's quadratic attention term makes its per-4x growth rise with context while ours stays flat</t>
         </is>
       </c>
-      <c r="E108" s="81" t="inlineStr">
+      <c r="E108" s="96" t="inlineStr">
         <is>
           <t>MEASURED (2 ratio points) + PROJECTION</t>
         </is>
@@ -4948,7 +5684,7 @@
           <t>quoting one context for all of training is the pessimistic corner, and it was this model's old implicit assumption. Cost-weighted over a curriculum the training term flips from a DRAG to a CONTRIBUTOR: x0.583 at 100% 2k, x2.22 at a modern 8k/64k/256k mix, x7.74 long-context-heavy, x12.08 with long RL rollouts. The mechanism: our per-token cost is FLAT in context and the transformer's GROWS, so long-context tokens dominate its bill as a token minority — 10% of tokens at 262k is 47% of its training cost. r(T) is MEASURED at 2k/8k and MODELED beyond; the curriculum SHARES are ILLUSTRATIVE and exposed as knobs (this repo carries no citation for any lab's recipe)</t>
         </is>
       </c>
-      <c r="E109" s="81" t="inlineStr">
+      <c r="E109" s="96" t="inlineStr">
         <is>
           <t>MEASURED r(T) + ILLUSTRATIVE mix</t>
         </is>
@@ -4970,7 +5706,7 @@
           <t>at 262k+ the transformer additionally pays sequence-parallelism and activation-memory costs that an O(1) internal state does not: its KV grows at 156 KB per token of context per stream, which is what forces sharding, ring/Ulysses attention and their communication overhead. Our own measurement shows the asymmetry in the small: peak training memory grew only x0.993 relative to the transformer's from 2k to 8k (x1.579 -&gt; x1.567), i.e. the ratio is FLAT-to-falling in context while the absolute gap the transformer must shard grows. NOT in the cost model — the training advantage above counts FLOPs/step-time only, so the direction of this omission is CONSERVATIVE (it understates us at long context). Quantifying it needs a multi-GPU long-context training receipt we do not have</t>
         </is>
       </c>
-      <c r="E110" s="81" t="inlineStr">
+      <c r="E110" s="96" t="inlineStr">
         <is>
           <t>DIRECTIONAL — measured components, not a costed lever</t>
         </is>
@@ -4992,7 +5728,7 @@
           <t>$2.50 (H100 rent, neocloud/committed mid; ladder 2.00-3.50)</t>
         </is>
       </c>
-      <c r="E111" s="81" t="inlineStr">
+      <c r="E111" s="96" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
@@ -5014,7 +5750,7 @@
           <t>85%</t>
         </is>
       </c>
-      <c r="E112" s="81" t="inlineStr">
+      <c r="E112" s="96" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
@@ -5036,7 +5772,7 @@
           <t>headline quoted at 262k (a measured decode cell); table sweeps 4k-1M. The decode lever crosses 1 at ~29,800 tokens and BELOW that the transformer serves more tokens per GPU-second than we do — stated on every surface</t>
         </is>
       </c>
-      <c r="E113" s="81" t="inlineStr">
+      <c r="E113" s="96" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
@@ -5058,7 +5794,7 @@
           <t>per generated token at ONE stream the transformer is AHEAD of us at 64k context — 4.92 vs 5.74 GPU-busy per token. The lever is that it cannot hold many long-context streams: it re-reads its whole KV cache per emitted token, so its aggregate throughput falls as 1/context while ours is flat. Measured: 1 stream at 262k (2 OOM — an exact ceiling) and 8 streams at 32k (16 OOM, so that ceiling is only bracketed at 8-15 and the 32k cell is a bounded x0.97-1.14, near parity) against 64 of ours in 1.62 GB</t>
         </is>
       </c>
-      <c r="E114" s="80" t="inlineStr">
+      <c r="E114" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5080,7 +5816,7 @@
           <t>NOT GRANTED by default since the 2026-08-14 re-base: the headline runs on the measured cells, in which neither family's decode is optimised (ours ran the unoptimised per-step path at 9.5% GPU-busy while the transformer sat at 95.6%). Setting tf_kv_compression=8.0 grants it paged attention + KV quantization, divides our decode lever by 8 and puts the TRANSFORMER ahead at 64k — reported, not hidden</t>
         </is>
       </c>
-      <c r="E115" s="81" t="inlineStr">
+      <c r="E115" s="96" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
@@ -5102,7 +5838,7 @@
           <t>562 tok/s/GPU (4,497/box): 64 concurrent 262,144-token streams on one GPU, context-flat 32k-262k (-4.0%). The 64-stream cell is a grid cap, not a ceiling — 1.62 GB of state on a 96 GB card at 9.5% GPU-busy — so it is a LOWER bound. Supersedes a 349,880 tok/s/box figure measured on the h-carry-only proxy</t>
         </is>
       </c>
-      <c r="E116" s="80" t="inlineStr">
+      <c r="E116" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5124,7 +5860,7 @@
           <t>25.4 MB/stream, the FULL internal cell (h + M memory), 24.2 MiB measured, context-flat. The 0.15 MB figure previously quoted was an h-carry-only proxy with no M memory and is retired as a headline</t>
         </is>
       </c>
-      <c r="E117" s="80" t="inlineStr">
+      <c r="E117" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5146,7 +5882,7 @@
           <t>197 KB per token of context per stream as reserved end-to-end (51.5 GB for one 262,144-token stream; the linear KV fit alone is 156 KB/token, the rest is workspace) — a 2nd stream OOMs a 96 GB card, and 16 streams OOM it at 32,768 tokens. Its retired 88.5 per-token decode cost was inflated by a growing-KV re-planning harness artifact; the traced figure is 14.92 GPU-busy at 262k</t>
         </is>
       </c>
-      <c r="E118" s="80" t="inlineStr">
+      <c r="E118" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5168,7 +5904,7 @@
           <t>x5.15 (bAttention, fwd+bwd) vs x3.70 (transformer Ulysses best, forward-only) at matched 16-in-flight load -&gt; x1.39; x6.27 at 256 in flight -&gt; x1.70</t>
         </is>
       </c>
-      <c r="E119" s="80" t="inlineStr">
+      <c r="E119" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5190,7 +5926,7 @@
           <t>64k-token sequence: 30.9 GB (fits 1 GPU) vs OOM at 78.4 GB attempted; pipeline stage 9.05 GB flat vs GPipe 43.3 GB</t>
         </is>
       </c>
-      <c r="E120" s="80" t="inlineStr">
+      <c r="E120" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5212,7 +5948,7 @@
           <t>cross-family prefill, bf16, 1xH100, parameter counts exactly matched, block scope (1 layer, batch 16): TF/bAttention 4.02 at d512/1M, 3.83 at d1024/1M, 2.01 at d2048/262k. Short context favours the transformer and is stated so. NOTE: measured on the PRE-CAMPAIGN kernels and not re-run since 2026-08-24, so the TODAY lever is conservative; the realized x3.936 sits in the model, not here</t>
         </is>
       </c>
-      <c r="E121" s="80" t="inlineStr">
+      <c r="E121" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5234,7 +5970,7 @@
           <t>the d2048/24-layer fp32 sweep gives 7.91 at 262k at full-model scope. No fp32 FlashAttention kernel exists, so that lane runs mem-efficient attention on the transformer and the owned arm is fp16 internally; params 16.7% apart. Full model in bf16 has not been run</t>
         </is>
       </c>
-      <c r="E122" s="81" t="inlineStr">
+      <c r="E122" s="96" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
@@ -5256,7 +5992,7 @@
           <t>same-arch GH200 gate at d1536: fp16 x1.185 step time and -17.5% peak memory, bf16 x1.171 and -20.6%; quality deltas +0.001 to +0.004 from the gate's smaller vehicle. Reported on its own; not an input to the compute lever</t>
         </is>
       </c>
-      <c r="E123" s="80" t="inlineStr">
+      <c r="E123" s="95" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
@@ -5278,7 +6014,7 @@
           <t>transformer needs x4.1 params [2.2-7.7] or x1.7 tokens [1.33-2.10, beta=0.28 assumption]; crossover N* ~321M = the top measured rung</t>
         </is>
       </c>
-      <c r="E124" s="81" t="inlineStr">
+      <c r="E124" s="96" t="inlineStr">
         <is>
           <t>PROJECTION</t>
         </is>
@@ -5300,7 +6036,7 @@
           <t>systems numbers are component-scope (bAttention d1536 fwd+bwd h-internal dynamics sub-block vs transformer d2048 forward-only layer); every speedup is vs the family's OWN 1-GPU baseline</t>
         </is>
       </c>
-      <c r="E125" s="81" t="inlineStr">
+      <c r="E125" s="96" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
@@ -5316,7 +6052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -5333,14 +6069,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>EVIDENCE — cost split, accelerator share, own-silicon TCO, filing data</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -5732,10 +6468,10 @@
           <t>memory share = 45%</t>
         </is>
       </c>
-      <c r="B27" s="33" t="n">
+      <c r="B27" s="39" t="n">
         <v>0.45</v>
       </c>
-      <c r="C27" s="65">
+      <c r="C27" s="61">
         <f>1/(B27/Inputs!$B$2+(1-B27)/Inputs!$B$3)</f>
         <v/>
       </c>
@@ -5751,10 +6487,10 @@
           <t>memory share = 50%</t>
         </is>
       </c>
-      <c r="B28" s="33" t="n">
+      <c r="B28" s="39" t="n">
         <v>0.5</v>
       </c>
-      <c r="C28" s="65">
+      <c r="C28" s="61">
         <f>1/(B28/Inputs!$B$2+(1-B28)/Inputs!$B$3)</f>
         <v/>
       </c>
@@ -5770,10 +6506,10 @@
           <t>memory share = 60%</t>
         </is>
       </c>
-      <c r="B29" s="33" t="n">
+      <c r="B29" s="39" t="n">
         <v>0.6</v>
       </c>
-      <c r="C29" s="65">
+      <c r="C29" s="61">
         <f>1/(B29/Inputs!$B$2+(1-B29)/Inputs!$B$3)</f>
         <v/>
       </c>
@@ -5789,10 +6525,10 @@
           <t>memory share = 70%</t>
         </is>
       </c>
-      <c r="B30" s="33" t="n">
+      <c r="B30" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="61">
         <f>1/(B30/Inputs!$B$2+(1-B30)/Inputs!$B$3)</f>
         <v/>
       </c>
@@ -5808,10 +6544,10 @@
           <t>memory share = 82%</t>
         </is>
       </c>
-      <c r="B31" s="33" t="n">
+      <c r="B31" s="39" t="n">
         <v>0.82</v>
       </c>
-      <c r="C31" s="65">
+      <c r="C31" s="61">
         <f>1/(B31/Inputs!$B$2+(1-B31)/Inputs!$B$3)</f>
         <v/>
       </c>
@@ -5826,7 +6562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -5852,14 +6588,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Engine: GPU cost ~60% memory / ~40% compute. RE-BASED 2026-09-01: TODAY (default): memory x100 + FLOPs x793 (full-workload serving lever — decode 2.5 ms/token x 64 streams ESTIMATE, prefill at the banked x3.936 — x equal-quality ratio x4.22 at 1T) -&gt; ~x154 cost-weighted (Inputs B20). CEILING: FLOPs x816 (prefill at the full x7.03 maturity factor = x3.936 measured x x1.786 target) -&gt; ~x154.</t>
+          <t>Engine: GPU cost ~60% memory / ~40% compute. Single scenario (2026-09-29): memory x100 + FLOPs x1,553 (inference throughput per GPU x368 at a 262k-token average context — decode 2.5 ms/token x 64 streams ESTIMATE, prefill at the banked x3.936 — x equal-quality ratio x4.22 at 1T) -&gt; ~x160 cost-weighted (Inputs B20). The front tabs price inference on whole GPUs instead (fleet shrinks by the smaller lever, x100).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Floored by the least-reduced part — at these levers that is MEMORY (/100), so the two scenarios land within rounding of each other. The pre-campaign family (x9.24 -&gt; ~20x / x28.2 -&gt; ~50x) is RETIRED 2026-09-01: measured on kernels that no longer exist.</t>
+          <t xml:space="preserve">  Floored by the least-reduced part — at these levers that is MEMORY (/100). The Today/Ceiling pair (retired 2026-09-29) and the pre-campaign family (x9.24 -&gt; ~20x) are no longer used.</t>
         </is>
       </c>
     </row>
@@ -5942,35 +6678,35 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>- Cost-weighted reduction ~x154 TODAY and ~x154 at the CEILING — memory-floored at /100; the levers differ ~3% but the reduction ~0.3%.</t>
+          <t>- Cost-weighted reduction ~x160 — memory-floored at /100.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>- Net AI FY25: 6 named firms spend ~$362B (capex+opex) vs ~$79B AI revenue = ~ -$283B/yr cash burn.</t>
+          <t>- Net AI FY25: 6 named firms spend ~$363B (capex+opex) vs ~$79B AI revenue = ~ -$284B/yr cash burn.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>- With our architecture: spend cut ~$161B -&gt; burn shrinks to ~ -$122B/yr (~44% of AI spend cut).</t>
+          <t>- With our architecture: spend cut ~$162B -&gt; burn shrinks to ~ -$122B/yr (~45% of AI spend cut).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>- Spend-cut value (named floor, 6% discount rate): FY25 ~$161B/yr (~$2.7T capitalized); FY26 r/r ~$380B/yr (~$6.3T). Ceiling: within rounding of Today (the cut saturates).</t>
+          <t>- Spend-cut value (named floor, 6% discount rate): FY25 ~$162B/yr (~$2.7T capitalized); FY26 ~$383B/yr (~$6.4T). The cut saturates: ~99% of the chip bill.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>- GLOBAL estimate (named ~80% of world AI capex): FY25 ~$3.3T, FY26 ~$7.9T capitalized. Clearly an estimate.</t>
+          <t>- GLOBAL estimate (named ~80% of world AI capex): FY25 ~$3.4T, FY26 ~$8.0T capitalized. Clearly an estimate.</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6765,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>- Multiplying the levers (100x * ~793x ~ 79,000x) is NOT physical: cost is additive (Amdahl), not multiplicative.</t>
+          <t>- Multiplying the levers (100x * ~1,553x) is NOT physical: cost is additive (Amdahl), not multiplicative.</t>
         </is>
       </c>
     </row>
@@ -8213,13 +8949,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8239,24 +8975,41 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Every dollar in this workbook comes from five levers. Each is shown with its value, how sure we are of it (MEASURED on our hardware runs, PROJECTED from measured trends, or an ESTIMATE / TARGET awaiting measurement), what it means, and which part of the AI bill it shrinks. Blue cells are linked to the technical Inputs tab; yellow cells are assumptions you can edit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>Every dollar in this workbook comes from five levers. Each is shown with its value, how sure we are of it (MEASURED on our hardware runs, PROJECTED from measured trends, or an ESTIMATE awaiting measurement), what it means, and which part of the AI bill it shrinks. Blue cells link to the Inputs tab (edit them there); yellow cells are assumptions you can edit here. ★ with an orange border = a high-impact input (see the What Matters tab). ◆ with a purple fill = a value that differs between the two scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Scenario (pick from the list)</t>
+          <t>◆ Scenario (pick from the list)</t>
         </is>
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Current kernels</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Today = the software kernels we have already built and measured. Optimized kernels = our funded kernel programme lands (a TARGET, not yet measured). The dollars differ by under 1%.</t>
+          <t>Current kernels = the software we have built and measured. Optimized kernels = our funded kernel programme lands (a TARGET). ONLY the purple ◆ cells differ between them (levers 3 and 5, columns D–E below; Inputs B24–B26). Everything else is shared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Average conversation length (context)</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>262k tokens</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Levers 4 and 5 are quoted at this context. Longer conversations favour Helarctos more.</t>
         </is>
       </c>
     </row>
@@ -8273,17 +9026,17 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active value</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>◆ Current kernels</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>Optimized kernels</t>
+          <t>◆ Optimized kernels</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
@@ -8310,20 +9063,22 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Smaller model for the same quality</t>
-        </is>
-      </c>
-      <c r="C7" s="22">
-        <f>IF(Scenario="Today",D7,E7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
+          <t>★ Smaller model for the same quality</t>
+        </is>
+      </c>
+      <c r="C7" s="32">
         <f>Inputs!$B$23</f>
         <v/>
       </c>
-      <c r="E7" s="21">
-        <f>Inputs!$B$23</f>
-        <v/>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
@@ -8353,16 +9108,18 @@
         </is>
       </c>
       <c r="C8" s="22">
-        <f>IF(Scenario="Today",D8,E8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="21">
-        <f>E7</f>
-        <v/>
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
@@ -8388,17 +9145,17 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Training speed per token (same model size)</t>
-        </is>
-      </c>
-      <c r="C9" s="22">
-        <f>IF(Scenario="Today",D9,E9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="31" t="n">
+          <t>◆ Training speed per token (same model size)</t>
+        </is>
+      </c>
+      <c r="C9" s="34">
+        <f>IF(Scenario="Optimized kernels",E9,D9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="35" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -8408,7 +9165,7 @@
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>At the same model size, Helarctos trains at roughly the same speed per token as a transformer, so we count no training speed-up. The training saving comes entirely from levers 1 and 2: a smaller model trained on fewer tokens. (Where Helarctos is much faster is inference — lever 5.)</t>
+          <t>At the same model size, Helarctos trains at roughly the same speed per token as a transformer, so we count no training speed-up in either scenario (enter a value under Optimized kernels if the kernel programme speeds training up). The training saving comes from levers 1 and 2: a smaller model trained on fewer tokens. (Where Helarctos is much faster is inference — lever 5.)</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -8425,20 +9182,22 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Memory per live conversation</t>
-        </is>
-      </c>
-      <c r="C10" s="32">
-        <f>IF(Scenario="Today",D10,E10)</f>
-        <v/>
-      </c>
-      <c r="D10" s="23">
+          <t>★ Memory per live conversation</t>
+        </is>
+      </c>
+      <c r="C10" s="36">
         <f>Inputs!$B$2</f>
         <v/>
       </c>
-      <c r="E10" s="23">
-        <f>Inputs!$B$2</f>
-        <v/>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
@@ -8464,19 +9223,19 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>More conversations served per GPU</t>
-        </is>
-      </c>
-      <c r="C11" s="22">
-        <f>IF(Scenario="Today",D11,E11)</f>
-        <v/>
-      </c>
-      <c r="D11" s="21">
-        <f>Inputs!$B$24/Inputs!$B$23</f>
-        <v/>
-      </c>
-      <c r="E11" s="21">
-        <f>Inputs!$B$25/Inputs!$B$23</f>
+          <t>◆★ More conversations served per GPU</t>
+        </is>
+      </c>
+      <c r="C11" s="37">
+        <f>IF(Scenario="Optimized kernels",E11,D11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="35">
+        <f>Inputs!$B$24</f>
+        <v/>
+      </c>
+      <c r="E11" s="35">
+        <f>Inputs!$B$25</f>
         <v/>
       </c>
       <c r="F11" s="24" t="inlineStr">
@@ -8486,7 +9245,7 @@
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Small per-conversation memory lets one GPU hold many long conversations at once (64 where a transformer fits 1–2 at 262k), and no growing cache is re-read for each new token. At the same model size: ~12× more tokens per GPU at an 8k-token average context, ~188× at 128k (used here), ~368× at 256k.</t>
+          <t>Small per-conversation memory lets one GPU hold many long conversations at once (64 where a transformer fits 1–2 at 262k), and no growing cache is re-read for each new token. At the same model size: ~12× more tokens per GPU at an 8k-token average context, ~188× at 128k, ~368× at 262k (used here).</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -8531,7 +9290,7 @@
           <t>Inference: memory needed per conversation falls by</t>
         </is>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="38">
         <f>MemoryLever</f>
         <v/>
       </c>
@@ -8616,7 +9375,7 @@
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="C22" s="33" t="n">
+      <c r="C22" s="39" t="n">
         <v>0.25</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -8631,7 +9390,7 @@
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="C23" s="33" t="n">
+      <c r="C23" s="39" t="n">
         <v>0.35</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -8646,7 +9405,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="39" t="n">
         <v>0.35</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -8661,7 +9420,7 @@
           <t>Meta</t>
         </is>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C25" s="39" t="n">
         <v>0.45</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -8676,7 +9435,7 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="C26" s="33" t="n">
+      <c r="C26" s="39" t="n">
         <v>0.55</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -8691,7 +9450,7 @@
           <t>SpaceX</t>
         </is>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C27" s="39" t="n">
         <v>0.5</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -8775,7 +9534,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="D22:H22"/>
@@ -8791,6 +9550,7 @@
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D5:H5"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="B34:H34"/>
@@ -8798,7 +9558,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Today,Optimized kernels"</formula1>
+      <formula1>"Current kernels,Optimized kernels"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8806,6 +9566,521 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B2545"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WHAT MATTERS — which inputs move the answer, and by how much</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Each row changes ONE input to a plausible low and high value, everything else at the defaults, and shows how the FY2026 saving ($375B/yr) moves. ★ marks inputs that swing it by $10B or more; those cells carry an orange border wherever they appear. Values were computed from the model at the default inputs when this workbook was built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Where to edit</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Low case</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>FY26 change</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>High case</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>FY26 change</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Accelerator share of servers</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>company tabs, row 6</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>−15%</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>-56.26114088809925</v>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="n">
+        <v>49.70541105765551</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>The GPU/TPU share of server spend. Same one-for-one effect. From chip and server teardowns (67–80%; a GB200 rack's GPUs are ~75–80% of its price).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Server share of AI capex</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>company tabs, row 5</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>−15%</t>
+        </is>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>-56.26114088809919</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="n">
+        <v>56.26114088809919</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>How much of each company's AI capex buys servers rather than buildings, power and networking. Helarctos shrinks the chip bill, so the dollars move one-for-one with it. CFO-disclosed for Microsoft and Alphabet; consistent with the 10-K property notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Smaller model for the same quality  (Helarctos lever)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Inputs B23 (lever 1)</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>-27.97081728933057</v>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>×6.4</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="n">
+        <v>4.630107479271089</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>The biggest Helarctos-specific assumption: it drives the whole training saving (smaller model × fewer tokens). A projection from models up to 663M parameters to trillion scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Conversations served per GPU  (Helarctos lever)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>Inputs B24/B25 (lever 5)</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>-26.18437230470289</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>×3,000</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>Only matters if it collapses. Inference GPUs are limited by memory (÷100) as long as this stays above ~×24 at the same model size; the estimate is ×368 at 262k.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Memory per conversation  (Helarctos lever)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Inputs B2 (lever 4)</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>÷10</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>-21.71463959598657</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>÷1,000</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="n">
+        <v>2.171463959598668</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>Sets how far inference GPUs shrink. Measured ×2,000 at 262k; ÷100 is our cap. It would fall toward ÷60 only if average conversations were ~8k tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Data-center share of capex</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>company tabs, row 4</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>−5%</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>-18.75371362936642</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>+5%</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>12.83675643943218</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>Share of capex that goes into data centres rather than offices and other assets. From the 10-K/10-Q property notes (93–98%; Amazon's AWS share 68–76%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="11" t="inlineStr"/>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Electricity rate</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Inputs B9</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>$0.05</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>-5.448206407663861</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>$0.12</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="n">
+        <v>7.2642752102185</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>Only changes the power part of the saving (~3% of the total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="11" t="inlineStr"/>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Training speed per token  (Helarctos lever)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Levers D9/E9 (lever 3)</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>×0.6</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="n">
+        <v>-5.406659527589568</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="n">
+        <v>4.054994645692204</v>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>Set to 1× (comparable at the same size). Small effect, because the smaller model already removes ~94% of training GPU-hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="11" t="inlineStr"/>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Wall power per GPU</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Inputs B8</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>1.5 kW</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="n">
+        <v>-5.053408841891212</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>3.0 kW</t>
+        </is>
+      </c>
+      <c r="G13" s="41" t="n">
+        <v>4.421732736654803</v>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>Only changes the power part of the saving (~3% of the total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="11" t="inlineStr"/>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Training share of the chip fleet</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Levers C22:C27</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>all 20%</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>3.10436229420543</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>all 60%</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="n">
+        <v>-4.020427173695225</v>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>Small effect: both fleets shrink by 94–99%, so moving spend between them barely changes the total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="11" t="inlineStr"/>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Memory share of GPU cost</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Inputs B4</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G15" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>No effect on the front tabs (GPUs are bought whole); under $1B on the technical Totals tab. Chip teardowns put HBM + packaging at ~64% of a B200's manufacturing cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CAPITALIZED VALUE ONLY</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>★ The discount rate (Inputs B6) doesn't change the annual saving, only its capitalized value: $9.4T at 4%, $6.3T at 6% (default), $3.8T at 10% (FY2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Takeaway: the answer is driven by how much these firms spend on chips (the share inputs) far more than by how large the Helarctos multiples are. The Helarctos levers only move it much if they fall far below today's values — e.g. a smaller-model advantage of ×2 instead of ×4.2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -8822,14 +10097,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Microsoft — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -8859,10 +10134,10 @@
           <t>Total capex ($B)</t>
         </is>
       </c>
-      <c r="B3" s="36" t="n">
+      <c r="B3" s="44" t="n">
         <v>88</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="45" t="n">
         <v>190</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -8874,13 +10149,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Infra / data-center share</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
+          <t>★ Infra / data-center share</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
         <v>0.97</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="46" t="n">
         <v>0.97</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -8892,13 +10167,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Server / short-lived share</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
+          <t>★ Server / short-lived share</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="46" t="n">
         <v>0.67</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -8910,13 +10185,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Accelerator share within servers</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
+          <t>★ Accelerator share within servers</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="46" t="n">
         <v>0.75</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -8931,7 +10206,7 @@
           <t>Market cap ($B, approx)</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
+      <c r="B7" s="47" t="n">
         <v>3700</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -8941,14 +10216,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>DERIVATION</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8956,11 +10231,11 @@
           <t>AI-infra capex ($B)</t>
         </is>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="48">
         <f>B3*B4</f>
         <v/>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="48">
         <f>C3*C4</f>
         <v/>
       </c>
@@ -8976,11 +10251,11 @@
           <t>Server bucket ($B)</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="48">
         <f>B10*B5</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="48">
         <f>C10*C5</f>
         <v/>
       </c>
@@ -8996,11 +10271,11 @@
           <t>ACCELERATOR capex ($B)</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="49">
         <f>B11*B6</f>
         <v/>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="49">
         <f>C11*C6</f>
         <v/>
       </c>
@@ -9031,14 +10306,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9046,11 +10321,11 @@
           <t>Fleet size (GPU-equiv)</t>
         </is>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="50">
         <f>B12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="50">
         <f>C12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
@@ -9066,11 +10341,11 @@
           <t>Total wall power (MW)</t>
         </is>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="50">
         <f>B16*Inputs!$B$8/1000</f>
         <v/>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="50">
         <f>C16*Inputs!$B$8/1000</f>
         <v/>
       </c>
@@ -9086,11 +10361,11 @@
           <t>Daily energy (MWh)</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="50">
         <f>B17*24</f>
         <v/>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="50">
         <f>C17*24</f>
         <v/>
       </c>
@@ -9102,11 +10377,11 @@
           <t>Daily all-in opex ($/day)</t>
         </is>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="50">
         <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="50">
         <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
@@ -9122,11 +10397,11 @@
           <t>Annual opex ($M)</t>
         </is>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="48">
         <f>B19*365/1000000</f>
         <v/>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="48">
         <f>C19*365/1000000</f>
         <v/>
       </c>
@@ -9138,25 +10413,25 @@
           <t>Lifetime opex ($B)</t>
         </is>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="51">
         <f>B20*Inputs!$B$11/1000</f>
         <v/>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="51">
         <f>C20*Inputs!$B$11/1000</f>
         <v/>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>EFFICIENT VERSION &amp; VALUE</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9164,11 +10439,11 @@
           <t>Efficient AI capex ($B)</t>
         </is>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="48">
         <f>B10-B25</f>
         <v/>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="48">
         <f>C10-C25</f>
         <v/>
       </c>
@@ -9184,11 +10459,11 @@
           <t>Capex avoided/yr ($B)</t>
         </is>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="48">
         <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="48">
         <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
@@ -9204,11 +10479,11 @@
           <t>Annual opex savings ($M)</t>
         </is>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="48">
         <f>B20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="48">
         <f>C20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
@@ -9220,11 +10495,11 @@
           <t>Sustained annual benefit ($B/yr)</t>
         </is>
       </c>
-      <c r="B27" s="43">
+      <c r="B27" s="52">
         <f>B25+B26/1000</f>
         <v/>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="52">
         <f>C25+C26/1000</f>
         <v/>
       </c>
@@ -9240,11 +10515,11 @@
           <t>Capitalized value ($B)</t>
         </is>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="53">
         <f>B27/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="53">
         <f>C27/Inputs!$B$6</f>
         <v/>
       </c>
@@ -9271,14 +10546,14 @@
       <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9286,10 +10561,10 @@
           <t>AI revenue ($B)</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="45" t="n">
         <v>50</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -9304,11 +10579,11 @@
           <t>AI capex ($B)</t>
         </is>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="48">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="48">
         <f>C10</f>
         <v/>
       </c>
@@ -9324,11 +10599,11 @@
           <t>AI opex ($B)</t>
         </is>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="48">
         <f>B20/1000</f>
         <v/>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="48">
         <f>C20/1000</f>
         <v/>
       </c>
@@ -9344,11 +10619,11 @@
           <t>Net AI NOW ($B)</t>
         </is>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="49">
         <f>B32-B33-B34</f>
         <v/>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="49">
         <f>C32-C33-C34</f>
         <v/>
       </c>
@@ -9364,11 +10639,11 @@
           <t>Spend cut, our arch ($B)</t>
         </is>
       </c>
-      <c r="B36" s="39">
+      <c r="B36" s="48">
         <f>B27</f>
         <v/>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="48">
         <f>C27</f>
         <v/>
       </c>
@@ -9384,11 +10659,11 @@
           <t>Net AI WITH our arch ($B)</t>
         </is>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="49">
         <f>B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="49">
         <f>C35+C36</f>
         <v/>
       </c>
@@ -9419,14 +10694,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>SOURCES &amp; REFERENCES</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -9434,7 +10709,7 @@
           <t>FY25 capex &gt;$88B incl leases; server life 2-6yr (FY25 10-K)</t>
         </is>
       </c>
-      <c r="B41" s="45" t="inlineStr">
+      <c r="B41" s="54" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/789019/000095017025100235/msft-20250630.htm</t>
         </is>
@@ -9446,7 +10721,7 @@
           <t>FY26 ~$190B guide; 'two-thirds' short-lived = GPUs+CPUs (Q3 FY26 call)</t>
         </is>
       </c>
-      <c r="B42" s="45" t="inlineStr">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>https://www.fool.com/earnings/call-transcripts/2026/04/29/microsoft-msft-q3-2026-earnings-transcript/</t>
         </is>
@@ -9458,7 +10733,7 @@
           <t>AI revenue $37B annual run-rate (Q3 FY26)</t>
         </is>
       </c>
-      <c r="B43" s="45" t="inlineStr">
+      <c r="B43" s="54" t="inlineStr">
         <is>
           <t>https://news.alphastreet.com/microsoft-msft-q3-fy2026-azure-hits-40-growth-as-ai-business-reaches-37-billion-run-rate/</t>
         </is>
@@ -9470,7 +10745,7 @@
           <t>~485k Hopper GPUs / ~$31B in 2024 (Omdia) - cross-checks accel capex</t>
         </is>
       </c>
-      <c r="B44" s="45" t="inlineStr">
+      <c r="B44" s="54" t="inlineStr">
         <is>
           <t>https://techcrunch.com/2024/12/18/microsoft-bought-nearly-500000-nvidia-hopper-chips-this-year/</t>
         </is>
@@ -9488,680 +10763,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId4"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>Alphabet — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>basis / source</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total capex ($B)</t>
-        </is>
-      </c>
-      <c r="B3" s="36" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="C3" s="37" t="n">
-        <v>185</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FY25 capex $91.4B [DISCLOSED]; FY26 $180-190B guide. 60% servers / 40% DC (CFO). Accel ~67% [BOM]. AI rev ESTIMATE (Cloud $70B run-rate, AI subset).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Infra / data-center share</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="C4" s="33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>FILING: P&amp;E note. Technical infrastructure +$61.8B vs office space +$2.9B and corporate +$1.9B in 2025 (10-K) -&gt; 93%; +$43.5B vs +$2.3B office in H1 2026 (10-Q) -&gt; 95%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Server / short-lived share</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C5" s="33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>CFO-disclosed (MSFT rose 50%-&gt;67%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Accelerator share within servers</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>from BOM teardowns (~67-80%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Market cap ($B, approx)</t>
-        </is>
-      </c>
-      <c r="B7" s="38" t="n">
-        <v>4250</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>approximate June 2026 market data -- edit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>DERIVATION</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI-infra capex ($B)</t>
-        </is>
-      </c>
-      <c r="B10" s="39">
-        <f>B3*B4</f>
-        <v/>
-      </c>
-      <c r="C10" s="39">
-        <f>C3*C4</f>
-        <v/>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>total x infra share</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Server bucket ($B)</t>
-        </is>
-      </c>
-      <c r="B11" s="39">
-        <f>B10*B5</f>
-        <v/>
-      </c>
-      <c r="C11" s="39">
-        <f>C10*C5</f>
-        <v/>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>infra x server share</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ACCELERATOR capex ($B)</t>
-        </is>
-      </c>
-      <c r="B12" s="40">
-        <f>B11*B6</f>
-        <v/>
-      </c>
-      <c r="C12" s="40">
-        <f>C11*C6</f>
-        <v/>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>server x accel share</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Accel % of total capex</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>B12/B3</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>C12/C3</f>
-        <v/>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>varies across companies</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet size (GPU-equiv)</t>
-        </is>
-      </c>
-      <c r="B16" s="41">
-        <f>B12*1000000000/Inputs!$B$7</f>
-        <v/>
-      </c>
-      <c r="C16" s="41">
-        <f>C12*1000000000/Inputs!$B$7</f>
-        <v/>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>accel capex / $ per GPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total wall power (MW)</t>
-        </is>
-      </c>
-      <c r="B17" s="41">
-        <f>B16*Inputs!$B$8/1000</f>
-        <v/>
-      </c>
-      <c r="C17" s="41">
-        <f>C16*Inputs!$B$8/1000</f>
-        <v/>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>GPUs x kW</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Daily energy (MWh)</t>
-        </is>
-      </c>
-      <c r="B18" s="41">
-        <f>B17*24</f>
-        <v/>
-      </c>
-      <c r="C18" s="41">
-        <f>C17*24</f>
-        <v/>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Daily all-in opex ($/day)</t>
-        </is>
-      </c>
-      <c r="B19" s="41">
-        <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
-        <v/>
-      </c>
-      <c r="C19" s="41">
-        <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
-        <v/>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>MWh x rate x (1+overhead)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Annual opex ($M)</t>
-        </is>
-      </c>
-      <c r="B20" s="39">
-        <f>B19*365/1000000</f>
-        <v/>
-      </c>
-      <c r="C20" s="39">
-        <f>C19*365/1000000</f>
-        <v/>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Lifetime opex ($B)</t>
-        </is>
-      </c>
-      <c r="B21" s="42">
-        <f>B20*Inputs!$B$11/1000</f>
-        <v/>
-      </c>
-      <c r="C21" s="42">
-        <f>C20*Inputs!$B$11/1000</f>
-        <v/>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>EFFICIENT VERSION &amp; VALUE</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Efficient AI capex ($B)</t>
-        </is>
-      </c>
-      <c r="B24" s="39">
-        <f>B10-B25</f>
-        <v/>
-      </c>
-      <c r="C24" s="39">
-        <f>C10-C25</f>
-        <v/>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>AI capex - avoided</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Capex avoided/yr ($B)</t>
-        </is>
-      </c>
-      <c r="B25" s="39">
-        <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
-        <v/>
-      </c>
-      <c r="C25" s="39">
-        <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
-        <v/>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>accel + (datacenter x dc-scale), all x (1-1/reduction)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Annual opex savings ($M)</t>
-        </is>
-      </c>
-      <c r="B26" s="39">
-        <f>B20*(1-1/Inputs!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C26" s="39">
-        <f>C20*(1-1/Inputs!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sustained annual benefit ($B/yr)</t>
-        </is>
-      </c>
-      <c r="B27" s="43">
-        <f>B25+B26/1000</f>
-        <v/>
-      </c>
-      <c r="C27" s="43">
-        <f>C25+C26/1000</f>
-        <v/>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>avoided + opex savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Capitalized value ($B)</t>
-        </is>
-      </c>
-      <c r="B28" s="44">
-        <f>B27/Inputs!$B$6</f>
-        <v/>
-      </c>
-      <c r="C28" s="44">
-        <f>C27/Inputs!$B$6</f>
-        <v/>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>benefit / discount rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>% of market cap</t>
-        </is>
-      </c>
-      <c r="B29" s="25">
-        <f>B28/$B$7</f>
-        <v/>
-      </c>
-      <c r="C29" s="25">
-        <f>C28/$B$7</f>
-        <v/>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AI revenue ($B)</t>
-        </is>
-      </c>
-      <c r="B32" s="37" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="37" t="n">
-        <v>40</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATE (see Methodology). MSFT $37B &amp; Amazon $15B run-rates disclosed; Google/Meta/SpaceX estimated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI capex ($B)</t>
-        </is>
-      </c>
-      <c r="B33" s="39">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="C33" s="39">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>AI-infra capex (full: accel + buildings + power + net)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI opex ($B)</t>
-        </is>
-      </c>
-      <c r="B34" s="39">
-        <f>B20/1000</f>
-        <v/>
-      </c>
-      <c r="C34" s="39">
-        <f>C20/1000</f>
-        <v/>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>annual power/operating</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Net AI NOW ($B)</t>
-        </is>
-      </c>
-      <c r="B35" s="40">
-        <f>B32-B33-B34</f>
-        <v/>
-      </c>
-      <c r="C35" s="40">
-        <f>C32-C33-C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>revenue - capex - opex (cash burn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Spend cut, our arch ($B)</t>
-        </is>
-      </c>
-      <c r="B36" s="39">
-        <f>B27</f>
-        <v/>
-      </c>
-      <c r="C36" s="39">
-        <f>C27</f>
-        <v/>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>accel capex avoided + opex saved</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Net AI WITH our arch ($B)</t>
-        </is>
-      </c>
-      <c r="B37" s="40">
-        <f>B35+B36</f>
-        <v/>
-      </c>
-      <c r="C37" s="40">
-        <f>C35+C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Net AI now + spend cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>% AI spend reduction</t>
-        </is>
-      </c>
-      <c r="B38" s="14">
-        <f>B36/(B33+B34)</f>
-        <v/>
-      </c>
-      <c r="C38" s="14">
-        <f>C36/(C33+C34)</f>
-        <v/>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>spend cut / total AI spend (accel-only; upside if DC scales)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; REFERENCES</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>FY25 capex $91.4B; CFO 60% servers / 40% DC+net (Q4'25 call)</t>
-        </is>
-      </c>
-      <c r="B41" s="45" t="inlineStr">
-        <is>
-          <t>https://www.fool.com/earnings/call-transcripts/2026/02/04/alphabet-googl-q4-2025-earnings-call-transcript/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>FY26 guide $180-190B (Q1'26)</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>https://www.cnbc.com/2026/04/29/alphabet-googl-q1-2026-earnings.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Server life 6yr; TPU at-cost TCO 20-50% below NVIDIA (SemiAnalysis)</t>
-        </is>
-      </c>
-      <c r="B43" s="45" t="inlineStr">
-        <is>
-          <t>https://newsletter.semianalysis.com/p/tpuv7-google-takes-a-swing-at-the</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B43:D43"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10184,14 +10785,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>Amazon — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>Alphabet — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
+        </is>
+      </c>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -10221,47 +10822,47 @@
           <t>Total capex ($B)</t>
         </is>
       </c>
-      <c r="B3" s="36" t="n">
-        <v>128.3</v>
-      </c>
-      <c r="C3" s="37" t="n">
-        <v>220</v>
+      <c r="B3" s="44" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="C3" s="45" t="n">
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FY25 cash capex $128.3B [DISCLOSED]; FY26 raised to ~$220B (Q2'26, 2026-07-30). AWS ~68-70% -&gt; strips fulfillment. Accel ~67% [BOM]. AI rev &gt;$15B AWS run-rate (Q1 FY26, Jassy).</t>
+          <t>FY25 capex $91.4B [DISCLOSED]; FY26 $180-190B guide. 60% servers / 40% DC (CFO). Accel ~67% [BOM]. AI rev ESTIMATE (Cloud $70B run-rate, AI subset).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Infra / data-center share</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="C4" s="33" t="n">
-        <v>0.76</v>
+          <t>★ Infra / data-center share</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>0.95</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FILING: segment note, AWS share of net P&amp;E additions. $96.5B of $142.4B in 2025 (10-K) -&gt; 68%; $90.1B of $118.6B in H1 2026 (10-Q) -&gt; 76%. Strips fulfillment/logistics.</t>
+          <t>FILING: P&amp;E note. Technical infrastructure +$61.8B vs office space +$2.9B and corporate +$1.9B in 2025 (10-K) -&gt; 93%; +$43.5B vs +$2.3B office in H1 2026 (10-Q) -&gt; 95%.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Server / short-lived share</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C5" s="33" t="n">
-        <v>0.65</v>
+          <t>★ Server / short-lived share</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>0.6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -10272,13 +10873,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Accelerator share within servers</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
+          <t>★ Accelerator share within servers</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="46" t="n">
         <v>0.67</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -10293,8 +10894,8 @@
           <t>Market cap ($B, approx)</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
-        <v>2830</v>
+      <c r="B7" s="47" t="n">
+        <v>4250</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -10303,14 +10904,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>DERIVATION</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10318,11 +10919,11 @@
           <t>AI-infra capex ($B)</t>
         </is>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="48">
         <f>B3*B4</f>
         <v/>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="48">
         <f>C3*C4</f>
         <v/>
       </c>
@@ -10338,11 +10939,11 @@
           <t>Server bucket ($B)</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="48">
         <f>B10*B5</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="48">
         <f>C10*C5</f>
         <v/>
       </c>
@@ -10358,11 +10959,11 @@
           <t>ACCELERATOR capex ($B)</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="49">
         <f>B11*B6</f>
         <v/>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="49">
         <f>C11*C6</f>
         <v/>
       </c>
@@ -10393,14 +10994,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10408,11 +11009,11 @@
           <t>Fleet size (GPU-equiv)</t>
         </is>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="50">
         <f>B12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="50">
         <f>C12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
@@ -10428,11 +11029,11 @@
           <t>Total wall power (MW)</t>
         </is>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="50">
         <f>B16*Inputs!$B$8/1000</f>
         <v/>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="50">
         <f>C16*Inputs!$B$8/1000</f>
         <v/>
       </c>
@@ -10448,11 +11049,11 @@
           <t>Daily energy (MWh)</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="50">
         <f>B17*24</f>
         <v/>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="50">
         <f>C17*24</f>
         <v/>
       </c>
@@ -10464,11 +11065,11 @@
           <t>Daily all-in opex ($/day)</t>
         </is>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="50">
         <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="50">
         <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
@@ -10484,11 +11085,11 @@
           <t>Annual opex ($M)</t>
         </is>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="48">
         <f>B19*365/1000000</f>
         <v/>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="48">
         <f>C19*365/1000000</f>
         <v/>
       </c>
@@ -10500,25 +11101,25 @@
           <t>Lifetime opex ($B)</t>
         </is>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="51">
         <f>B20*Inputs!$B$11/1000</f>
         <v/>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="51">
         <f>C20*Inputs!$B$11/1000</f>
         <v/>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>EFFICIENT VERSION &amp; VALUE</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10526,11 +11127,11 @@
           <t>Efficient AI capex ($B)</t>
         </is>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="48">
         <f>B10-B25</f>
         <v/>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="48">
         <f>C10-C25</f>
         <v/>
       </c>
@@ -10546,11 +11147,11 @@
           <t>Capex avoided/yr ($B)</t>
         </is>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="48">
         <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="48">
         <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
@@ -10566,11 +11167,11 @@
           <t>Annual opex savings ($M)</t>
         </is>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="48">
         <f>B20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="48">
         <f>C20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
@@ -10582,11 +11183,11 @@
           <t>Sustained annual benefit ($B/yr)</t>
         </is>
       </c>
-      <c r="B27" s="43">
+      <c r="B27" s="52">
         <f>B25+B26/1000</f>
         <v/>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="52">
         <f>C25+C26/1000</f>
         <v/>
       </c>
@@ -10602,11 +11203,11 @@
           <t>Capitalized value ($B)</t>
         </is>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="53">
         <f>B27/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="53">
         <f>C27/Inputs!$B$6</f>
         <v/>
       </c>
@@ -10633,14 +11234,14 @@
       <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10648,11 +11249,11 @@
           <t>AI revenue ($B)</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="C32" s="37" t="n">
-        <v>22</v>
+      <c r="B32" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="45" t="n">
+        <v>40</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -10666,11 +11267,11 @@
           <t>AI capex ($B)</t>
         </is>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="48">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="48">
         <f>C10</f>
         <v/>
       </c>
@@ -10686,11 +11287,11 @@
           <t>AI opex ($B)</t>
         </is>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="48">
         <f>B20/1000</f>
         <v/>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="48">
         <f>C20/1000</f>
         <v/>
       </c>
@@ -10706,11 +11307,11 @@
           <t>Net AI NOW ($B)</t>
         </is>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="49">
         <f>B32-B33-B34</f>
         <v/>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="49">
         <f>C32-C33-C34</f>
         <v/>
       </c>
@@ -10726,11 +11327,11 @@
           <t>Spend cut, our arch ($B)</t>
         </is>
       </c>
-      <c r="B36" s="39">
+      <c r="B36" s="48">
         <f>B27</f>
         <v/>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="48">
         <f>C27</f>
         <v/>
       </c>
@@ -10746,11 +11347,11 @@
           <t>Net AI WITH our arch ($B)</t>
         </is>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="49">
         <f>B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="49">
         <f>C35+C36</f>
         <v/>
       </c>
@@ -10781,48 +11382,48 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>SOURCES &amp; REFERENCES</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>FY25 cash capex $128.3B; AWS 67.8% of net P&amp;E adds; server life 6-&gt;5yr (FY25 10-K)</t>
-        </is>
-      </c>
-      <c r="B41" s="45" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1018724/000101872426000004/amzn-20251231.htm</t>
+          <t>FY25 capex $91.4B; CFO 60% servers / 40% DC+net (Q4'25 call)</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/earnings/call-transcripts/2026/02/04/alphabet-googl-q4-2025-earnings-call-transcript/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>~$200B 2026 capex, 'predominantly AWS' (Q4'25 call)</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>https://www.fool.com/earnings/call-transcripts/2026/02/05/amazon-amzn-q4-2025-earnings-call-transcript/</t>
+          <t>FY26 guide $180-190B (Q1'26)</t>
+        </is>
+      </c>
+      <c r="B42" s="54" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/04/29/alphabet-googl-q1-2026-earnings.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>AWS AI revenue &gt;$15B annual run-rate (Q1'26, Jassy)</t>
-        </is>
-      </c>
-      <c r="B43" s="45" t="inlineStr">
-        <is>
-          <t>https://www.bnnbloomberg.ca/business/artificial-intelligence/2026/04/09/amazon-cloud-units-ai-revenue-run-rate-exceeds-us15-billion-in-first-quarter-ceo-says/</t>
+          <t>Server life 6yr; TPU at-cost TCO 20-50% below NVIDIA (SemiAnalysis)</t>
+        </is>
+      </c>
+      <c r="B43" s="54" t="inlineStr">
+        <is>
+          <t>https://newsletter.semianalysis.com/p/tpuv7-google-takes-a-swing-at-the</t>
         </is>
       </c>
     </row>
@@ -10848,6 +11449,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>Amazon — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
+        </is>
+      </c>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>basis / source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total capex ($B)</t>
+        </is>
+      </c>
+      <c r="B3" s="44" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="C3" s="45" t="n">
+        <v>220</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FY25 cash capex $128.3B [DISCLOSED]; FY26 raised to ~$220B (Q2'26, 2026-07-30). AWS ~68-70% -&gt; strips fulfillment. Accel ~67% [BOM]. AI rev &gt;$15B AWS run-rate (Q1 FY26, Jassy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>★ Infra / data-center share</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>FILING: segment note, AWS share of net P&amp;E additions. $96.5B of $142.4B in 2025 (10-K) -&gt; 68%; $90.1B of $118.6B in H1 2026 (10-Q) -&gt; 76%. Strips fulfillment/logistics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>★ Server / short-lived share</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>CFO-disclosed (MSFT rose 50%-&gt;67%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>★ Accelerator share within servers</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>from BOM teardowns (~67-80%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Market cap ($B, approx)</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>2830</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>approximate June 2026 market data -- edit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>DERIVATION</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI-infra capex ($B)</t>
+        </is>
+      </c>
+      <c r="B10" s="48">
+        <f>B3*B4</f>
+        <v/>
+      </c>
+      <c r="C10" s="48">
+        <f>C3*C4</f>
+        <v/>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>total x infra share</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Server bucket ($B)</t>
+        </is>
+      </c>
+      <c r="B11" s="48">
+        <f>B10*B5</f>
+        <v/>
+      </c>
+      <c r="C11" s="48">
+        <f>C10*C5</f>
+        <v/>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>infra x server share</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ACCELERATOR capex ($B)</t>
+        </is>
+      </c>
+      <c r="B12" s="49">
+        <f>B11*B6</f>
+        <v/>
+      </c>
+      <c r="C12" s="49">
+        <f>C11*C6</f>
+        <v/>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>server x accel share</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Accel % of total capex</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>B12/B3</f>
+        <v/>
+      </c>
+      <c r="C13" s="14">
+        <f>C12/C3</f>
+        <v/>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>varies across companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet size (GPU-equiv)</t>
+        </is>
+      </c>
+      <c r="B16" s="50">
+        <f>B12*1000000000/Inputs!$B$7</f>
+        <v/>
+      </c>
+      <c r="C16" s="50">
+        <f>C12*1000000000/Inputs!$B$7</f>
+        <v/>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>accel capex / $ per GPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total wall power (MW)</t>
+        </is>
+      </c>
+      <c r="B17" s="50">
+        <f>B16*Inputs!$B$8/1000</f>
+        <v/>
+      </c>
+      <c r="C17" s="50">
+        <f>C16*Inputs!$B$8/1000</f>
+        <v/>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>GPUs x kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Daily energy (MWh)</t>
+        </is>
+      </c>
+      <c r="B18" s="50">
+        <f>B17*24</f>
+        <v/>
+      </c>
+      <c r="C18" s="50">
+        <f>C17*24</f>
+        <v/>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Daily all-in opex ($/day)</t>
+        </is>
+      </c>
+      <c r="B19" s="50">
+        <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
+        <v/>
+      </c>
+      <c r="C19" s="50">
+        <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>MWh x rate x (1+overhead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Annual opex ($M)</t>
+        </is>
+      </c>
+      <c r="B20" s="48">
+        <f>B19*365/1000000</f>
+        <v/>
+      </c>
+      <c r="C20" s="48">
+        <f>C19*365/1000000</f>
+        <v/>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lifetime opex ($B)</t>
+        </is>
+      </c>
+      <c r="B21" s="51">
+        <f>B20*Inputs!$B$11/1000</f>
+        <v/>
+      </c>
+      <c r="C21" s="51">
+        <f>C20*Inputs!$B$11/1000</f>
+        <v/>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>EFFICIENT VERSION &amp; VALUE</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Efficient AI capex ($B)</t>
+        </is>
+      </c>
+      <c r="B24" s="48">
+        <f>B10-B25</f>
+        <v/>
+      </c>
+      <c r="C24" s="48">
+        <f>C10-C25</f>
+        <v/>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>AI capex - avoided</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Capex avoided/yr ($B)</t>
+        </is>
+      </c>
+      <c r="B25" s="48">
+        <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
+        <v/>
+      </c>
+      <c r="C25" s="48">
+        <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
+        <v/>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>accel + (datacenter x dc-scale), all x (1-1/reduction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Annual opex savings ($M)</t>
+        </is>
+      </c>
+      <c r="B26" s="48">
+        <f>B20*(1-1/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="C26" s="48">
+        <f>C20*(1-1/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sustained annual benefit ($B/yr)</t>
+        </is>
+      </c>
+      <c r="B27" s="52">
+        <f>B25+B26/1000</f>
+        <v/>
+      </c>
+      <c r="C27" s="52">
+        <f>C25+C26/1000</f>
+        <v/>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>avoided + opex savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Capitalized value ($B)</t>
+        </is>
+      </c>
+      <c r="B28" s="53">
+        <f>B27/Inputs!$B$6</f>
+        <v/>
+      </c>
+      <c r="C28" s="53">
+        <f>C27/Inputs!$B$6</f>
+        <v/>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>benefit / discount rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>% of market cap</t>
+        </is>
+      </c>
+      <c r="B29" s="25">
+        <f>B28/$B$7</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>C28/$B$7</f>
+        <v/>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI revenue ($B)</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ESTIMATE (see Methodology). MSFT $37B &amp; Amazon $15B run-rates disclosed; Google/Meta/SpaceX estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI capex ($B)</t>
+        </is>
+      </c>
+      <c r="B33" s="48">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="C33" s="48">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>AI-infra capex (full: accel + buildings + power + net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI opex ($B)</t>
+        </is>
+      </c>
+      <c r="B34" s="48">
+        <f>B20/1000</f>
+        <v/>
+      </c>
+      <c r="C34" s="48">
+        <f>C20/1000</f>
+        <v/>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>annual power/operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Net AI NOW ($B)</t>
+        </is>
+      </c>
+      <c r="B35" s="49">
+        <f>B32-B33-B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="49">
+        <f>C32-C33-C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>revenue - capex - opex (cash burn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Spend cut, our arch ($B)</t>
+        </is>
+      </c>
+      <c r="B36" s="48">
+        <f>B27</f>
+        <v/>
+      </c>
+      <c r="C36" s="48">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>accel capex avoided + opex saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Net AI WITH our arch ($B)</t>
+        </is>
+      </c>
+      <c r="B37" s="49">
+        <f>B35+B36</f>
+        <v/>
+      </c>
+      <c r="C37" s="49">
+        <f>C35+C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Net AI now + spend cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>% AI spend reduction</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>B36/(B33+B34)</f>
+        <v/>
+      </c>
+      <c r="C38" s="14">
+        <f>C36/(C33+C34)</f>
+        <v/>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>spend cut / total AI spend (accel-only; upside if DC scales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; REFERENCES</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>FY25 cash capex $128.3B; AWS 67.8% of net P&amp;E adds; server life 6-&gt;5yr (FY25 10-K)</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1018724/000101872426000004/amzn-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>~$200B 2026 capex, 'predominantly AWS' (Q4'25 call)</t>
+        </is>
+      </c>
+      <c r="B42" s="54" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/earnings/call-transcripts/2026/02/05/amazon-amzn-q4-2025-earnings-call-transcript/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>AWS AI revenue &gt;$15B annual run-rate (Q1'26, Jassy)</t>
+        </is>
+      </c>
+      <c r="B43" s="54" t="inlineStr">
+        <is>
+          <t>https://www.bnnbloomberg.ca/business/artificial-intelligence/2026/04/09/amazon-cloud-units-ai-revenue-run-rate-exceeds-us15-billion-in-first-quarter-ceo-says/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B43:D43"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10858,14 +12133,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Meta — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -10895,10 +12170,10 @@
           <t>Total capex ($B)</t>
         </is>
       </c>
-      <c r="B3" s="36" t="n">
+      <c r="B3" s="44" t="n">
         <v>72.2</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="45" t="n">
         <v>137.5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -10910,13 +12185,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Infra / data-center share</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
+          <t>★ Infra / data-center share</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
         <v>0.95</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="46" t="n">
         <v>0.98</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -10928,13 +12203,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Server / short-lived share</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
+          <t>★ Server / short-lived share</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
         <v>0.65</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="46" t="n">
         <v>0.65</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -10946,13 +12221,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Accelerator share within servers</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
+          <t>★ Accelerator share within servers</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
         <v>0.74</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="46" t="n">
         <v>0.74</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -10967,7 +12242,7 @@
           <t>Market cap ($B, approx)</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
+      <c r="B7" s="47" t="n">
         <v>1490</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -10977,14 +12252,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>DERIVATION</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10992,11 +12267,11 @@
           <t>AI-infra capex ($B)</t>
         </is>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="48">
         <f>B3*B4</f>
         <v/>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="48">
         <f>C3*C4</f>
         <v/>
       </c>
@@ -11012,11 +12287,11 @@
           <t>Server bucket ($B)</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="48">
         <f>B10*B5</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="48">
         <f>C10*C5</f>
         <v/>
       </c>
@@ -11032,11 +12307,11 @@
           <t>ACCELERATOR capex ($B)</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="49">
         <f>B11*B6</f>
         <v/>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="49">
         <f>C11*C6</f>
         <v/>
       </c>
@@ -11067,14 +12342,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11082,11 +12357,11 @@
           <t>Fleet size (GPU-equiv)</t>
         </is>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="50">
         <f>B12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="50">
         <f>C12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
@@ -11102,11 +12377,11 @@
           <t>Total wall power (MW)</t>
         </is>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="50">
         <f>B16*Inputs!$B$8/1000</f>
         <v/>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="50">
         <f>C16*Inputs!$B$8/1000</f>
         <v/>
       </c>
@@ -11122,11 +12397,11 @@
           <t>Daily energy (MWh)</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="50">
         <f>B17*24</f>
         <v/>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="50">
         <f>C17*24</f>
         <v/>
       </c>
@@ -11138,11 +12413,11 @@
           <t>Daily all-in opex ($/day)</t>
         </is>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="50">
         <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="50">
         <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
@@ -11158,11 +12433,11 @@
           <t>Annual opex ($M)</t>
         </is>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="48">
         <f>B19*365/1000000</f>
         <v/>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="48">
         <f>C19*365/1000000</f>
         <v/>
       </c>
@@ -11174,25 +12449,25 @@
           <t>Lifetime opex ($B)</t>
         </is>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="51">
         <f>B20*Inputs!$B$11/1000</f>
         <v/>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="51">
         <f>C20*Inputs!$B$11/1000</f>
         <v/>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>EFFICIENT VERSION &amp; VALUE</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11200,11 +12475,11 @@
           <t>Efficient AI capex ($B)</t>
         </is>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="48">
         <f>B10-B25</f>
         <v/>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="48">
         <f>C10-C25</f>
         <v/>
       </c>
@@ -11220,11 +12495,11 @@
           <t>Capex avoided/yr ($B)</t>
         </is>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="48">
         <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="48">
         <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
@@ -11240,11 +12515,11 @@
           <t>Annual opex savings ($M)</t>
         </is>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="48">
         <f>B20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="48">
         <f>C20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
@@ -11256,11 +12531,11 @@
           <t>Sustained annual benefit ($B/yr)</t>
         </is>
       </c>
-      <c r="B27" s="43">
+      <c r="B27" s="52">
         <f>B25+B26/1000</f>
         <v/>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="52">
         <f>C25+C26/1000</f>
         <v/>
       </c>
@@ -11276,11 +12551,11 @@
           <t>Capitalized value ($B)</t>
         </is>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="53">
         <f>B27/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="53">
         <f>C27/Inputs!$B$6</f>
         <v/>
       </c>
@@ -11307,14 +12582,14 @@
       <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11322,10 +12597,10 @@
           <t>AI revenue ($B)</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="45" t="n">
         <v>8</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -11340,11 +12615,11 @@
           <t>AI capex ($B)</t>
         </is>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="48">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="48">
         <f>C10</f>
         <v/>
       </c>
@@ -11360,11 +12635,11 @@
           <t>AI opex ($B)</t>
         </is>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="48">
         <f>B20/1000</f>
         <v/>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="48">
         <f>C20/1000</f>
         <v/>
       </c>
@@ -11380,11 +12655,11 @@
           <t>Net AI NOW ($B)</t>
         </is>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="49">
         <f>B32-B33-B34</f>
         <v/>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="49">
         <f>C32-C33-C34</f>
         <v/>
       </c>
@@ -11400,11 +12675,11 @@
           <t>Spend cut, our arch ($B)</t>
         </is>
       </c>
-      <c r="B36" s="39">
+      <c r="B36" s="48">
         <f>B27</f>
         <v/>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="48">
         <f>C27</f>
         <v/>
       </c>
@@ -11420,11 +12695,11 @@
           <t>Net AI WITH our arch ($B)</t>
         </is>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="49">
         <f>B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="49">
         <f>C35+C36</f>
         <v/>
       </c>
@@ -11455,14 +12730,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>SOURCES &amp; REFERENCES</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -11470,7 +12745,7 @@
           <t>FY25 capex $72.2B incl finance leases (Q4/FY25 release)</t>
         </is>
       </c>
-      <c r="B41" s="45" t="inlineStr">
+      <c r="B41" s="54" t="inlineStr">
         <is>
           <t>https://investor.atmeta.com/investor-news/press-release-details/2026/Meta-Reports-Fourth-Quarter-and-Full-Year-2025-Results/default.aspx</t>
         </is>
@@ -11482,7 +12757,7 @@
           <t>FY26 $125-145B guide; raise driven by HBM pricing (Q1'26 call)</t>
         </is>
       </c>
-      <c r="B42" s="45" t="inlineStr">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>https://www.fool.com/earnings/call-transcripts/2026/04/29/meta-meta-q1-2026-earnings-call-transcript/</t>
         </is>
@@ -11494,7 +12769,7 @@
           <t>&gt;1.3M GPUs by end-2025 (Zuckerberg) - cross-checks accel capex</t>
         </is>
       </c>
-      <c r="B43" s="45" t="inlineStr">
+      <c r="B43" s="54" t="inlineStr">
         <is>
           <t>https://techcrunch.com/2025/01/24/mark-zuckerberg-says-meta-will-have-1-3m-gpus-for-ai-by-year-end/</t>
         </is>
@@ -11506,7 +12781,7 @@
           <t>Server life 5.5yr (-$2.9B depreciation)</t>
         </is>
       </c>
-      <c r="B44" s="45" t="inlineStr">
+      <c r="B44" s="54" t="inlineStr">
         <is>
           <t>https://www.thestack.technology/meta-extends-server-life-again-saving-it-2-9-billion/</t>
         </is>
@@ -11518,7 +12793,7 @@
           <t>~25% of capex to NVIDIA (Bloomberg) - accel-share basis</t>
         </is>
       </c>
-      <c r="B45" s="45" t="inlineStr">
+      <c r="B45" s="54" t="inlineStr">
         <is>
           <t>https://finance.yahoo.com/news/big-techs-spending-drove-nvidias-rise-154027146.html</t>
         </is>
@@ -11543,7 +12818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -11560,14 +12835,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Oracle — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -11597,10 +12872,10 @@
           <t>Total capex ($B)</t>
         </is>
       </c>
-      <c r="B3" s="36" t="n">
+      <c r="B3" s="44" t="n">
         <v>21.2</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="45" t="n">
         <v>55.7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -11612,13 +12887,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Infra / data-center share</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
+          <t>★ Infra / data-center share</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
         <v>0.85</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="46" t="n">
         <v>0.9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -11630,13 +12905,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Server / short-lived share</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
+          <t>★ Server / short-lived share</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="46" t="n">
         <v>0.75</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -11648,13 +12923,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Accelerator share within servers</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
+          <t>★ Accelerator share within servers</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="46" t="n">
         <v>0.7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -11669,7 +12944,7 @@
           <t>Market cap ($B, approx)</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
+      <c r="B7" s="47" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -11679,14 +12954,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>DERIVATION</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11694,11 +12969,11 @@
           <t>AI-infra capex ($B)</t>
         </is>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="48">
         <f>B3*B4</f>
         <v/>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="48">
         <f>C3*C4</f>
         <v/>
       </c>
@@ -11714,11 +12989,11 @@
           <t>Server bucket ($B)</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="48">
         <f>B10*B5</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="48">
         <f>C10*C5</f>
         <v/>
       </c>
@@ -11734,11 +13009,11 @@
           <t>ACCELERATOR capex ($B)</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="49">
         <f>B11*B6</f>
         <v/>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="49">
         <f>C11*C6</f>
         <v/>
       </c>
@@ -11769,14 +13044,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11784,11 +13059,11 @@
           <t>Fleet size (GPU-equiv)</t>
         </is>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="50">
         <f>B12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="50">
         <f>C12*1000000000/Inputs!$B$7</f>
         <v/>
       </c>
@@ -11804,11 +13079,11 @@
           <t>Total wall power (MW)</t>
         </is>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="50">
         <f>B16*Inputs!$B$8/1000</f>
         <v/>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="50">
         <f>C16*Inputs!$B$8/1000</f>
         <v/>
       </c>
@@ -11824,11 +13099,11 @@
           <t>Daily energy (MWh)</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="50">
         <f>B17*24</f>
         <v/>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="50">
         <f>C17*24</f>
         <v/>
       </c>
@@ -11840,11 +13115,11 @@
           <t>Daily all-in opex ($/day)</t>
         </is>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="50">
         <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="50">
         <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
         <v/>
       </c>
@@ -11860,11 +13135,11 @@
           <t>Annual opex ($M)</t>
         </is>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="48">
         <f>B19*365/1000000</f>
         <v/>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="48">
         <f>C19*365/1000000</f>
         <v/>
       </c>
@@ -11876,25 +13151,25 @@
           <t>Lifetime opex ($B)</t>
         </is>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="51">
         <f>B20*Inputs!$B$11/1000</f>
         <v/>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="51">
         <f>C20*Inputs!$B$11/1000</f>
         <v/>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>EFFICIENT VERSION &amp; VALUE</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11902,11 +13177,11 @@
           <t>Efficient AI capex ($B)</t>
         </is>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="48">
         <f>B10-B25</f>
         <v/>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="48">
         <f>C10-C25</f>
         <v/>
       </c>
@@ -11922,11 +13197,11 @@
           <t>Capex avoided/yr ($B)</t>
         </is>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="48">
         <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="48">
         <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
         <v/>
       </c>
@@ -11942,11 +13217,11 @@
           <t>Annual opex savings ($M)</t>
         </is>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="48">
         <f>B20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="48">
         <f>C20*(1-1/Inputs!$B$5)</f>
         <v/>
       </c>
@@ -11958,11 +13233,11 @@
           <t>Sustained annual benefit ($B/yr)</t>
         </is>
       </c>
-      <c r="B27" s="43">
+      <c r="B27" s="52">
         <f>B25+B26/1000</f>
         <v/>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="52">
         <f>C25+C26/1000</f>
         <v/>
       </c>
@@ -11978,11 +13253,11 @@
           <t>Capitalized value ($B)</t>
         </is>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="53">
         <f>B27/Inputs!$B$6</f>
         <v/>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="53">
         <f>C27/Inputs!$B$6</f>
         <v/>
       </c>
@@ -12009,14 +13284,14 @@
       <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12024,10 +13299,10 @@
           <t>AI revenue ($B)</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="45" t="n">
         <v>15</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -12042,11 +13317,11 @@
           <t>AI capex ($B)</t>
         </is>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="48">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="48">
         <f>C10</f>
         <v/>
       </c>
@@ -12062,11 +13337,11 @@
           <t>AI opex ($B)</t>
         </is>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="48">
         <f>B20/1000</f>
         <v/>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="48">
         <f>C20/1000</f>
         <v/>
       </c>
@@ -12082,11 +13357,11 @@
           <t>Net AI NOW ($B)</t>
         </is>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="49">
         <f>B32-B33-B34</f>
         <v/>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="49">
         <f>C32-C33-C34</f>
         <v/>
       </c>
@@ -12102,11 +13377,11 @@
           <t>Spend cut, our arch ($B)</t>
         </is>
       </c>
-      <c r="B36" s="39">
+      <c r="B36" s="48">
         <f>B27</f>
         <v/>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="48">
         <f>C27</f>
         <v/>
       </c>
@@ -12122,11 +13397,11 @@
           <t>Net AI WITH our arch ($B)</t>
         </is>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="49">
         <f>B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="49">
         <f>C35+C36</f>
         <v/>
       </c>
@@ -12157,14 +13432,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>SOURCES &amp; REFERENCES</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -12172,7 +13447,7 @@
           <t>FY25 capex $21.2B; FY26 ~$50B guide on $67B rev (CIO Dive)</t>
         </is>
       </c>
-      <c r="B41" s="45" t="inlineStr">
+      <c r="B41" s="54" t="inlineStr">
         <is>
           <t>https://www.ciodive.com/news/oracle-capex-spike-cloud-ai-data-center/807721/</t>
         </is>
@@ -12184,7 +13459,7 @@
           <t>OCI run-rate ~$27B exiting FY25; IaaS $3.0B Q4 +52%; RPO $138B (Q4 FY25)</t>
         </is>
       </c>
-      <c r="B42" s="45" t="inlineStr">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>https://futurumgroup.com/insights/oracle-delivers-q4-fy-2025-results-with-27-cloud-growth-rpo-hits-138-billion/</t>
         </is>
@@ -12196,7 +13471,7 @@
           <t>FY26 OCI +77% to ~$18B; RPO $523B +433% on AI deals (Q2 FY26)</t>
         </is>
       </c>
-      <c r="B43" s="45" t="inlineStr">
+      <c r="B43" s="54" t="inlineStr">
         <is>
           <t>https://futurumgroup.com/insights/oracle-q2-fy-2026-cloud-grows-capex-rises-for-ai-buildout/</t>
         </is>
@@ -12215,692 +13490,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>SpaceX — accelerator capex &amp; value (FY2025 actual + FY2026 estimate)</t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>basis / source</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total capex ($B)</t>
-        </is>
-      </c>
-      <c r="B3" s="36" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="C3" s="37" t="n">
-        <v>55</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FY25 S-1 AI capex $12.7B [DISCLOSED]; FY26 ~$55B EST from H1'26 DISCLOSED $23.5B (Q1 $7.7B, Q2 $15.8B; 82.7% of total capex) + company guiding capex roughly flat Q3/Q4. ~all accelerator (greenfield COLOSSUS I/II). AI rev ~0 today; Anthropic (up to $1.25B/mo) and Google (up to $920M/mo) compute deals ramp from 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Infra / data-center share</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>FILING: capex is the AI segment's own figure (S-1; Q2 2026 10-Q segment note, $23.6B in H1 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Server / short-lived share</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="C5" s="33" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>CFO-disclosed (MSFT rose 50%-&gt;67%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Accelerator share within servers</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>from BOM teardowns (~67-80%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Market cap ($B, approx)</t>
-        </is>
-      </c>
-      <c r="B7" s="38" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>approximate June 2026 market data -- edit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>DERIVATION</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI-infra capex ($B)</t>
-        </is>
-      </c>
-      <c r="B10" s="39">
-        <f>B3*B4</f>
-        <v/>
-      </c>
-      <c r="C10" s="39">
-        <f>C3*C4</f>
-        <v/>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>total x infra share</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Server bucket ($B)</t>
-        </is>
-      </c>
-      <c r="B11" s="39">
-        <f>B10*B5</f>
-        <v/>
-      </c>
-      <c r="C11" s="39">
-        <f>C10*C5</f>
-        <v/>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>infra x server share</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ACCELERATOR capex ($B)</t>
-        </is>
-      </c>
-      <c r="B12" s="40">
-        <f>B11*B6</f>
-        <v/>
-      </c>
-      <c r="C12" s="40">
-        <f>C11*C6</f>
-        <v/>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>server x accel share</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Accel % of total capex</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>B12/B3</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>C12/C3</f>
-        <v/>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>varies across companies</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>FLEET &amp; OPERATING COST (from accelerator capex)</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet size (GPU-equiv)</t>
-        </is>
-      </c>
-      <c r="B16" s="41">
-        <f>B12*1000000000/Inputs!$B$7</f>
-        <v/>
-      </c>
-      <c r="C16" s="41">
-        <f>C12*1000000000/Inputs!$B$7</f>
-        <v/>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>accel capex / $ per GPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total wall power (MW)</t>
-        </is>
-      </c>
-      <c r="B17" s="41">
-        <f>B16*Inputs!$B$8/1000</f>
-        <v/>
-      </c>
-      <c r="C17" s="41">
-        <f>C16*Inputs!$B$8/1000</f>
-        <v/>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>GPUs x kW</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Daily energy (MWh)</t>
-        </is>
-      </c>
-      <c r="B18" s="41">
-        <f>B17*24</f>
-        <v/>
-      </c>
-      <c r="C18" s="41">
-        <f>C17*24</f>
-        <v/>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Daily all-in opex ($/day)</t>
-        </is>
-      </c>
-      <c r="B19" s="41">
-        <f>B18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
-        <v/>
-      </c>
-      <c r="C19" s="41">
-        <f>C18*1000*Inputs!$B$9*(1+Inputs!$B$10)</f>
-        <v/>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>MWh x rate x (1+overhead)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Annual opex ($M)</t>
-        </is>
-      </c>
-      <c r="B20" s="39">
-        <f>B19*365/1000000</f>
-        <v/>
-      </c>
-      <c r="C20" s="39">
-        <f>C19*365/1000000</f>
-        <v/>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Lifetime opex ($B)</t>
-        </is>
-      </c>
-      <c r="B21" s="42">
-        <f>B20*Inputs!$B$11/1000</f>
-        <v/>
-      </c>
-      <c r="C21" s="42">
-        <f>C20*Inputs!$B$11/1000</f>
-        <v/>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>EFFICIENT VERSION &amp; VALUE</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Efficient AI capex ($B)</t>
-        </is>
-      </c>
-      <c r="B24" s="39">
-        <f>B10-B25</f>
-        <v/>
-      </c>
-      <c r="C24" s="39">
-        <f>C10-C25</f>
-        <v/>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>AI capex - avoided</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Capex avoided/yr ($B)</t>
-        </is>
-      </c>
-      <c r="B25" s="39">
-        <f>(B12+(B10-B12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
-        <v/>
-      </c>
-      <c r="C25" s="39">
-        <f>(C12+(C10-C12)*Inputs!$B$13)*(1-1/Inputs!$B$20)</f>
-        <v/>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>accel + (datacenter x dc-scale), all x (1-1/reduction)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Annual opex savings ($M)</t>
-        </is>
-      </c>
-      <c r="B26" s="39">
-        <f>B20*(1-1/Inputs!$B$5)</f>
-        <v/>
-      </c>
-      <c r="C26" s="39">
-        <f>C20*(1-1/Inputs!$B$5)</f>
-        <v/>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sustained annual benefit ($B/yr)</t>
-        </is>
-      </c>
-      <c r="B27" s="43">
-        <f>B25+B26/1000</f>
-        <v/>
-      </c>
-      <c r="C27" s="43">
-        <f>C25+C26/1000</f>
-        <v/>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>avoided + opex savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Capitalized value ($B)</t>
-        </is>
-      </c>
-      <c r="B28" s="44">
-        <f>B27/Inputs!$B$6</f>
-        <v/>
-      </c>
-      <c r="C28" s="44">
-        <f>C27/Inputs!$B$6</f>
-        <v/>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>benefit / discount rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>% of market cap</t>
-        </is>
-      </c>
-      <c r="B29" s="25">
-        <f>B28/$B$7</f>
-        <v/>
-      </c>
-      <c r="C29" s="25">
-        <f>C28/$B$7</f>
-        <v/>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>AI ECONOMICS (cash basis: AI revenue - AI capex - AI opex)</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AI revenue ($B)</t>
-        </is>
-      </c>
-      <c r="B32" s="37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C32" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>ESTIMATE (see Methodology). MSFT $37B &amp; Amazon $15B run-rates disclosed; Google/Meta/SpaceX estimated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI capex ($B)</t>
-        </is>
-      </c>
-      <c r="B33" s="39">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="C33" s="39">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>AI-infra capex (full: accel + buildings + power + net)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI opex ($B)</t>
-        </is>
-      </c>
-      <c r="B34" s="39">
-        <f>B20/1000</f>
-        <v/>
-      </c>
-      <c r="C34" s="39">
-        <f>C20/1000</f>
-        <v/>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>annual power/operating</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Net AI NOW ($B)</t>
-        </is>
-      </c>
-      <c r="B35" s="40">
-        <f>B32-B33-B34</f>
-        <v/>
-      </c>
-      <c r="C35" s="40">
-        <f>C32-C33-C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>revenue - capex - opex (cash burn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Spend cut, our arch ($B)</t>
-        </is>
-      </c>
-      <c r="B36" s="39">
-        <f>B27</f>
-        <v/>
-      </c>
-      <c r="C36" s="39">
-        <f>C27</f>
-        <v/>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>accel capex avoided + opex saved</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Net AI WITH our arch ($B)</t>
-        </is>
-      </c>
-      <c r="B37" s="40">
-        <f>B35+B36</f>
-        <v/>
-      </c>
-      <c r="C37" s="40">
-        <f>C35+C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Net AI now + spend cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>% AI spend reduction</t>
-        </is>
-      </c>
-      <c r="B38" s="14">
-        <f>B36/(B33+B34)</f>
-        <v/>
-      </c>
-      <c r="C38" s="14">
-        <f>C36/(C33+C34)</f>
-        <v/>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>spend cut / total AI spend (accel-only; upside if DC scales)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; REFERENCES</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>S-1 registration statement (SEC EDGAR)</t>
-        </is>
-      </c>
-      <c r="B41" s="45" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1181412/000162828026036936/spaceexplorationtechnologi.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>S-1 financials &amp; AI breakdown (Hargreaves Lansdown)</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>https://www.hl.co.uk/news/inside-spacexs-ipo-filing-revenue-starlink-ai-and-key-financials</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>$12.7B AI capex = ~60% of capex; COLOSSUS buildout (Investing.com)</t>
-        </is>
-      </c>
-      <c r="B43" s="45" t="inlineStr">
-        <is>
-          <t>https://www.investing.com/analysis/spacex-is-quietly-becoming-an-ai-compute-and-orbital-infrastructure-company-200681776</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>AI1 orbital data centers; Anthropic as compute customer (DCD)</t>
-        </is>
-      </c>
-      <c r="B44" s="45" t="inlineStr">
-        <is>
-          <t>https://www.datacenterdynamics.com/en/news/spacex-ipo-musks-firm-set-to-launch-first-orbital-data-center-ai1-satellites-in-2027-will-put-compute-on-starlink-craft/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B43:D43"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId4"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -630,20 +630,6 @@
               </a:ln>
             </spPr>
           </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="1BAF7A"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <numFmt formatCode="&quot;$&quot;#,##0&quot;B&quot;"/>
             <showLegendKey val="0"/>
@@ -654,12 +640,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Value Bridge'!$A$49:$A$52</f>
+              <f>'Value Bridge'!$A$49:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Value Bridge'!$F$49:$F$52</f>
+              <f>'Value Bridge'!$F$49:$F$51</f>
             </numRef>
           </val>
         </ser>
@@ -1260,7 +1246,7 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
-    <row r="16" ht="62" customHeight="1">
+    <row r="16" ht="92" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Training</t>
@@ -1279,7 +1265,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="62" customHeight="1">
+    <row r="17" ht="92" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Inference</t>
@@ -1294,7 +1280,7 @@
         <v/>
       </c>
       <c r="D17" s="3">
-        <f>"A transformer's memory grows with every token of every live conversation; Helarctos keeps a fixed-size state (÷"&amp;TEXT(MemoryLever,"0")&amp;" memory) and does "&amp;TEXT(ServeComputeLever,"0")&amp;"× less compute per token. A GPU is bought whole, so the fleet shrinks by whichever limit binds: "&amp;TEXT(ServeGPULever,"0")&amp;"× fewer inference GPUs, and their power."</f>
+        <f>"A transformer's memory grows with every token of every live conversation; Helarctos keeps a fixed-size state (÷"&amp;TEXT(MemoryLever,"0")&amp;" memory per conversation), so each GPU serves "&amp;TEXT(ServeComputeLever,"0")&amp;"× more tokens. A GPU is bought whole, so the fleet shrinks by whichever limit binds: "&amp;TEXT(ServeGPULever,"0")&amp;"× fewer inference GPUs, and their power."</f>
         <v/>
       </c>
     </row>
@@ -2818,13 +2804,13 @@
         <v>-965.3195453336799</v>
       </c>
       <c r="F14" s="57" t="n">
-        <v>574.1429873323519</v>
+        <v>573.6639462810871</v>
       </c>
       <c r="G14" s="57" t="n">
-        <v>-391.1765580013281</v>
+        <v>-391.6555990525928</v>
       </c>
       <c r="H14" s="58" t="n">
-        <v>0.4912161074175423</v>
+        <v>0.4908062571090175</v>
       </c>
     </row>
     <row r="16">
@@ -3190,7 +3176,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>B27 = inference throughput per GPU at a 262k-token average context for the active scenario (B26, picked on the Levers tab) x the equal-quality parameter ratio (B23). Edit B23-B25, or overtype this cell to pin the lever. See ServingTraining for the measured background.</t>
+          <t>B27 = inference throughput per GPU at a 262k-token average context for the active scenario (B26, picked on the Levers tab). Inference cost does not scale with model size, so the equal-quality ratio (B23) applies to training only. Edit B24-B25, or overtype this cell to pin the lever. See ServingTraining for the measured background.</t>
         </is>
       </c>
     </row>
@@ -3604,11 +3590,11 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Compute (FLOPs) lever = B23 x B26</t>
+          <t>Inference compute (FLOPs) lever = B26</t>
         </is>
       </c>
       <c r="B27" s="71">
-        <f>$B$23*$B$26</f>
+        <f>$B$26</f>
         <v/>
       </c>
       <c r="C27" t="inlineStr">
@@ -3800,12 +3786,12 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Compute lever (x)</t>
+          <t>◆ Inference lever, current kernels (x)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Throughput per GPU, same size (x)</t>
+          <t>◆ Inference lever, optimized kernels (x)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr"/>
@@ -3822,11 +3808,11 @@
       <c r="C14" s="25" t="n">
         <v>0.05208995366081766</v>
       </c>
-      <c r="D14" s="50" t="n">
-        <v>50.29665229131971</v>
+      <c r="D14" s="48" t="n">
+        <v>11.92287815199857</v>
       </c>
       <c r="E14" s="48" t="n">
-        <v>11.92287815199857</v>
+        <v>12.20269551906716</v>
       </c>
     </row>
     <row r="15">
@@ -3841,11 +3827,11 @@
       <c r="C15" s="25" t="n">
         <v>0.05196631516233694</v>
       </c>
-      <c r="D15" s="50" t="n">
-        <v>200.6239377794075</v>
+      <c r="D15" s="48" t="n">
+        <v>47.55813072137281</v>
       </c>
       <c r="E15" s="48" t="n">
-        <v>47.55813072137281</v>
+        <v>48.67155861377862</v>
       </c>
     </row>
     <row r="16">
@@ -3860,11 +3846,11 @@
       <c r="C16" s="25" t="n">
         <v>0.06235575593664416</v>
       </c>
-      <c r="D16" s="50" t="n">
-        <v>793.2064858179596</v>
+      <c r="D16" s="48" t="n">
+        <v>188.0304920694428</v>
       </c>
       <c r="E16" s="48" t="n">
-        <v>188.0304920694428</v>
+        <v>193.3375983858266</v>
       </c>
     </row>
     <row r="17">
@@ -3879,11 +3865,11 @@
       <c r="C17" s="25" t="n">
         <v>0.08221381175542121</v>
       </c>
-      <c r="D17" s="50" t="n">
-        <v>1552.723400990788</v>
+      <c r="D17" s="48" t="n">
+        <v>368.0748334211694</v>
       </c>
       <c r="E17" s="48" t="n">
-        <v>368.0748334211694</v>
+        <v>381.8963339071965</v>
       </c>
     </row>
     <row r="19">
@@ -5209,7 +5195,7 @@
         <v>151.049323023638</v>
       </c>
       <c r="F81" s="94" t="n">
-        <v>-10.90451281465531</v>
+        <v>-10.76938526370006</v>
       </c>
       <c r="G81" s="95" t="inlineStr">
         <is>
@@ -5238,7 +5224,7 @@
         <v>154.9628350868998</v>
       </c>
       <c r="F82" s="94" t="n">
-        <v>-6.991000751393557</v>
+        <v>-6.85587320043831</v>
       </c>
       <c r="G82" s="96" t="inlineStr">
         <is>
@@ -5267,7 +5253,7 @@
         <v>155.9554685338785</v>
       </c>
       <c r="F83" s="94" t="n">
-        <v>-5.998367304414813</v>
+        <v>-5.863239753459567</v>
       </c>
       <c r="G83" s="96" t="inlineStr">
         <is>
@@ -5296,7 +5282,7 @@
         <v>156.09876278548</v>
       </c>
       <c r="F84" s="94" t="n">
-        <v>-5.855073052813339</v>
+        <v>-5.719945501858092</v>
       </c>
       <c r="G84" s="96" t="inlineStr">
         <is>
@@ -6588,7 +6574,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Engine: GPU cost ~60% memory / ~40% compute. Single scenario (2026-09-29): memory x100 + FLOPs x1,553 (inference throughput per GPU x368 at a 262k-token average context — decode 2.5 ms/token x 64 streams ESTIMATE, prefill at the banked x3.936 — x equal-quality ratio x4.22 at 1T) -&gt; ~x160 cost-weighted (Inputs B20). The front tabs price inference on whole GPUs instead (fleet shrinks by the smaller lever, x100).</t>
+          <t>Engine: GPU cost ~60% memory / ~40% compute. Single scenario (2026-09-29): memory x100 + inference compute x368 (throughput per GPU at a 262k-token average context; size-independent — decode 2.5 ms/token x 64 streams ESTIMATE, prefill at the banked x3.936 — x equal-quality ratio x4.22 at 1T) -&gt; ~x160 cost-weighted (Inputs B20). The front tabs price inference on whole GPUs instead (fleet shrinks by the smaller lever, x100).</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6664,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>- Cost-weighted reduction ~x160 — memory-floored at /100.</t>
+          <t>- Cost-weighted reduction ~x141 — memory-floored at /100.</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7272,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>smaller model × more conversations per GPU (levers 1 × 5)</t>
+          <t>many more conversations per GPU (lever 5)</t>
         </is>
       </c>
     </row>
@@ -7545,19 +7531,18 @@
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>Smaller model for the same quality (levers 1, 2)</t>
+          <t>Smaller model trained on fewer tokens — training (levers 1–3)</t>
         </is>
       </c>
       <c r="B50" s="21">
-        <f>SmallerModel^2</f>
+        <f>TrainLever</f>
         <v/>
       </c>
       <c r="C50" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="21">
-        <f>SmallerModel</f>
-        <v/>
+      <c r="D50" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="E50" s="25">
         <f>(D70*(1-1/B50)+E70*(1-1/MIN(C50,D50)))/B70</f>
@@ -7573,13 +7558,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>+ Fixed-size memory per conversation (lever 4)</t>
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>+ Fixed-size memory: many more conversations per GPU — inference (levers 4, 5)</t>
         </is>
       </c>
       <c r="B51" s="21">
-        <f>SmallerModel^2</f>
+        <f>TrainLever</f>
         <v/>
       </c>
       <c r="C51" s="23">
@@ -7587,7 +7572,7 @@
         <v/>
       </c>
       <c r="D51" s="21">
-        <f>SmallerModel</f>
+        <f>ServeComputeLever</f>
         <v/>
       </c>
       <c r="E51" s="25">
@@ -7603,41 +7588,10 @@
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>+ Many more conversations per GPU (lever 5)</t>
-        </is>
-      </c>
-      <c r="B52" s="21">
-        <f>TrainLever</f>
-        <v/>
-      </c>
-      <c r="C52" s="23">
-        <f>MemoryLever</f>
-        <v/>
-      </c>
-      <c r="D52" s="21">
-        <f>ServeComputeLever</f>
-        <v/>
-      </c>
-      <c r="E52" s="25">
-        <f>(D70*(1-1/B52)+E70*(1-1/MIN(C52,D52)))/B70</f>
-        <v/>
-      </c>
-      <c r="F52" s="18">
-        <f>E52*(B70+I70)</f>
-        <v/>
-      </c>
-      <c r="G52" s="26">
-        <f>F52-F51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="62" customHeight="1">
+    <row r="55" ht="48" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Read this as: the smaller model alone removes nearly all of the TRAINING bill (fewer parameters AND fewer tokens compound) but no inference GPUs — at long context a transformer's inference GPUs are full of memory (the growing KV cache), not busy computing, and a smaller model doesn't change that. Fixed-size memory unlocks inference, until compute becomes the limit; many more conversations per GPU lifts that limit. By then ~99% of the chip bill is gone: bigger multiples can't add much, because a cost can only fall to zero once. That is why this workbook reports dollars, not multiples. The order is the storyline; the end point does not depend on it.</t>
+          <t>Read this as: TRAINING savings come from the smaller model (fewer parameters AND fewer tokens compound, ~18× fewer GPU-hours). INFERENCE savings come from fixed-size memory, which lets each GPU hold many more long conversations — model size doesn't change inference cost. Each fleet then shrinks by ~94–99%: bigger multiples can't add much, because a cost can only fall to zero once. That is why this workbook reports dollars, not multiples.</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9009,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="78" customHeight="1">
+    <row r="7" ht="104" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>1</t>
@@ -9092,11 +9046,11 @@
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>Training and inference compute</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="78" customHeight="1">
+          <t>Training (inference cost doesn't depend on model size)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="104" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>2</t>
@@ -9137,7 +9091,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="78" customHeight="1">
+    <row r="9" ht="104" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>3</t>
@@ -9174,7 +9128,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="78" customHeight="1">
+    <row r="10" ht="104" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>4</t>
@@ -9215,7 +9169,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="78" customHeight="1">
+    <row r="11" ht="104" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>5</t>
@@ -9307,12 +9261,12 @@
         </is>
       </c>
       <c r="C16" s="22">
-        <f>SmallerModel*ServeThroughput</f>
+        <f>ServeThroughput</f>
         <v/>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>lever 1 × lever 5</t>
+          <t>lever 5 (inference cost doesn't depend on model size)</t>
         </is>
       </c>
     </row>
@@ -9766,33 +9720,33 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Conversations served per GPU  (Helarctos lever)</t>
+          <t>Memory per conversation  (Helarctos lever)</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Inputs B24/B25 (lever 5)</t>
+          <t>Inputs B2 (lever 4)</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>×2</t>
+          <t>÷10</t>
         </is>
       </c>
       <c r="E8" s="40" t="n">
-        <v>-26.18437230470289</v>
+        <v>-21.71463959598657</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>×3,000</t>
+          <t>÷1,000</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
-        <v>0</v>
+        <v>1.757227168894815</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>Only matters if it collapses. Inference GPUs are limited by memory (÷100) as long as this stays above ~×24 at the same model size; the estimate is ×368 at 262k.</t>
+          <t>Sets how far inference GPUs shrink. Measured ×2,000 at 262k; ÷100 is our cap. It would fall toward ÷60 only if average conversations were ~8k tokens.</t>
         </is>
       </c>
     </row>
@@ -9804,33 +9758,33 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Memory per conversation  (Helarctos lever)</t>
+          <t>Data-center share of capex</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>Inputs B2 (lever 4)</t>
+          <t>company tabs, row 4</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>÷10</t>
+          <t>−5%</t>
         </is>
       </c>
       <c r="E9" s="40" t="n">
-        <v>-21.71463959598657</v>
+        <v>-18.75371362936642</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>÷1,000</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="G9" s="40" t="n">
-        <v>2.171463959598668</v>
+        <v>12.83675643943218</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>Sets how far inference GPUs shrink. Measured ×2,000 at 262k; ÷100 is our cap. It would fall toward ÷60 only if average conversations were ~8k tokens.</t>
+          <t>Share of capex that goes into data centres rather than offices and other assets. From the 10-K/10-Q property notes (93–98%; Amazon's AWS share 68–76%).</t>
         </is>
       </c>
     </row>
@@ -9842,33 +9796,33 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Data-center share of capex</t>
+          <t>Conversations served per GPU  (Helarctos lever)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>company tabs, row 4</t>
+          <t>Inputs B24/B25 (lever 5)</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>−5%</t>
+          <t>×12 (8k context)</t>
         </is>
       </c>
       <c r="E10" s="40" t="n">
-        <v>-18.75371362936642</v>
+        <v>-17.69341004117427</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>×3,000</t>
         </is>
       </c>
       <c r="G10" s="40" t="n">
-        <v>12.83675643943218</v>
+        <v>0</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>Share of capex that goes into data centres rather than offices and other assets. From the 10-K/10-Q property notes (93–98%; Amazon's AWS share 68–76%).</t>
+          <t>Only matters if it collapses. Inference GPUs are limited by memory (÷100) as long as this stays above ~×24 at the same model size; the estimate is ×368 at 262k.</t>
         </is>
       </c>
     </row>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -4475,10 +4475,10 @@
       <c r="D22" s="90" t="n"/>
       <c r="E22" s="90" t="n"/>
     </row>
-    <row r="23" ht="78" customHeight="1">
+    <row r="23" ht="138" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>H1 · Equal-quality parameter ratio at 1T (smaller model; H2 = same) ★</t>
+          <t>H1 · Equal-quality parameter ratio at ~1T dense-equivalent (smaller model; H2 = same) ★</t>
         </is>
       </c>
       <c r="B23" s="112" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E23" s="91" t="inlineStr">
         <is>
-          <t>FIT-DERIVED (sealed 2026-08-14 refit): bAttention matches the transformer fit's quality on 23.7% of the params at 1T -&gt; x4.22 compute per token at equal quality. 84.2% at 1B, 55.2% at 10B, 36.2% at 100B, 15.5% at 10T (x6.44). A projection of the two fits, not a measurement. Same in both scenarios.</t>
+          <t>FIT-DERIVED (sealed 2026-08-14 refit): bAttention matches the transformer fit's quality on 23.7% of the params at 1T -&gt; x4.22 compute per token at equal quality. 84.2% at 1B, 55.2% at 10B, 36.2% at 100B, 15.5% at 10T (x6.44). A projection of the two fits, not a measurement. Same in both scenarios. Scale: ~1T dense-equivalent: about what today's 5-6T-total mixture-of-experts flagships amount to (Grok 5 at 6T, Kimi K3 at 2.8T; a mixture-of-experts model runs only a fraction of its parameters per token and performs roughly like a dense model of sqrt(total x active) size).</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="63" customHeight="1">
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" s="52" t="inlineStr">
         <is>
           <t>H1</t>
@@ -10078,12 +10078,12 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>PROJECTED — quality trends measured on models we trained (47M–663M parameters), extended to 1T</t>
+          <t>PROJECTED — quality trends measured on models we trained (47M–663M parameters), extended to ~1T dense-equivalent</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>A Helarctos model matches a 1-trillion-parameter transformer's quality with ~24% of the parameters: 4.2× fewer numbers to store, update and run.</t>
+          <t>A Helarctos model matches a ~1T dense-equivalent transformer — about what today's 5–6T-total mixture-of-experts flagships amount to — with ~24% of the parameters: 4.2× fewer numbers to store, update and run.</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="33" customHeight="1">
       <c r="A44" s="66" t="inlineStr">
         <is>
           <t>•</t>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>H1 is a projection: quality trends measured up to 663M parameters, extended to trillion scale.</t>
+          <t>H1 is a projection: quality trends measured up to 663M parameters, extended to ~1T dense-equivalent — about what today's 5–6T-total mixture-of-experts flagships (Grok 5 at 6T, Kimi K3 at 2.8T) amount to.</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
       <c r="G5" s="67" t="n"/>
       <c r="H5" s="67" t="n"/>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="70" t="inlineStr">
         <is>
           <t>★</t>
@@ -10889,15 +10889,15 @@
       </c>
       <c r="F6" s="71" t="inlineStr">
         <is>
-          <t>×6.4</t>
+          <t>×5.7 (5T dense)</t>
         </is>
       </c>
       <c r="G6" s="72" t="n">
-        <v>4.630107479271089</v>
+        <v>3.617436659798898</v>
       </c>
       <c r="H6" s="73" t="inlineStr">
         <is>
-          <t>The biggest Helarctos-specific assumption: it drives the whole training saving (smaller model × fewer tokens). A projection from models up to 663M parameters to trillion scale.</t>
+          <t>The biggest Helarctos-specific assumption: it drives the whole training saving (smaller model × fewer tokens). A projection from models up to 663M parameters to ~1T dense-equivalent (today's 5–6T mixture-of-experts flagships). High case: a 5T dense model.</t>
         </is>
       </c>
     </row>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -4935,7 +4935,7 @@
     <row r="12">
       <c r="A12" s="86" t="inlineStr">
         <is>
-          <t>CONTEXT SENSITIVITY — prefill share of serving cost vs fleet E[context]</t>
+          <t>CONVERSATION-LENGTH SENSITIVITY — prompt share of serving cost vs average conversation length</t>
         </is>
       </c>
       <c r="B12" s="87" t="n"/>
@@ -4947,7 +4947,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="89" t="inlineStr">
         <is>
-          <t>E[context]</t>
+          <t>Conversation length</t>
         </is>
       </c>
       <c r="B13" s="89" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="F17" s="88" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-24/25 (1 x GH200, ONE layer, fwd+bwd, bf16, checkpointing off both arms, modern transformer block 24Q/4KV head_dim 256 RoPE 64 gated): transformer is 1.72x faster at T=2,048 (101.7 vs 59.3 ms/step) and 1.79x at T=8,192; the equal-token B4/T32,768 ~parity cell is RETIRED 2026-08-25 as a B4 occupancy artifact, and the flat per-token model puts the crossover at a PROJECTED T~13,008 (from T~88,000 pre-campaign). It read 6.12x (400.4 ms) the same morning. Training PEAK MEMORY, same frame: 1.579x at T=2,048 (17,087.5 vs 10,823.6 MiB), from 2.829x -- that is TRAINING memory, not the /100 SERVING lever. TARGET (no receipt): T=8,192 step &lt;= 83.08 ms and memory 0.88x.</t>
+          <t>RE-BASED 2026-08-24/25 (1 x GH200, ONE layer, fwd+bwd, bf16, checkpointing off both arms, modern transformer block 24Q/4KV head_dim 256 RoPE 64 gated): transformer is 1.72x faster at T=2,048 (101.7 vs 59.3 ms/step) and 1.79x at T=8,192; the equal-token B4/T32,768 ~parity cell is RETIRED 2026-08-25 as a B4 occupancy artifact, and the flat per-token model puts the crossover at a PROJECTED T~13,008 (from T~88,000 pre-campaign). It read 6.12x (400.4 ms) the same morning. Training PEAK MEMORY, same frame: 1.579x at T=2,048 (17,087.5 vs 10,823.6 MiB), from 2.829x -- that is TRAINING memory, not the H4 serving-memory lever. TARGET (no receipt): T=8,192 step &lt;= 83.08 ms and memory 0.88x.</t>
         </is>
       </c>
     </row>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="33" customHeight="1">
       <c r="A30" s="88" t="inlineStr">
         <is>
-          <t>- Multiplying the levers (100x * ~1,553x) is NOT physical: cost is additive (Amdahl), not multiplicative.</t>
+          <t>- Multiplying the levers (memory x2,032 * tokens per GPU x368) is NOT physical: a GPU is bought whole, so the fleet shrinks by the smaller of the two.</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>fixed at 262k (app: sidebar)</t>
+          <t>262k default (app: sidebar)</t>
         </is>
       </c>
       <c r="D18" s="68" t="inlineStr">
@@ -11615,11 +11615,11 @@
       </c>
       <c r="F18" s="68" t="inlineStr">
         <is>
-          <t>128k</t>
+          <t>262k (default)</t>
         </is>
       </c>
       <c r="G18" s="71" t="n">
-        <v>-0.6276610598471848</v>
+        <v>0</v>
       </c>
       <c r="H18" s="70" t="inlineStr">
         <is>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -11593,7 +11593,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="67" t="inlineStr"/>
       <c r="B18" s="14" t="inlineStr">
         <is>
@@ -11615,15 +11615,15 @@
       </c>
       <c r="F18" s="68" t="inlineStr">
         <is>
-          <t>262k (default)</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G18" s="71" t="n">
-        <v>0</v>
+        <v>0.4844550470273816</v>
       </c>
       <c r="H18" s="70" t="inlineStr">
         <is>
-          <t>Shorter conversations shrink both the memory advantage and tokens per GPU (×48 at 32k). The workbook is fixed at 262k; the app's sidebar lets you change it.</t>
+          <t>Shorter conversations shrink both the memory advantage and tokens per GPU (×48 at 32k); longer ones grow them (×1,411 tokens per GPU at 1M, where one transformer conversation no longer fits a GPU). The workbook is fixed at 262k; the app's sidebar lets you change it.</t>
         </is>
       </c>
     </row>

--- a/AI_Capex_Efficiency.xlsx
+++ b/AI_Capex_Efficiency.xlsx
@@ -2377,14 +2377,16 @@
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Spend made unnecessary, FY2026 (static at the build defaults; the live cells above follow the picker)</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>774.1494653624206</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>777.3625628522243</v>
+          <t>Spend made unnecessary, FY2026 (live: the ladder formula at each scenario's levers; follows the data-centre switch)</t>
+        </is>
+      </c>
+      <c r="B29" s="20">
+        <f>SUMPRODUCT(('Value Bridge'!$D$96:$D$101*(1-1/B24)+'Value Bridge'!$E$96:$E$101*(1-1/MIN(MemoryLever,B26)))*(1+('Value Bridge'!$I$96:$I$101+'Value Bridge'!$R$96:$R$101*ServersFollow+'Value Bridge'!$S$96:$S$101*DCFollow)/'Value Bridge'!$B$96:$B$101))</f>
+        <v/>
+      </c>
+      <c r="C29" s="20">
+        <f>SUMPRODUCT(('Value Bridge'!$D$96:$D$101*(1-1/C24)+'Value Bridge'!$E$96:$E$101*(1-1/MIN(MemoryLever,C26)))*(1+('Value Bridge'!$I$96:$I$101+'Value Bridge'!$R$96:$R$101*ServersFollow+'Value Bridge'!$S$96:$S$101*DCFollow)/'Value Bridge'!$B$96:$B$101))</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1">
